--- a/NFL Current Week Projections.xlsx
+++ b/NFL Current Week Projections.xlsx
@@ -7873,10 +7873,10 @@
         <v>8000</v>
       </c>
       <c r="F5" s="38" t="n">
-        <v>281.5</v>
+        <v>280.5</v>
       </c>
       <c r="G5" s="54" t="n">
-        <v>-225</v>
+        <v>-220</v>
       </c>
       <c r="H5" s="38" t="n">
         <v>0.5</v>
@@ -7888,25 +7888,25 @@
         <v>0.5</v>
       </c>
       <c r="K5" s="39" t="n">
-        <v>0.6923</v>
+        <v>0.6875</v>
       </c>
       <c r="L5" s="39" t="n">
         <v>0.08699999999999999</v>
       </c>
       <c r="M5" s="39" t="n">
-        <v>13.6</v>
+        <v>13.54</v>
       </c>
       <c r="N5" s="40" t="n">
         <v>26.5</v>
       </c>
       <c r="O5" s="40" t="n">
-        <v>18.76</v>
+        <v>18.73</v>
       </c>
       <c r="P5" s="40" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="Q5" s="41" t="n">
-        <v>0.0289</v>
+        <v>0.0283</v>
       </c>
     </row>
     <row r="6">
@@ -7935,37 +7935,37 @@
         <v>253.5</v>
       </c>
       <c r="G6" s="54" t="n">
-        <v>-145</v>
+        <v>-133</v>
       </c>
       <c r="H6" s="38" t="n">
         <v>10.5</v>
       </c>
       <c r="I6" s="54" t="n">
-        <v>700</v>
+        <v>750</v>
       </c>
       <c r="J6" s="38" t="n">
         <v>0.5</v>
       </c>
       <c r="K6" s="45" t="n">
-        <v>0.5918</v>
+        <v>0.5708</v>
       </c>
       <c r="L6" s="45" t="n">
-        <v>0.125</v>
+        <v>0.1176</v>
       </c>
       <c r="M6" s="45" t="n">
-        <v>13.31</v>
+        <v>13.18</v>
       </c>
       <c r="N6" s="40" t="n">
         <v>24.9</v>
       </c>
       <c r="O6" s="40" t="n">
-        <v>17.94</v>
+        <v>17.87</v>
       </c>
       <c r="P6" s="40" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="Q6" s="41" t="n">
-        <v>0.025</v>
+        <v>0.0242</v>
       </c>
     </row>
     <row r="7">
@@ -7991,40 +7991,40 @@
         <v>8500</v>
       </c>
       <c r="F7" s="38" t="n">
-        <v>242</v>
+        <v>241.5</v>
       </c>
       <c r="G7" s="54" t="n">
-        <v>-135</v>
+        <v>-136</v>
       </c>
       <c r="H7" s="38" t="n">
         <v>19.5</v>
       </c>
       <c r="I7" s="54" t="n">
-        <v>360</v>
+        <v>375</v>
       </c>
       <c r="J7" s="38" t="n">
         <v>0.5</v>
       </c>
       <c r="K7" s="45" t="n">
-        <v>0.5745</v>
+        <v>0.5763</v>
       </c>
       <c r="L7" s="45" t="n">
-        <v>0.2174</v>
+        <v>0.2105</v>
       </c>
       <c r="M7" s="45" t="n">
-        <v>14.23</v>
+        <v>14.18</v>
       </c>
       <c r="N7" s="40" t="n">
         <v>28.6</v>
       </c>
       <c r="O7" s="40" t="n">
-        <v>19.98</v>
+        <v>19.95</v>
       </c>
       <c r="P7" s="40" t="n">
         <v>2.35</v>
       </c>
       <c r="Q7" s="41" t="n">
-        <v>0.0341</v>
+        <v>0.0333</v>
       </c>
     </row>
     <row r="8">
@@ -8053,37 +8053,37 @@
         <v>260.5</v>
       </c>
       <c r="G8" s="54" t="n">
-        <v>-165</v>
+        <v>-167</v>
       </c>
       <c r="H8" s="38" t="n">
         <v>6.5</v>
       </c>
       <c r="I8" s="54" t="n">
-        <v>850</v>
+        <v>800</v>
       </c>
       <c r="J8" s="38" t="n">
         <v>0.5</v>
       </c>
       <c r="K8" s="45" t="n">
-        <v>0.6226</v>
+        <v>0.6254999999999999</v>
       </c>
       <c r="L8" s="45" t="n">
-        <v>0.1053</v>
+        <v>0.1111</v>
       </c>
       <c r="M8" s="45" t="n">
-        <v>13.19</v>
+        <v>13.24</v>
       </c>
       <c r="N8" s="40" t="n">
-        <v>27.7</v>
+        <v>27.9</v>
       </c>
       <c r="O8" s="40" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="P8" s="40" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="Q8" s="41" t="n">
-        <v>0.029</v>
+        <v>0.0291</v>
       </c>
     </row>
     <row r="9">
@@ -8114,29 +8114,29 @@
       </c>
       <c r="H9" s="46" t="n"/>
       <c r="I9" s="54" t="n">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="J9" s="46" t="n"/>
       <c r="K9" s="39" t="n">
         <v>0.6875</v>
       </c>
       <c r="L9" s="39" t="n">
-        <v>0.303</v>
+        <v>0.3077</v>
       </c>
       <c r="M9" s="39" t="n">
-        <v>4.57</v>
+        <v>4.6</v>
       </c>
       <c r="N9" s="40" t="n">
-        <v>0</v>
+        <v>26.9</v>
       </c>
       <c r="O9" s="40" t="n">
-        <v>4.57</v>
+        <v>13.52</v>
       </c>
       <c r="P9" s="40" t="n">
-        <v>0.53</v>
+        <v>1.57</v>
       </c>
       <c r="Q9" s="41" t="n">
-        <v>0</v>
+        <v>0.0062</v>
       </c>
     </row>
     <row r="10">
@@ -8162,40 +8162,40 @@
         <v>7700</v>
       </c>
       <c r="F10" s="38" t="n">
-        <v>260.5</v>
+        <v>258.5</v>
       </c>
       <c r="G10" s="54" t="n">
-        <v>-143</v>
+        <v>-140</v>
       </c>
       <c r="H10" s="38" t="n">
         <v>0.5</v>
       </c>
       <c r="I10" s="54" t="n">
-        <v>2200</v>
+        <v>2000</v>
       </c>
       <c r="J10" s="38" t="n">
         <v>0.5</v>
       </c>
       <c r="K10" s="39" t="n">
-        <v>0.5885</v>
+        <v>0.5833</v>
       </c>
       <c r="L10" s="39" t="n">
-        <v>0.0435</v>
+        <v>0.0476</v>
       </c>
       <c r="M10" s="39" t="n">
-        <v>12.08</v>
+        <v>12.01</v>
       </c>
       <c r="N10" s="40" t="n">
         <v>26.7</v>
       </c>
       <c r="O10" s="40" t="n">
-        <v>17.93</v>
+        <v>17.89</v>
       </c>
       <c r="P10" s="40" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="Q10" s="41" t="n">
-        <v>0.0254</v>
+        <v>0.0248</v>
       </c>
     </row>
     <row r="11">
@@ -8221,7 +8221,7 @@
         <v>7600</v>
       </c>
       <c r="F11" s="38" t="n">
-        <v>281.5</v>
+        <v>282.5</v>
       </c>
       <c r="G11" s="54" t="n">
         <v>-180</v>
@@ -8230,7 +8230,7 @@
         <v>7.5</v>
       </c>
       <c r="I11" s="54" t="n">
-        <v>800</v>
+        <v>825</v>
       </c>
       <c r="J11" s="38" t="n">
         <v>0.5</v>
@@ -8239,22 +8239,22 @@
         <v>0.6429</v>
       </c>
       <c r="L11" s="39" t="n">
-        <v>0.1111</v>
+        <v>0.1081</v>
       </c>
       <c r="M11" s="39" t="n">
-        <v>14.25</v>
+        <v>14.27</v>
       </c>
       <c r="N11" s="40" t="n">
         <v>28</v>
       </c>
       <c r="O11" s="40" t="n">
-        <v>19.75</v>
+        <v>19.76</v>
       </c>
       <c r="P11" s="40" t="n">
         <v>2.6</v>
       </c>
       <c r="Q11" s="41" t="n">
-        <v>0.0377</v>
+        <v>0.0371</v>
       </c>
     </row>
     <row r="12">
@@ -8280,7 +8280,7 @@
         <v>7500</v>
       </c>
       <c r="F12" s="38" t="n">
-        <v>256.5</v>
+        <v>255.5</v>
       </c>
       <c r="G12" s="54" t="n">
         <v>-165</v>
@@ -8301,19 +8301,19 @@
         <v>0.1538</v>
       </c>
       <c r="M12" s="45" t="n">
-        <v>13.62</v>
+        <v>13.58</v>
       </c>
       <c r="N12" s="40" t="n">
-        <v>27.4</v>
+        <v>27.5</v>
       </c>
       <c r="O12" s="40" t="n">
-        <v>19.13</v>
+        <v>19.15</v>
       </c>
       <c r="P12" s="40" t="n">
         <v>2.55</v>
       </c>
       <c r="Q12" s="41" t="n">
-        <v>0.0339</v>
+        <v>0.0335</v>
       </c>
     </row>
     <row r="13">
@@ -8339,40 +8339,40 @@
         <v>6800</v>
       </c>
       <c r="F13" s="38" t="n">
-        <v>237.5</v>
+        <v>239.5</v>
       </c>
       <c r="G13" s="54" t="n">
-        <v>105</v>
+        <v>-101</v>
       </c>
       <c r="H13" s="38" t="n">
         <v>1.5</v>
       </c>
       <c r="I13" s="54" t="n">
-        <v>2200</v>
+        <v>2000</v>
       </c>
       <c r="J13" s="38" t="n">
         <v>0.5</v>
       </c>
       <c r="K13" s="45" t="n">
-        <v>0.4878</v>
+        <v>0.5024999999999999</v>
       </c>
       <c r="L13" s="45" t="n">
-        <v>0.0435</v>
+        <v>0.0476</v>
       </c>
       <c r="M13" s="45" t="n">
-        <v>10.86</v>
+        <v>11.03</v>
       </c>
       <c r="N13" s="40" t="n">
         <v>23.8</v>
       </c>
       <c r="O13" s="40" t="n">
-        <v>16.04</v>
+        <v>16.14</v>
       </c>
       <c r="P13" s="40" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="Q13" s="41" t="n">
-        <v>0.0188</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="14">
@@ -8398,7 +8398,7 @@
         <v>6900</v>
       </c>
       <c r="F14" s="38" t="n">
-        <v>228</v>
+        <v>230.5</v>
       </c>
       <c r="G14" s="54" t="n">
         <v>122</v>
@@ -8419,13 +8419,13 @@
         <v>0.08</v>
       </c>
       <c r="M14" s="39" t="n">
-        <v>10.55</v>
+        <v>10.65</v>
       </c>
       <c r="N14" s="40" t="n">
         <v>20.5</v>
       </c>
       <c r="O14" s="40" t="n">
-        <v>14.53</v>
+        <v>14.59</v>
       </c>
       <c r="P14" s="40" t="n">
         <v>2.11</v>
@@ -8457,16 +8457,16 @@
         <v>7000</v>
       </c>
       <c r="F15" s="38" t="n">
-        <v>225.5</v>
+        <v>227.5</v>
       </c>
       <c r="G15" s="54" t="n">
         <v>143</v>
       </c>
       <c r="H15" s="38" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="I15" s="54" t="n">
-        <v>800</v>
+        <v>850</v>
       </c>
       <c r="J15" s="38" t="n">
         <v>0.5</v>
@@ -8475,22 +8475,22 @@
         <v>0.4115</v>
       </c>
       <c r="L15" s="45" t="n">
-        <v>0.1111</v>
+        <v>0.1053</v>
       </c>
       <c r="M15" s="45" t="n">
-        <v>11.08</v>
+        <v>11.03</v>
       </c>
       <c r="N15" s="40" t="n">
         <v>20.5</v>
       </c>
       <c r="O15" s="40" t="n">
-        <v>14.85</v>
+        <v>14.82</v>
       </c>
       <c r="P15" s="40" t="n">
         <v>2.12</v>
       </c>
       <c r="Q15" s="41" t="n">
-        <v>0.0129</v>
+        <v>0.0126</v>
       </c>
     </row>
     <row r="16">
@@ -8516,40 +8516,40 @@
         <v>7400</v>
       </c>
       <c r="F16" s="38" t="n">
-        <v>205.5</v>
+        <v>208.5</v>
       </c>
       <c r="G16" s="54" t="n">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="H16" s="38" t="n">
         <v>29.5</v>
       </c>
       <c r="I16" s="54" t="n">
-        <v>410</v>
+        <v>380</v>
       </c>
       <c r="J16" s="38" t="n">
         <v>0.5</v>
       </c>
       <c r="K16" s="45" t="n">
-        <v>0.3876</v>
+        <v>0.3774</v>
       </c>
       <c r="L16" s="45" t="n">
-        <v>0.1961</v>
+        <v>0.2083</v>
       </c>
       <c r="M16" s="45" t="n">
-        <v>12.9</v>
+        <v>13.05</v>
       </c>
       <c r="N16" s="40" t="n">
         <v>19.4</v>
       </c>
       <c r="O16" s="40" t="n">
-        <v>15.5</v>
+        <v>15.59</v>
       </c>
       <c r="P16" s="40" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="Q16" s="41" t="n">
-        <v>0.0145</v>
+        <v>0.0147</v>
       </c>
     </row>
     <row r="17">
@@ -8575,10 +8575,10 @@
         <v>6900</v>
       </c>
       <c r="F17" s="38" t="n">
-        <v>222</v>
+        <v>221.5</v>
       </c>
       <c r="G17" s="54" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="H17" s="38" t="n">
         <v>6.5</v>
@@ -8590,25 +8590,25 @@
         <v>0.5</v>
       </c>
       <c r="K17" s="39" t="n">
-        <v>0.4762</v>
+        <v>0.4651</v>
       </c>
       <c r="L17" s="39" t="n">
         <v>0.1053</v>
       </c>
       <c r="M17" s="39" t="n">
-        <v>11.07</v>
+        <v>11</v>
       </c>
       <c r="N17" s="40" t="n">
         <v>22.7</v>
       </c>
       <c r="O17" s="40" t="n">
-        <v>15.72</v>
+        <v>15.68</v>
       </c>
       <c r="P17" s="40" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="Q17" s="41" t="n">
-        <v>0.0169</v>
+        <v>0.0165</v>
       </c>
     </row>
     <row r="18">
@@ -8736,16 +8736,16 @@
         <v>6600</v>
       </c>
       <c r="F20" s="38" t="n">
-        <v>182.5</v>
+        <v>183.5</v>
       </c>
       <c r="G20" s="54" t="n">
         <v>-196</v>
       </c>
       <c r="H20" s="38" t="n">
-        <v>30</v>
+        <v>30.5</v>
       </c>
       <c r="I20" s="54" t="n">
-        <v>400</v>
+        <v>370</v>
       </c>
       <c r="J20" s="38" t="n">
         <v>0.5</v>
@@ -8754,22 +8754,22 @@
         <v>0.6622</v>
       </c>
       <c r="L20" s="39" t="n">
-        <v>0.2</v>
+        <v>0.2128</v>
       </c>
       <c r="M20" s="39" t="n">
-        <v>13.15</v>
+        <v>13.32</v>
       </c>
       <c r="N20" s="40" t="n">
         <v>17.4</v>
       </c>
       <c r="O20" s="40" t="n">
-        <v>14.85</v>
+        <v>14.95</v>
       </c>
       <c r="P20" s="40" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="Q20" s="41" t="n">
-        <v>0.0139</v>
+        <v>0.0141</v>
       </c>
     </row>
     <row r="21">
@@ -8795,7 +8795,7 @@
         <v>7100</v>
       </c>
       <c r="F21" s="38" t="n">
-        <v>215.5</v>
+        <v>216.5</v>
       </c>
       <c r="G21" s="54" t="n">
         <v>155</v>
@@ -8804,7 +8804,7 @@
         <v>16.5</v>
       </c>
       <c r="I21" s="54" t="n">
-        <v>500</v>
+        <v>525</v>
       </c>
       <c r="J21" s="38" t="n">
         <v>0.5</v>
@@ -8813,7 +8813,7 @@
         <v>0.3922</v>
       </c>
       <c r="L21" s="45" t="n">
-        <v>0.1667</v>
+        <v>0.16</v>
       </c>
       <c r="M21" s="45" t="n">
         <v>11.84</v>
@@ -8828,7 +8828,7 @@
         <v>2.2</v>
       </c>
       <c r="Q21" s="41" t="n">
-        <v>0.0159</v>
+        <v>0.0156</v>
       </c>
     </row>
     <row r="22">
@@ -8854,13 +8854,13 @@
         <v>7200</v>
       </c>
       <c r="F22" s="38" t="n">
-        <v>221.5</v>
+        <v>219.5</v>
       </c>
       <c r="G22" s="54" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="H22" s="38" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="I22" s="54" t="n">
         <v>450</v>
@@ -8869,25 +8869,25 @@
         <v>0.5</v>
       </c>
       <c r="K22" s="39" t="n">
-        <v>0.463</v>
+        <v>0.4545</v>
       </c>
       <c r="L22" s="39" t="n">
         <v>0.1818</v>
       </c>
       <c r="M22" s="39" t="n">
-        <v>11.9</v>
+        <v>11.74</v>
       </c>
       <c r="N22" s="40" t="n">
         <v>22.3</v>
       </c>
       <c r="O22" s="40" t="n">
-        <v>16.06</v>
+        <v>15.96</v>
       </c>
       <c r="P22" s="40" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="Q22" s="41" t="n">
-        <v>0.0176</v>
+        <v>0.0168</v>
       </c>
     </row>
     <row r="23">
@@ -8913,10 +8913,10 @@
         <v>6500</v>
       </c>
       <c r="F23" s="38" t="n">
-        <v>182.5</v>
+        <v>181.5</v>
       </c>
       <c r="G23" s="54" t="n">
-        <v>-225</v>
+        <v>-200</v>
       </c>
       <c r="H23" s="38" t="n">
         <v>9.5</v>
@@ -8928,25 +8928,25 @@
         <v>0.5</v>
       </c>
       <c r="K23" s="39" t="n">
-        <v>0.6923</v>
+        <v>0.6667</v>
       </c>
       <c r="L23" s="39" t="n">
         <v>0.1538</v>
       </c>
       <c r="M23" s="39" t="n">
-        <v>10.94</v>
+        <v>10.8</v>
       </c>
       <c r="N23" s="40" t="n">
         <v>15.9</v>
       </c>
       <c r="O23" s="40" t="n">
-        <v>12.93</v>
+        <v>12.84</v>
       </c>
       <c r="P23" s="40" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="Q23" s="41" t="n">
-        <v>0.0072</v>
+        <v>0.0069</v>
       </c>
     </row>
     <row r="24">
@@ -8972,13 +8972,13 @@
         <v>6700</v>
       </c>
       <c r="F24" s="38" t="n">
-        <v>194.5</v>
+        <v>188.5</v>
       </c>
       <c r="G24" s="54" t="n">
-        <v>-218</v>
+        <v>-235</v>
       </c>
       <c r="H24" s="38" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="I24" s="54" t="n">
         <v>850</v>
@@ -8987,25 +8987,25 @@
         <v>0.5</v>
       </c>
       <c r="K24" s="45" t="n">
-        <v>0.6855</v>
+        <v>0.7015</v>
       </c>
       <c r="L24" s="45" t="n">
         <v>0.1053</v>
       </c>
       <c r="M24" s="45" t="n">
-        <v>10.8</v>
+        <v>10.73</v>
       </c>
       <c r="N24" s="40" t="n">
         <v>13.6</v>
       </c>
       <c r="O24" s="40" t="n">
-        <v>11.92</v>
+        <v>11.88</v>
       </c>
       <c r="P24" s="40" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="Q24" s="41" t="n">
-        <v>0.0044</v>
+        <v>0.0043</v>
       </c>
     </row>
     <row r="25">
@@ -9031,40 +9031,40 @@
         <v>7300</v>
       </c>
       <c r="F25" s="38" t="n">
-        <v>205.5</v>
+        <v>209.5</v>
       </c>
       <c r="G25" s="54" t="n">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="H25" s="38" t="n">
-        <v>24.5</v>
+        <v>25.5</v>
       </c>
       <c r="I25" s="54" t="n">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="J25" s="38" t="n">
         <v>0.5</v>
       </c>
       <c r="K25" s="45" t="n">
-        <v>0.4405</v>
+        <v>0.4587</v>
       </c>
       <c r="L25" s="45" t="n">
-        <v>0.1887</v>
+        <v>0.1905</v>
       </c>
       <c r="M25" s="45" t="n">
-        <v>12.56</v>
+        <v>12.91</v>
       </c>
       <c r="N25" s="40" t="n">
         <v>25</v>
       </c>
       <c r="O25" s="40" t="n">
-        <v>17.54</v>
+        <v>17.74</v>
       </c>
       <c r="P25" s="40" t="n">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="Q25" s="41" t="n">
-        <v>0.0249</v>
+        <v>0.0256</v>
       </c>
     </row>
     <row r="26">
@@ -9106,16 +9106,16 @@
         <v>2.75</v>
       </c>
       <c r="N26" s="40" t="n">
-        <v>20.8</v>
+        <v>0</v>
       </c>
       <c r="O26" s="40" t="n">
-        <v>9.970000000000001</v>
+        <v>2.75</v>
       </c>
       <c r="P26" s="40" t="n">
-        <v>1.42</v>
+        <v>0.39</v>
       </c>
       <c r="Q26" s="41" t="n">
-        <v>0.0012</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -9347,16 +9347,16 @@
         <v>6700</v>
       </c>
       <c r="F31" s="38" t="n">
-        <v>201.5</v>
+        <v>203.5</v>
       </c>
       <c r="G31" s="54" t="n">
         <v>-211</v>
       </c>
       <c r="H31" s="38" t="n">
-        <v>23.5</v>
+        <v>22.5</v>
       </c>
       <c r="I31" s="54" t="n">
-        <v>550</v>
+        <v>500</v>
       </c>
       <c r="J31" s="38" t="n">
         <v>0.5</v>
@@ -9365,22 +9365,22 @@
         <v>0.6785</v>
       </c>
       <c r="L31" s="39" t="n">
-        <v>0.1538</v>
+        <v>0.1667</v>
       </c>
       <c r="M31" s="39" t="n">
-        <v>13.05</v>
+        <v>13.1</v>
       </c>
       <c r="N31" s="40" t="n">
         <v>23.5</v>
       </c>
       <c r="O31" s="40" t="n">
-        <v>17.23</v>
+        <v>17.26</v>
       </c>
       <c r="P31" s="40" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="Q31" s="41" t="n">
-        <v>0.0259</v>
+        <v>0.0256</v>
       </c>
     </row>
     <row r="32">
@@ -12718,7 +12718,7 @@
         <v>2.34</v>
       </c>
       <c r="O5" s="41" t="n">
-        <v>0.1584</v>
+        <v>0.112</v>
       </c>
     </row>
     <row r="6">
@@ -12744,34 +12744,34 @@
         <v>9400</v>
       </c>
       <c r="F6" s="38" t="n">
-        <v>87.5</v>
+        <v>88.5</v>
       </c>
       <c r="G6" s="54" t="n">
-        <v>-235</v>
+        <v>-275</v>
       </c>
       <c r="H6" s="38" t="n">
         <v>3.5</v>
       </c>
       <c r="I6" s="38" t="n">
-        <v>27.5</v>
+        <v>29.5</v>
       </c>
       <c r="J6" s="45" t="n">
-        <v>0.7015</v>
+        <v>0.7333</v>
       </c>
       <c r="K6" s="39" t="n">
-        <v>17.46</v>
+        <v>17.95</v>
       </c>
       <c r="L6" s="45" t="n">
-        <v>20.3</v>
+        <v>22.4</v>
       </c>
       <c r="M6" s="40" t="n">
-        <v>18.6</v>
+        <v>19.73</v>
       </c>
       <c r="N6" s="40" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="O6" s="41" t="n">
-        <v>0.0864</v>
+        <v>0.0737</v>
       </c>
     </row>
     <row r="7">
@@ -12797,10 +12797,10 @@
         <v>7100</v>
       </c>
       <c r="F7" s="38" t="n">
-        <v>69.5</v>
+        <v>65.5</v>
       </c>
       <c r="G7" s="54" t="n">
-        <v>-125</v>
+        <v>-118</v>
       </c>
       <c r="H7" s="38" t="n">
         <v>2.5</v>
@@ -12809,22 +12809,22 @@
         <v>14.5</v>
       </c>
       <c r="J7" s="39" t="n">
-        <v>0.5556</v>
+        <v>0.5413</v>
       </c>
       <c r="K7" s="39" t="n">
-        <v>12.98</v>
+        <v>12.5</v>
       </c>
       <c r="L7" s="39" t="n">
         <v>16</v>
       </c>
       <c r="M7" s="40" t="n">
-        <v>14.19</v>
+        <v>13.9</v>
       </c>
       <c r="N7" s="40" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="O7" s="41" t="n">
-        <v>0.0511</v>
+        <v>0.0336</v>
       </c>
     </row>
     <row r="8">
@@ -12850,10 +12850,10 @@
         <v>9000</v>
       </c>
       <c r="F8" s="38" t="n">
-        <v>86</v>
+        <v>85.5</v>
       </c>
       <c r="G8" s="54" t="n">
-        <v>-210</v>
+        <v>-200</v>
       </c>
       <c r="H8" s="38" t="n">
         <v>1.5</v>
@@ -12862,22 +12862,22 @@
         <v>6.5</v>
       </c>
       <c r="J8" s="45" t="n">
-        <v>0.6774</v>
+        <v>0.6667</v>
       </c>
       <c r="K8" s="39" t="n">
-        <v>14.06</v>
+        <v>13.95</v>
       </c>
       <c r="L8" s="45" t="n">
-        <v>20.3</v>
+        <v>22.5</v>
       </c>
       <c r="M8" s="40" t="n">
-        <v>16.56</v>
+        <v>17.37</v>
       </c>
       <c r="N8" s="40" t="n">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="O8" s="41" t="n">
-        <v>0.06270000000000001</v>
+        <v>0.0518</v>
       </c>
     </row>
     <row r="9">
@@ -12903,34 +12903,34 @@
         <v>8500</v>
       </c>
       <c r="F9" s="38" t="n">
-        <v>71.5</v>
+        <v>70.5</v>
       </c>
       <c r="G9" s="54" t="n">
-        <v>-118</v>
+        <v>-110</v>
       </c>
       <c r="H9" s="38" t="n">
         <v>2.5</v>
       </c>
       <c r="I9" s="38" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="J9" s="45" t="n">
-        <v>0.5413</v>
+        <v>0.5238</v>
       </c>
       <c r="K9" s="39" t="n">
-        <v>13.3</v>
+        <v>13.19</v>
       </c>
       <c r="L9" s="45" t="n">
         <v>16.5</v>
       </c>
       <c r="M9" s="40" t="n">
-        <v>14.58</v>
+        <v>14.52</v>
       </c>
       <c r="N9" s="40" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="O9" s="41" t="n">
-        <v>0.0443</v>
+        <v>0.0309</v>
       </c>
     </row>
     <row r="10">
@@ -12959,7 +12959,7 @@
         <v>60.5</v>
       </c>
       <c r="G10" s="54" t="n">
-        <v>-225</v>
+        <v>-235</v>
       </c>
       <c r="H10" s="38" t="n">
         <v>5.5</v>
@@ -12968,22 +12968,22 @@
         <v>44.5</v>
       </c>
       <c r="J10" s="39" t="n">
-        <v>0.6923</v>
+        <v>0.7015</v>
       </c>
       <c r="K10" s="39" t="n">
-        <v>17.4</v>
+        <v>17.46</v>
       </c>
       <c r="L10" s="39" t="n">
         <v>22.4</v>
       </c>
       <c r="M10" s="40" t="n">
-        <v>19.4</v>
+        <v>19.44</v>
       </c>
       <c r="N10" s="40" t="n">
         <v>2.23</v>
       </c>
       <c r="O10" s="41" t="n">
-        <v>0.1094</v>
+        <v>0.07779999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -13009,34 +13009,34 @@
         <v>7900</v>
       </c>
       <c r="F11" s="38" t="n">
-        <v>63.5</v>
+        <v>68.5</v>
       </c>
       <c r="G11" s="54" t="n">
-        <v>-150</v>
+        <v>-137</v>
       </c>
       <c r="H11" s="38" t="n">
         <v>3.5</v>
       </c>
       <c r="I11" s="38" t="n">
-        <v>25.5</v>
+        <v>27.5</v>
       </c>
       <c r="J11" s="39" t="n">
-        <v>0.6</v>
+        <v>0.5780999999999999</v>
       </c>
       <c r="K11" s="39" t="n">
-        <v>14.25</v>
+        <v>14.82</v>
       </c>
       <c r="L11" s="39" t="n">
-        <v>20.2</v>
+        <v>21</v>
       </c>
       <c r="M11" s="40" t="n">
-        <v>16.63</v>
+        <v>17.29</v>
       </c>
       <c r="N11" s="40" t="n">
-        <v>2.11</v>
+        <v>2.19</v>
       </c>
       <c r="O11" s="41" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.0605</v>
       </c>
     </row>
     <row r="12">
@@ -13062,10 +13062,10 @@
         <v>7400</v>
       </c>
       <c r="F12" s="38" t="n">
-        <v>51.5</v>
+        <v>54.5</v>
       </c>
       <c r="G12" s="54" t="n">
-        <v>-125</v>
+        <v>-118</v>
       </c>
       <c r="H12" s="38" t="n">
         <v>3.5</v>
@@ -13074,22 +13074,22 @@
         <v>25.5</v>
       </c>
       <c r="J12" s="39" t="n">
-        <v>0.5556</v>
+        <v>0.5413</v>
       </c>
       <c r="K12" s="39" t="n">
-        <v>12.78</v>
+        <v>13</v>
       </c>
       <c r="L12" s="39" t="n">
         <v>17.6</v>
       </c>
       <c r="M12" s="40" t="n">
-        <v>14.71</v>
+        <v>14.84</v>
       </c>
       <c r="N12" s="40" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="O12" s="41" t="n">
-        <v>0.0546</v>
+        <v>0.0398</v>
       </c>
     </row>
     <row r="13">
@@ -13115,10 +13115,10 @@
         <v>5900</v>
       </c>
       <c r="F13" s="38" t="n">
-        <v>40.5</v>
+        <v>38.5</v>
       </c>
       <c r="G13" s="54" t="n">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="H13" s="38" t="n">
         <v>2.5</v>
@@ -13127,22 +13127,22 @@
         <v>14.5</v>
       </c>
       <c r="J13" s="39" t="n">
-        <v>0.4167</v>
+        <v>0.4082</v>
       </c>
       <c r="K13" s="39" t="n">
-        <v>9.25</v>
+        <v>9</v>
       </c>
       <c r="L13" s="39" t="n">
         <v>12.7</v>
       </c>
       <c r="M13" s="40" t="n">
-        <v>10.63</v>
+        <v>10.48</v>
       </c>
       <c r="N13" s="40" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="O13" s="41" t="n">
-        <v>0.0234</v>
+        <v>0.0157</v>
       </c>
     </row>
     <row r="14">
@@ -13169,27 +13169,27 @@
       </c>
       <c r="F14" s="38" t="n"/>
       <c r="G14" s="54" t="n">
-        <v>-111</v>
+        <v>105</v>
       </c>
       <c r="H14" s="38" t="n"/>
       <c r="I14" s="38" t="n"/>
       <c r="J14" s="39" t="n">
-        <v>0.5261</v>
+        <v>0.4878</v>
       </c>
       <c r="K14" s="39" t="n">
-        <v>3.16</v>
+        <v>2.93</v>
       </c>
       <c r="L14" s="39" t="n">
         <v>15.4</v>
       </c>
       <c r="M14" s="40" t="n">
-        <v>8.050000000000001</v>
+        <v>7.92</v>
       </c>
       <c r="N14" s="40" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="O14" s="41" t="n">
-        <v>0.0064</v>
+        <v>0.0042</v>
       </c>
     </row>
     <row r="15">
@@ -13215,7 +13215,7 @@
         <v>7200</v>
       </c>
       <c r="F15" s="38" t="n">
-        <v>66</v>
+        <v>65.5</v>
       </c>
       <c r="G15" s="54" t="n">
         <v>115</v>
@@ -13224,25 +13224,25 @@
         <v>2.5</v>
       </c>
       <c r="I15" s="38" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="J15" s="39" t="n">
         <v>0.4651</v>
       </c>
       <c r="K15" s="39" t="n">
-        <v>12.19</v>
+        <v>12.24</v>
       </c>
       <c r="L15" s="39" t="n">
         <v>15</v>
       </c>
       <c r="M15" s="40" t="n">
-        <v>13.31</v>
+        <v>13.34</v>
       </c>
       <c r="N15" s="40" t="n">
         <v>1.85</v>
       </c>
       <c r="O15" s="41" t="n">
-        <v>0.0403</v>
+        <v>0.0287</v>
       </c>
     </row>
     <row r="16">
@@ -13268,7 +13268,7 @@
         <v>6000</v>
       </c>
       <c r="F16" s="38" t="n">
-        <v>51.5</v>
+        <v>54.5</v>
       </c>
       <c r="G16" s="54" t="n">
         <v>200</v>
@@ -13277,25 +13277,25 @@
         <v>1.5</v>
       </c>
       <c r="I16" s="38" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="J16" s="39" t="n">
         <v>0.3333</v>
       </c>
       <c r="K16" s="39" t="n">
-        <v>8.65</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="L16" s="39" t="n">
         <v>13.1</v>
       </c>
       <c r="M16" s="40" t="n">
-        <v>10.43</v>
+        <v>10.67</v>
       </c>
       <c r="N16" s="40" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="O16" s="41" t="n">
-        <v>0.0213</v>
+        <v>0.0164</v>
       </c>
     </row>
     <row r="17">
@@ -13321,30 +13321,30 @@
         <v>5800</v>
       </c>
       <c r="F17" s="38" t="n">
-        <v>46.5</v>
+        <v>49</v>
       </c>
       <c r="G17" s="54" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="H17" s="46" t="n"/>
       <c r="I17" s="46" t="n"/>
       <c r="J17" s="45" t="n">
-        <v>0.3846</v>
+        <v>0.3704</v>
       </c>
       <c r="K17" s="39" t="n">
-        <v>6.96</v>
+        <v>7.12</v>
       </c>
       <c r="L17" s="45" t="n">
         <v>11.6</v>
       </c>
       <c r="M17" s="40" t="n">
-        <v>8.81</v>
+        <v>8.91</v>
       </c>
       <c r="N17" s="40" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="O17" s="41" t="n">
-        <v>0.0116</v>
+        <v>0.0086</v>
       </c>
     </row>
     <row r="18">
@@ -13370,28 +13370,26 @@
         <v>4900</v>
       </c>
       <c r="F18" s="38" t="n"/>
-      <c r="G18" s="54" t="n">
-        <v>475</v>
-      </c>
+      <c r="G18" s="54" t="n"/>
       <c r="H18" s="38" t="n"/>
       <c r="I18" s="38" t="n"/>
       <c r="J18" s="45" t="n">
         <v>0.1739</v>
       </c>
       <c r="K18" s="39" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="L18" s="45" t="n">
         <v>0</v>
       </c>
       <c r="M18" s="40" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="N18" s="40" t="n">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="O18" s="41" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="19">
@@ -13417,10 +13415,10 @@
         <v>7800</v>
       </c>
       <c r="F19" s="38" t="n">
-        <v>47.5</v>
+        <v>41.5</v>
       </c>
       <c r="G19" s="54" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="H19" s="38" t="n">
         <v>3.5</v>
@@ -13429,22 +13427,22 @@
         <v>20.5</v>
       </c>
       <c r="J19" s="39" t="n">
-        <v>0.5</v>
+        <v>0.4878</v>
       </c>
       <c r="K19" s="39" t="n">
-        <v>11.55</v>
+        <v>10.88</v>
       </c>
       <c r="L19" s="39" t="n">
-        <v>14.9</v>
+        <v>14.6</v>
       </c>
       <c r="M19" s="40" t="n">
-        <v>12.89</v>
+        <v>12.37</v>
       </c>
       <c r="N19" s="40" t="n">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="O19" s="41" t="n">
-        <v>0.0325</v>
+        <v>0.0199</v>
       </c>
     </row>
     <row r="20">
@@ -13561,34 +13559,34 @@
         <v>6500</v>
       </c>
       <c r="F22" s="38" t="n">
-        <v>45.5</v>
+        <v>46.5</v>
       </c>
       <c r="G22" s="54" t="n">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="H22" s="38" t="n">
         <v>2.5</v>
       </c>
       <c r="I22" s="38" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="J22" s="45" t="n">
-        <v>0.3774</v>
+        <v>0.3448</v>
       </c>
       <c r="K22" s="39" t="n">
-        <v>9.66</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="L22" s="45" t="n">
         <v>14.1</v>
       </c>
       <c r="M22" s="40" t="n">
-        <v>11.44</v>
+        <v>11.17</v>
       </c>
       <c r="N22" s="40" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="O22" s="41" t="n">
-        <v>0.027</v>
+        <v>0.0175</v>
       </c>
     </row>
     <row r="23">
@@ -13614,30 +13612,30 @@
         <v>6600</v>
       </c>
       <c r="F23" s="38" t="n">
-        <v>31.5</v>
+        <v>28.5</v>
       </c>
       <c r="G23" s="54" t="n">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="H23" s="38" t="n"/>
       <c r="I23" s="38" t="n"/>
       <c r="J23" s="45" t="n">
-        <v>0.2174</v>
+        <v>0.2128</v>
       </c>
       <c r="K23" s="39" t="n">
-        <v>4.45</v>
+        <v>4.13</v>
       </c>
       <c r="L23" s="45" t="n">
         <v>7.3</v>
       </c>
       <c r="M23" s="40" t="n">
-        <v>5.59</v>
+        <v>5.4</v>
       </c>
       <c r="N23" s="40" t="n">
-        <v>0.85</v>
+        <v>0.82</v>
       </c>
       <c r="O23" s="41" t="n">
-        <v>0.001</v>
+        <v>0.0005999999999999999</v>
       </c>
     </row>
     <row r="24">
@@ -13664,27 +13662,27 @@
       </c>
       <c r="F24" s="38" t="n"/>
       <c r="G24" s="54" t="n">
-        <v>-105</v>
+        <v>-110</v>
       </c>
       <c r="H24" s="38" t="n"/>
       <c r="I24" s="38" t="n"/>
       <c r="J24" s="39" t="n">
-        <v>0.5122</v>
+        <v>0.5238</v>
       </c>
       <c r="K24" s="39" t="n">
-        <v>3.07</v>
+        <v>3.14</v>
       </c>
       <c r="L24" s="39" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="M24" s="40" t="n">
-        <v>5.76</v>
+        <v>5.81</v>
       </c>
       <c r="N24" s="40" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="O24" s="41" t="n">
-        <v>0.0013</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="25">
@@ -13722,16 +13720,16 @@
         <v>2.31</v>
       </c>
       <c r="L25" s="45" t="n">
-        <v>13.1</v>
+        <v>0</v>
       </c>
       <c r="M25" s="40" t="n">
-        <v>6.62</v>
+        <v>2.31</v>
       </c>
       <c r="N25" s="40" t="n">
-        <v>1.09</v>
+        <v>0.38</v>
       </c>
       <c r="O25" s="41" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -13756,31 +13754,27 @@
       <c r="E26" s="37" t="n">
         <v>5400</v>
       </c>
-      <c r="F26" s="38" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="G26" s="54" t="n">
-        <v>270</v>
-      </c>
+      <c r="F26" s="38" t="n"/>
+      <c r="G26" s="54" t="n"/>
       <c r="H26" s="38" t="n"/>
       <c r="I26" s="38" t="n"/>
       <c r="J26" s="39" t="n">
         <v>0.2703</v>
       </c>
       <c r="K26" s="39" t="n">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="L26" s="39" t="n">
-        <v>6.7</v>
+        <v>22.4</v>
       </c>
       <c r="M26" s="40" t="n">
-        <v>5.12</v>
+        <v>22.4</v>
       </c>
       <c r="N26" s="40" t="n">
-        <v>0.95</v>
+        <v>4.15</v>
       </c>
       <c r="O26" s="41" t="n">
-        <v>0.0007</v>
+        <v>0.2262</v>
       </c>
     </row>
     <row r="27">
@@ -13806,28 +13800,26 @@
         <v>6400</v>
       </c>
       <c r="F27" s="46" t="n"/>
-      <c r="G27" s="54" t="n">
-        <v>-167</v>
-      </c>
+      <c r="G27" s="54" t="n"/>
       <c r="H27" s="46" t="n"/>
       <c r="I27" s="46" t="n"/>
       <c r="J27" s="45" t="n">
         <v>0.6254999999999999</v>
       </c>
       <c r="K27" s="39" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="L27" s="45" t="n">
         <v>0</v>
       </c>
       <c r="M27" s="40" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N27" s="40" t="n">
-        <v>0.59</v>
+        <v>0</v>
       </c>
       <c r="O27" s="41" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="28">
@@ -13853,10 +13845,10 @@
         <v>5800</v>
       </c>
       <c r="F28" s="38" t="n">
-        <v>18.5</v>
+        <v>14.5</v>
       </c>
       <c r="G28" s="54" t="n">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="H28" s="38" t="n">
         <v>3.5</v>
@@ -13865,22 +13857,22 @@
         <v>24.5</v>
       </c>
       <c r="J28" s="45" t="n">
-        <v>0.2632</v>
+        <v>0.2597</v>
       </c>
       <c r="K28" s="39" t="n">
-        <v>7.63</v>
+        <v>7.21</v>
       </c>
       <c r="L28" s="45" t="n">
         <v>11</v>
       </c>
       <c r="M28" s="40" t="n">
-        <v>8.98</v>
+        <v>8.73</v>
       </c>
       <c r="N28" s="40" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="O28" s="41" t="n">
-        <v>0.0125</v>
+        <v>0.007900000000000001</v>
       </c>
     </row>
     <row r="29">
@@ -13906,7 +13898,7 @@
         <v>5500</v>
       </c>
       <c r="F29" s="38" t="n">
-        <v>35.5</v>
+        <v>36.5</v>
       </c>
       <c r="G29" s="54" t="n">
         <v>180</v>
@@ -13915,25 +13907,25 @@
         <v>1.5</v>
       </c>
       <c r="I29" s="38" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="J29" s="39" t="n">
         <v>0.3571</v>
       </c>
       <c r="K29" s="39" t="n">
-        <v>7.59</v>
+        <v>7.54</v>
       </c>
       <c r="L29" s="39" t="n">
-        <v>10.7</v>
+        <v>11.4</v>
       </c>
       <c r="M29" s="40" t="n">
-        <v>8.84</v>
+        <v>9.09</v>
       </c>
       <c r="N29" s="40" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="O29" s="41" t="n">
-        <v>0.0126</v>
+        <v>0.009900000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -13960,24 +13952,24 @@
       </c>
       <c r="F30" s="46" t="n"/>
       <c r="G30" s="54" t="n">
-        <v>290</v>
+        <v>800</v>
       </c>
       <c r="H30" s="46" t="n"/>
       <c r="I30" s="46" t="n"/>
       <c r="J30" s="45" t="n">
-        <v>0.2564</v>
+        <v>0.1111</v>
       </c>
       <c r="K30" s="39" t="n">
-        <v>1.54</v>
+        <v>0.67</v>
       </c>
       <c r="L30" s="45" t="n">
         <v>0</v>
       </c>
       <c r="M30" s="40" t="n">
-        <v>1.54</v>
+        <v>0.67</v>
       </c>
       <c r="N30" s="40" t="n">
-        <v>0.33</v>
+        <v>0.14</v>
       </c>
       <c r="O30" s="41" t="n">
         <v>0</v>
@@ -14006,30 +13998,34 @@
         <v>5600</v>
       </c>
       <c r="F31" s="38" t="n">
-        <v>66</v>
+        <v>66.5</v>
       </c>
       <c r="G31" s="54" t="n">
         <v>125</v>
       </c>
-      <c r="H31" s="38" t="n"/>
-      <c r="I31" s="38" t="n"/>
+      <c r="H31" s="38" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I31" s="38" t="n">
+        <v>6.5</v>
+      </c>
       <c r="J31" s="39" t="n">
         <v>0.4444</v>
       </c>
       <c r="K31" s="39" t="n">
-        <v>9.27</v>
+        <v>10.72</v>
       </c>
       <c r="L31" s="39" t="n">
         <v>15.1</v>
       </c>
       <c r="M31" s="40" t="n">
-        <v>11.6</v>
+        <v>12.47</v>
       </c>
       <c r="N31" s="40" t="n">
-        <v>2.07</v>
+        <v>2.23</v>
       </c>
       <c r="O31" s="41" t="n">
-        <v>0.0344</v>
+        <v>0.0315</v>
       </c>
     </row>
     <row r="32">
@@ -14055,30 +14051,34 @@
         <v>6200</v>
       </c>
       <c r="F32" s="38" t="n">
-        <v>61.5</v>
+        <v>63.5</v>
       </c>
       <c r="G32" s="54" t="n">
-        <v>-118</v>
-      </c>
-      <c r="H32" s="46" t="n"/>
-      <c r="I32" s="46" t="n"/>
+        <v>-120</v>
+      </c>
+      <c r="H32" s="38" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I32" s="38" t="n">
+        <v>14.5</v>
+      </c>
       <c r="J32" s="45" t="n">
-        <v>0.5413</v>
+        <v>0.5455</v>
       </c>
       <c r="K32" s="39" t="n">
-        <v>9.4</v>
+        <v>12.32</v>
       </c>
       <c r="L32" s="45" t="n">
         <v>14.9</v>
       </c>
       <c r="M32" s="40" t="n">
-        <v>11.6</v>
+        <v>13.35</v>
       </c>
       <c r="N32" s="40" t="n">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="O32" s="41" t="n">
-        <v>0.0302</v>
+        <v>0.0349</v>
       </c>
     </row>
     <row r="33">
@@ -14104,34 +14104,34 @@
         <v>6100</v>
       </c>
       <c r="F33" s="38" t="n">
-        <v>49.5</v>
+        <v>47.5</v>
       </c>
       <c r="G33" s="54" t="n">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="H33" s="38" t="n">
         <v>1.5</v>
       </c>
       <c r="I33" s="38" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="J33" s="39" t="n">
-        <v>0.4167</v>
+        <v>0.4082</v>
       </c>
       <c r="K33" s="39" t="n">
-        <v>8.75</v>
+        <v>8.4</v>
       </c>
       <c r="L33" s="39" t="n">
         <v>14.9</v>
       </c>
       <c r="M33" s="40" t="n">
-        <v>11.21</v>
+        <v>11</v>
       </c>
       <c r="N33" s="40" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="O33" s="41" t="n">
-        <v>0.0272</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="34">
@@ -14246,26 +14246,28 @@
       <c r="E36" s="37" t="n">
         <v>4000</v>
       </c>
-      <c r="F36" s="38" t="n"/>
+      <c r="F36" s="38" t="n">
+        <v>20</v>
+      </c>
       <c r="G36" s="54" t="n">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="H36" s="38" t="n"/>
       <c r="I36" s="46" t="n"/>
       <c r="J36" s="39" t="n">
-        <v>0.2083</v>
+        <v>0.2128</v>
       </c>
       <c r="K36" s="39" t="n">
-        <v>1.25</v>
+        <v>3.28</v>
       </c>
       <c r="L36" s="39" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M36" s="40" t="n">
-        <v>1.25</v>
+        <v>2.97</v>
       </c>
       <c r="N36" s="40" t="n">
-        <v>0.31</v>
+        <v>0.74</v>
       </c>
       <c r="O36" s="41" t="n">
         <v>0</v>
@@ -14294,27 +14296,27 @@
         <v>5200</v>
       </c>
       <c r="F37" s="38" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="G37" s="54" t="n">
-        <v>390</v>
+        <v>425</v>
       </c>
       <c r="H37" s="46" t="n"/>
       <c r="I37" s="46" t="n"/>
       <c r="J37" s="45" t="n">
-        <v>0.2041</v>
+        <v>0.1905</v>
       </c>
       <c r="K37" s="39" t="n">
-        <v>2.27</v>
+        <v>2.14</v>
       </c>
       <c r="L37" s="45" t="n">
         <v>3.2</v>
       </c>
       <c r="M37" s="40" t="n">
-        <v>2.64</v>
+        <v>2.57</v>
       </c>
       <c r="N37" s="40" t="n">
-        <v>0.51</v>
+        <v>0.49</v>
       </c>
       <c r="O37" s="41" t="n">
         <v>0</v>
@@ -14346,28 +14348,28 @@
         <v>8.5</v>
       </c>
       <c r="G38" s="54" t="n">
-        <v>370</v>
+        <v>400</v>
       </c>
       <c r="H38" s="38" t="n">
         <v>1.5</v>
       </c>
       <c r="I38" s="38" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="J38" s="45" t="n">
-        <v>0.2128</v>
+        <v>0.2</v>
       </c>
       <c r="K38" s="39" t="n">
-        <v>3.58</v>
+        <v>3.45</v>
       </c>
       <c r="L38" s="45" t="n">
         <v>3.7</v>
       </c>
       <c r="M38" s="40" t="n">
-        <v>3.63</v>
+        <v>3.55</v>
       </c>
       <c r="N38" s="40" t="n">
-        <v>0.91</v>
+        <v>0.89</v>
       </c>
       <c r="O38" s="41" t="n">
         <v>0</v>
@@ -14442,30 +14444,34 @@
         <v>5700</v>
       </c>
       <c r="F40" s="38" t="n">
-        <v>44.5</v>
+        <v>30.5</v>
       </c>
       <c r="G40" s="54" t="n">
-        <v>180</v>
-      </c>
-      <c r="H40" s="38" t="n"/>
-      <c r="I40" s="38" t="n"/>
+        <v>230</v>
+      </c>
+      <c r="H40" s="38" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I40" s="38" t="n">
+        <v>10.5</v>
+      </c>
       <c r="J40" s="45" t="n">
-        <v>0.3571</v>
+        <v>0.303</v>
       </c>
       <c r="K40" s="39" t="n">
-        <v>6.59</v>
+        <v>7.17</v>
       </c>
       <c r="L40" s="45" t="n">
-        <v>7.8</v>
+        <v>11.9</v>
       </c>
       <c r="M40" s="40" t="n">
-        <v>7.08</v>
+        <v>9.06</v>
       </c>
       <c r="N40" s="40" t="n">
-        <v>1.24</v>
+        <v>1.59</v>
       </c>
       <c r="O40" s="41" t="n">
-        <v>0.0046</v>
+        <v>0.0094</v>
       </c>
     </row>
     <row r="41">
@@ -14491,34 +14497,34 @@
         <v>5000</v>
       </c>
       <c r="F41" s="38" t="n">
-        <v>21.5</v>
+        <v>28.5</v>
       </c>
       <c r="G41" s="54" t="n">
-        <v>295</v>
+        <v>310</v>
       </c>
       <c r="H41" s="38" t="n">
         <v>1.5</v>
       </c>
       <c r="I41" s="38" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="J41" s="39" t="n">
-        <v>0.2532</v>
+        <v>0.2439</v>
       </c>
       <c r="K41" s="39" t="n">
-        <v>5.17</v>
+        <v>5.91</v>
       </c>
       <c r="L41" s="39" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="M41" s="40" t="n">
-        <v>5.66</v>
+        <v>6.07</v>
       </c>
       <c r="N41" s="40" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="O41" s="41" t="n">
-        <v>0.0016</v>
+        <v>0.0017</v>
       </c>
     </row>
     <row r="42">
@@ -14544,30 +14550,30 @@
         <v>5100</v>
       </c>
       <c r="F42" s="38" t="n">
-        <v>22</v>
+        <v>23.5</v>
       </c>
       <c r="G42" s="54" t="n">
-        <v>450</v>
+        <v>380</v>
       </c>
       <c r="H42" s="46" t="n"/>
       <c r="I42" s="46" t="n"/>
       <c r="J42" s="39" t="n">
-        <v>0.1818</v>
+        <v>0.2083</v>
       </c>
       <c r="K42" s="39" t="n">
-        <v>3.29</v>
+        <v>3.6</v>
       </c>
       <c r="L42" s="39" t="n">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
       <c r="M42" s="40" t="n">
-        <v>4.41</v>
+        <v>4.76</v>
       </c>
       <c r="N42" s="40" t="n">
-        <v>0.87</v>
+        <v>0.93</v>
       </c>
       <c r="O42" s="41" t="n">
-        <v>0.0001</v>
+        <v>0.0003</v>
       </c>
     </row>
     <row r="43">
@@ -14640,28 +14646,28 @@
       </c>
       <c r="F44" s="46" t="n"/>
       <c r="G44" s="54" t="n">
-        <v>700</v>
+        <v>750</v>
       </c>
       <c r="H44" s="38" t="n">
         <v>1.5</v>
       </c>
       <c r="I44" s="38" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="J44" s="45" t="n">
-        <v>0.125</v>
+        <v>0.1176</v>
       </c>
       <c r="K44" s="39" t="n">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="L44" s="45" t="n">
         <v>4.9</v>
       </c>
       <c r="M44" s="40" t="n">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
       <c r="N44" s="40" t="n">
-        <v>0.71</v>
+        <v>0.7</v>
       </c>
       <c r="O44" s="41" t="n">
         <v>0</v>
@@ -14693,7 +14699,7 @@
         <v>11.5</v>
       </c>
       <c r="G45" s="54" t="n">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="H45" s="38" t="n">
         <v>2.5</v>
@@ -14702,22 +14708,22 @@
         <v>13.5</v>
       </c>
       <c r="J45" s="39" t="n">
-        <v>0.2</v>
+        <v>0.1961</v>
       </c>
       <c r="K45" s="39" t="n">
-        <v>4.95</v>
+        <v>4.93</v>
       </c>
       <c r="L45" s="39" t="n">
         <v>6.3</v>
       </c>
       <c r="M45" s="40" t="n">
-        <v>5.49</v>
+        <v>5.48</v>
       </c>
       <c r="N45" s="40" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="O45" s="41" t="n">
-        <v>0.0013</v>
+        <v>0.0009</v>
       </c>
     </row>
     <row r="46">
@@ -14744,21 +14750,21 @@
       </c>
       <c r="F46" s="46" t="n"/>
       <c r="G46" s="54" t="n">
-        <v>550</v>
+        <v>700</v>
       </c>
       <c r="H46" s="46" t="n"/>
       <c r="I46" s="46" t="n"/>
       <c r="J46" s="45" t="n">
-        <v>0.1538</v>
+        <v>0.125</v>
       </c>
       <c r="K46" s="39" t="n">
-        <v>0.92</v>
+        <v>0.75</v>
       </c>
       <c r="L46" s="45" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="M46" s="40" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="N46" s="40" t="n">
         <v>0.58</v>
@@ -14791,7 +14797,7 @@
       </c>
       <c r="F47" s="38" t="n"/>
       <c r="G47" s="54" t="n">
-        <v>525</v>
+        <v>575</v>
       </c>
       <c r="H47" s="38" t="n">
         <v>1.5</v>
@@ -14800,19 +14806,19 @@
         <v>11.5</v>
       </c>
       <c r="J47" s="39" t="n">
-        <v>0.16</v>
+        <v>0.1481</v>
       </c>
       <c r="K47" s="39" t="n">
-        <v>2.86</v>
+        <v>2.79</v>
       </c>
       <c r="L47" s="39" t="n">
         <v>3.2</v>
       </c>
       <c r="M47" s="40" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="N47" s="40" t="n">
-        <v>0.7</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="O47" s="41" t="n">
         <v>0</v>
@@ -14844,7 +14850,7 @@
         <v>23.5</v>
       </c>
       <c r="G48" s="54" t="n">
-        <v>400</v>
+        <v>425</v>
       </c>
       <c r="H48" s="38" t="n">
         <v>1.5</v>
@@ -14853,22 +14859,22 @@
         <v>8.5</v>
       </c>
       <c r="J48" s="39" t="n">
-        <v>0.2</v>
+        <v>0.1905</v>
       </c>
       <c r="K48" s="39" t="n">
-        <v>5.15</v>
+        <v>5.09</v>
       </c>
       <c r="L48" s="39" t="n">
         <v>6</v>
       </c>
       <c r="M48" s="40" t="n">
-        <v>5.49</v>
+        <v>5.46</v>
       </c>
       <c r="N48" s="40" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="O48" s="41" t="n">
-        <v>0.0015</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="49">
@@ -14894,30 +14900,30 @@
         <v>4800</v>
       </c>
       <c r="F49" s="38" t="n">
-        <v>30.5</v>
+        <v>40.5</v>
       </c>
       <c r="G49" s="54" t="n">
-        <v>330</v>
+        <v>260</v>
       </c>
       <c r="H49" s="46" t="n"/>
       <c r="I49" s="46" t="n"/>
       <c r="J49" s="45" t="n">
-        <v>0.2326</v>
+        <v>0.2778</v>
       </c>
       <c r="K49" s="39" t="n">
-        <v>4.45</v>
+        <v>5.72</v>
       </c>
       <c r="L49" s="45" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="M49" s="40" t="n">
-        <v>4.45</v>
+        <v>6.99</v>
       </c>
       <c r="N49" s="40" t="n">
-        <v>0.93</v>
+        <v>1.46</v>
       </c>
       <c r="O49" s="41" t="n">
-        <v>0.0002</v>
+        <v>0.0038</v>
       </c>
     </row>
     <row r="50">
@@ -15036,24 +15042,24 @@
       </c>
       <c r="F52" s="46" t="n"/>
       <c r="G52" s="54" t="n">
-        <v>250</v>
+        <v>900</v>
       </c>
       <c r="H52" s="46" t="n"/>
       <c r="I52" s="46" t="n"/>
       <c r="J52" s="39" t="n">
-        <v>0.2857</v>
+        <v>0.1</v>
       </c>
       <c r="K52" s="39" t="n">
-        <v>1.71</v>
+        <v>0.6</v>
       </c>
       <c r="L52" s="39" t="n">
         <v>0</v>
       </c>
       <c r="M52" s="40" t="n">
-        <v>1.71</v>
+        <v>0.6</v>
       </c>
       <c r="N52" s="40" t="n">
-        <v>0.31</v>
+        <v>0.11</v>
       </c>
       <c r="O52" s="41" t="n">
         <v>0</v>
@@ -15082,34 +15088,34 @@
         <v>4800</v>
       </c>
       <c r="F53" s="40" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="G53" s="55" t="n">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="H53" s="40" t="n">
         <v>2.5</v>
       </c>
       <c r="I53" s="40" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="J53" s="40" t="n">
-        <v>0.125</v>
+        <v>0.1429</v>
       </c>
       <c r="K53" s="40" t="n">
-        <v>4.25</v>
+        <v>4.16</v>
       </c>
       <c r="L53" s="40" t="n">
         <v>6.4</v>
       </c>
       <c r="M53" s="40" t="n">
-        <v>5.11</v>
+        <v>5.05</v>
       </c>
       <c r="N53" s="40" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="O53" s="41" t="n">
-        <v>0.0008</v>
+        <v>0.0005</v>
       </c>
     </row>
     <row r="54">
@@ -15135,30 +15141,30 @@
         <v>5400</v>
       </c>
       <c r="F54" s="40" t="n">
-        <v>29.5</v>
+        <v>28.5</v>
       </c>
       <c r="G54" s="55" t="n">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="H54" s="40" t="n"/>
       <c r="I54" s="40" t="n"/>
       <c r="J54" s="40" t="n">
-        <v>0.1905</v>
+        <v>0.1923</v>
       </c>
       <c r="K54" s="40" t="n">
-        <v>4.09</v>
+        <v>4</v>
       </c>
       <c r="L54" s="40" t="n">
         <v>7.1</v>
       </c>
       <c r="M54" s="40" t="n">
-        <v>5.3</v>
+        <v>5.24</v>
       </c>
       <c r="N54" s="40" t="n">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="O54" s="41" t="n">
-        <v>0.0009</v>
+        <v>0.0005999999999999999</v>
       </c>
     </row>
     <row r="55">
@@ -15198,13 +15204,13 @@
         <v>1.61</v>
       </c>
       <c r="L55" s="40" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="M55" s="40" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="N55" s="40" t="n">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="O55" s="41" t="n">
         <v>0</v>
@@ -15278,28 +15284,26 @@
         <v>4400</v>
       </c>
       <c r="F57" s="53" t="n"/>
-      <c r="G57" s="55" t="n">
-        <v>1050</v>
-      </c>
+      <c r="G57" s="55" t="n"/>
       <c r="H57" s="53" t="n"/>
       <c r="I57" s="53" t="n"/>
       <c r="J57" s="40" t="n">
         <v>0.08699999999999999</v>
       </c>
       <c r="K57" s="40" t="n">
-        <v>0.52</v>
+        <v>0</v>
       </c>
       <c r="L57" s="40" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M57" s="40" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="N57" s="40" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="O57" s="41" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="58">
@@ -15370,7 +15374,7 @@
         <v>4700</v>
       </c>
       <c r="F59" s="40" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="G59" s="55" t="n">
         <v>1000</v>
@@ -15381,16 +15385,16 @@
         <v>0.09089999999999999</v>
       </c>
       <c r="K59" s="40" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="L59" s="40" t="n">
         <v>4.7</v>
       </c>
       <c r="M59" s="40" t="n">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="N59" s="40" t="n">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
       <c r="O59" s="41" t="n">
         <v>0</v>
@@ -15509,26 +15513,28 @@
       <c r="E62" s="52" t="n">
         <v>4700</v>
       </c>
-      <c r="F62" s="53" t="n"/>
+      <c r="F62" s="40" t="n">
+        <v>13.5</v>
+      </c>
       <c r="G62" s="55" t="n">
-        <v>1700</v>
+        <v>1500</v>
       </c>
       <c r="H62" s="53" t="n"/>
       <c r="I62" s="53" t="n"/>
       <c r="J62" s="40" t="n">
-        <v>0.0556</v>
+        <v>0.0625</v>
       </c>
       <c r="K62" s="40" t="n">
-        <v>0.33</v>
+        <v>1.73</v>
       </c>
       <c r="L62" s="40" t="n">
         <v>3</v>
       </c>
       <c r="M62" s="40" t="n">
-        <v>1.4</v>
+        <v>2.24</v>
       </c>
       <c r="N62" s="40" t="n">
-        <v>0.3</v>
+        <v>0.48</v>
       </c>
       <c r="O62" s="41" t="n">
         <v>0</v>
@@ -15603,7 +15609,9 @@
       <c r="E64" s="52" t="n">
         <v>4900</v>
       </c>
-      <c r="F64" s="40" t="n"/>
+      <c r="F64" s="40" t="n">
+        <v>12.5</v>
+      </c>
       <c r="G64" s="55" t="n">
         <v>900</v>
       </c>
@@ -15613,16 +15621,16 @@
         <v>0.1</v>
       </c>
       <c r="K64" s="40" t="n">
-        <v>0.6</v>
+        <v>1.85</v>
       </c>
       <c r="L64" s="40" t="n">
         <v>3.5</v>
       </c>
       <c r="M64" s="40" t="n">
-        <v>1.76</v>
+        <v>2.51</v>
       </c>
       <c r="N64" s="40" t="n">
-        <v>0.36</v>
+        <v>0.51</v>
       </c>
       <c r="O64" s="41" t="n">
         <v>0</v>
@@ -15652,24 +15660,24 @@
       </c>
       <c r="F65" s="53" t="n"/>
       <c r="G65" s="55" t="n">
-        <v>850</v>
+        <v>1100</v>
       </c>
       <c r="H65" s="53" t="n"/>
       <c r="I65" s="53" t="n"/>
       <c r="J65" s="40" t="n">
-        <v>0.1053</v>
+        <v>0.0833</v>
       </c>
       <c r="K65" s="40" t="n">
-        <v>0.63</v>
+        <v>0.5</v>
       </c>
       <c r="L65" s="40" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="M65" s="40" t="n">
-        <v>1.34</v>
+        <v>1.1</v>
       </c>
       <c r="N65" s="40" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="O65" s="41" t="n">
         <v>0</v>
@@ -15699,24 +15707,24 @@
       </c>
       <c r="F66" s="53" t="n"/>
       <c r="G66" s="55" t="n">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="H66" s="53" t="n"/>
       <c r="I66" s="53" t="n"/>
       <c r="J66" s="40" t="n">
-        <v>0.0556</v>
+        <v>0.0588</v>
       </c>
       <c r="K66" s="40" t="n">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="L66" s="40" t="n">
         <v>0</v>
       </c>
       <c r="M66" s="40" t="n">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="N66" s="40" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="O66" s="41" t="n">
         <v>0</v>
@@ -15745,26 +15753,28 @@
         <v>4400</v>
       </c>
       <c r="F67" s="40" t="n"/>
-      <c r="G67" s="55" t="n"/>
+      <c r="G67" s="55" t="n">
+        <v>600</v>
+      </c>
       <c r="H67" s="53" t="n"/>
       <c r="I67" s="53" t="n"/>
       <c r="J67" s="40" t="n">
-        <v>0.1739</v>
+        <v>0.1429</v>
       </c>
       <c r="K67" s="40" t="n">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="L67" s="40" t="n">
         <v>0</v>
       </c>
       <c r="M67" s="40" t="n">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="N67" s="40" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="O67" s="41" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -15791,21 +15801,21 @@
       </c>
       <c r="F68" s="53" t="n"/>
       <c r="G68" s="55" t="n">
-        <v>2700</v>
+        <v>3000</v>
       </c>
       <c r="H68" s="53" t="n"/>
       <c r="I68" s="53" t="n"/>
       <c r="J68" s="40" t="n">
-        <v>0.0357</v>
+        <v>0.0323</v>
       </c>
       <c r="K68" s="40" t="n">
-        <v>0.21</v>
+        <v>0.19</v>
       </c>
       <c r="L68" s="40" t="n">
         <v>0</v>
       </c>
       <c r="M68" s="40" t="n">
-        <v>0.21</v>
+        <v>0.19</v>
       </c>
       <c r="N68" s="40" t="n">
         <v>0.05</v>
@@ -15838,24 +15848,24 @@
       </c>
       <c r="F69" s="53" t="n"/>
       <c r="G69" s="55" t="n">
-        <v>700</v>
+        <v>650</v>
       </c>
       <c r="H69" s="53" t="n"/>
       <c r="I69" s="53" t="n"/>
       <c r="J69" s="40" t="n">
-        <v>0.125</v>
+        <v>0.1333</v>
       </c>
       <c r="K69" s="40" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="L69" s="40" t="n">
         <v>0</v>
       </c>
       <c r="M69" s="40" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="N69" s="40" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="O69" s="41" t="n">
         <v>0</v>
@@ -15931,26 +15941,28 @@
         <v>4000</v>
       </c>
       <c r="F71" s="40" t="n"/>
-      <c r="G71" s="55" t="n"/>
+      <c r="G71" s="55" t="n">
+        <v>4000</v>
+      </c>
       <c r="H71" s="53" t="n"/>
       <c r="I71" s="53" t="n"/>
       <c r="J71" s="40" t="n">
-        <v>0.1053</v>
+        <v>0.0244</v>
       </c>
       <c r="K71" s="40" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="L71" s="40" t="n">
         <v>0</v>
       </c>
       <c r="M71" s="40" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="N71" s="40" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="O71" s="41" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -15977,24 +15989,24 @@
       </c>
       <c r="F72" s="53" t="n"/>
       <c r="G72" s="55" t="n">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="H72" s="53" t="n"/>
       <c r="I72" s="53" t="n"/>
       <c r="J72" s="40" t="n">
-        <v>0.0625</v>
+        <v>0.0588</v>
       </c>
       <c r="K72" s="40" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="L72" s="40" t="n">
         <v>0</v>
       </c>
       <c r="M72" s="40" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="N72" s="40" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="O72" s="41" t="n">
         <v>0</v>
@@ -16023,27 +16035,27 @@
         <v>5300</v>
       </c>
       <c r="F73" s="40" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="G73" s="55" t="n">
-        <v>550</v>
+        <v>600</v>
       </c>
       <c r="H73" s="53" t="n"/>
       <c r="I73" s="53" t="n"/>
       <c r="J73" s="40" t="n">
-        <v>0.1538</v>
+        <v>0.1429</v>
       </c>
       <c r="K73" s="40" t="n">
-        <v>2.47</v>
+        <v>2.36</v>
       </c>
       <c r="L73" s="40" t="n">
         <v>5.3</v>
       </c>
       <c r="M73" s="40" t="n">
-        <v>3.6</v>
+        <v>3.53</v>
       </c>
       <c r="N73" s="40" t="n">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="O73" s="41" t="n">
         <v>0</v>
@@ -16254,24 +16266,24 @@
       </c>
       <c r="F78" s="53" t="n"/>
       <c r="G78" s="55" t="n">
-        <v>3500</v>
+        <v>5000</v>
       </c>
       <c r="H78" s="53" t="n"/>
       <c r="I78" s="53" t="n"/>
       <c r="J78" s="40" t="n">
-        <v>0.0278</v>
+        <v>0.0196</v>
       </c>
       <c r="K78" s="40" t="n">
-        <v>0.17</v>
+        <v>0.12</v>
       </c>
       <c r="L78" s="40" t="n">
         <v>0</v>
       </c>
       <c r="M78" s="40" t="n">
-        <v>0.17</v>
+        <v>0.12</v>
       </c>
       <c r="N78" s="40" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="O78" s="41" t="n">
         <v>0</v>
@@ -16347,24 +16359,24 @@
       </c>
       <c r="F80" s="53" t="n"/>
       <c r="G80" s="55" t="n">
-        <v>2400</v>
+        <v>2500</v>
       </c>
       <c r="H80" s="53" t="n"/>
       <c r="I80" s="53" t="n"/>
       <c r="J80" s="40" t="n">
-        <v>0.04</v>
+        <v>0.0385</v>
       </c>
       <c r="K80" s="40" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="L80" s="40" t="n">
         <v>0</v>
       </c>
       <c r="M80" s="40" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="N80" s="40" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="O80" s="41" t="n">
         <v>0</v>
@@ -16394,24 +16406,24 @@
       </c>
       <c r="F81" s="53" t="n"/>
       <c r="G81" s="55" t="n">
-        <v>3300</v>
+        <v>6000</v>
       </c>
       <c r="H81" s="53" t="n"/>
       <c r="I81" s="53" t="n"/>
       <c r="J81" s="40" t="n">
-        <v>0.0294</v>
+        <v>0.0164</v>
       </c>
       <c r="K81" s="40" t="n">
-        <v>0.18</v>
+        <v>0.1</v>
       </c>
       <c r="L81" s="40" t="n">
         <v>0</v>
       </c>
       <c r="M81" s="40" t="n">
-        <v>0.18</v>
+        <v>0.1</v>
       </c>
       <c r="N81" s="40" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="O81" s="41" t="n">
         <v>0</v>
@@ -16487,24 +16499,24 @@
       </c>
       <c r="F83" s="53" t="n"/>
       <c r="G83" s="55" t="n">
-        <v>3500</v>
+        <v>4500</v>
       </c>
       <c r="H83" s="53" t="n"/>
       <c r="I83" s="53" t="n"/>
       <c r="J83" s="40" t="n">
-        <v>0.0278</v>
+        <v>0.0217</v>
       </c>
       <c r="K83" s="40" t="n">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
       <c r="L83" s="40" t="n">
         <v>0</v>
       </c>
       <c r="M83" s="40" t="n">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
       <c r="N83" s="40" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="O83" s="41" t="n">
         <v>0</v>
@@ -16534,21 +16546,21 @@
       </c>
       <c r="F84" s="53" t="n"/>
       <c r="G84" s="55" t="n">
-        <v>5500</v>
+        <v>6500</v>
       </c>
       <c r="H84" s="53" t="n"/>
       <c r="I84" s="53" t="n"/>
       <c r="J84" s="40" t="n">
-        <v>0.0179</v>
+        <v>0.0152</v>
       </c>
       <c r="K84" s="40" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="L84" s="40" t="n">
         <v>0</v>
       </c>
       <c r="M84" s="40" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="N84" s="40" t="n">
         <v>0.02</v>
@@ -16581,21 +16593,21 @@
       </c>
       <c r="F85" s="53" t="n"/>
       <c r="G85" s="55" t="n">
-        <v>3300</v>
+        <v>3500</v>
       </c>
       <c r="H85" s="53" t="n"/>
       <c r="I85" s="53" t="n"/>
       <c r="J85" s="40" t="n">
-        <v>0.0294</v>
+        <v>0.0278</v>
       </c>
       <c r="K85" s="40" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="L85" s="40" t="n">
         <v>0</v>
       </c>
       <c r="M85" s="40" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="N85" s="40" t="n">
         <v>0.04</v>
@@ -16628,24 +16640,24 @@
       </c>
       <c r="F86" s="53" t="n"/>
       <c r="G86" s="55" t="n">
-        <v>270</v>
+        <v>750</v>
       </c>
       <c r="H86" s="53" t="n"/>
       <c r="I86" s="53" t="n"/>
       <c r="J86" s="40" t="n">
-        <v>0.2703</v>
+        <v>0.1176</v>
       </c>
       <c r="K86" s="40" t="n">
-        <v>1.62</v>
+        <v>0.71</v>
       </c>
       <c r="L86" s="40" t="n">
         <v>5.8</v>
       </c>
       <c r="M86" s="40" t="n">
-        <v>3.29</v>
+        <v>2.74</v>
       </c>
       <c r="N86" s="40" t="n">
-        <v>0.63</v>
+        <v>0.53</v>
       </c>
       <c r="O86" s="41" t="n">
         <v>0</v>
@@ -16722,21 +16734,21 @@
       </c>
       <c r="F88" s="53" t="n"/>
       <c r="G88" s="55" t="n">
-        <v>3300</v>
+        <v>3500</v>
       </c>
       <c r="H88" s="53" t="n"/>
       <c r="I88" s="53" t="n"/>
       <c r="J88" s="40" t="n">
-        <v>0.0294</v>
+        <v>0.0278</v>
       </c>
       <c r="K88" s="40" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="L88" s="40" t="n">
         <v>0</v>
       </c>
       <c r="M88" s="40" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="N88" s="40" t="n">
         <v>0.04</v>
@@ -16769,24 +16781,24 @@
       </c>
       <c r="F89" s="53" t="n"/>
       <c r="G89" s="55" t="n">
-        <v>2200</v>
+        <v>2400</v>
       </c>
       <c r="H89" s="53" t="n"/>
       <c r="I89" s="53" t="n"/>
       <c r="J89" s="40" t="n">
-        <v>0.0435</v>
+        <v>0.04</v>
       </c>
       <c r="K89" s="40" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="L89" s="40" t="n">
         <v>0</v>
       </c>
       <c r="M89" s="40" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="N89" s="40" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="O89" s="41" t="n">
         <v>0</v>
@@ -16861,24 +16873,24 @@
       </c>
       <c r="F91" s="53" t="n"/>
       <c r="G91" s="55" t="n">
-        <v>3300</v>
+        <v>2200</v>
       </c>
       <c r="H91" s="53" t="n"/>
       <c r="I91" s="53" t="n"/>
       <c r="J91" s="40" t="n">
-        <v>0.0294</v>
+        <v>0.0435</v>
       </c>
       <c r="K91" s="40" t="n">
-        <v>0.18</v>
+        <v>0.26</v>
       </c>
       <c r="L91" s="40" t="n">
         <v>0</v>
       </c>
       <c r="M91" s="40" t="n">
-        <v>0.18</v>
+        <v>0.26</v>
       </c>
       <c r="N91" s="40" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="O91" s="41" t="n">
         <v>0</v>
@@ -16953,24 +16965,24 @@
       </c>
       <c r="F93" s="53" t="n"/>
       <c r="G93" s="55" t="n">
-        <v>4500</v>
+        <v>6000</v>
       </c>
       <c r="H93" s="53" t="n"/>
       <c r="I93" s="53" t="n"/>
       <c r="J93" s="40" t="n">
-        <v>0.0217</v>
+        <v>0.0164</v>
       </c>
       <c r="K93" s="40" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="L93" s="40" t="n">
         <v>0</v>
       </c>
       <c r="M93" s="40" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="N93" s="40" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="O93" s="41" t="n">
         <v>0</v>
@@ -17000,24 +17012,24 @@
       </c>
       <c r="F94" s="53" t="n"/>
       <c r="G94" s="55" t="n">
-        <v>2400</v>
+        <v>3000</v>
       </c>
       <c r="H94" s="53" t="n"/>
       <c r="I94" s="53" t="n"/>
       <c r="J94" s="40" t="n">
-        <v>0.04</v>
+        <v>0.0323</v>
       </c>
       <c r="K94" s="40" t="n">
-        <v>0.24</v>
+        <v>0.19</v>
       </c>
       <c r="L94" s="40" t="n">
         <v>0</v>
       </c>
       <c r="M94" s="40" t="n">
-        <v>0.24</v>
+        <v>0.19</v>
       </c>
       <c r="N94" s="40" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="O94" s="41" t="n">
         <v>0</v>
@@ -17094,24 +17106,24 @@
       </c>
       <c r="F96" s="53" t="n"/>
       <c r="G96" s="55" t="n">
-        <v>3500</v>
+        <v>3000</v>
       </c>
       <c r="H96" s="53" t="n"/>
       <c r="I96" s="53" t="n"/>
       <c r="J96" s="40" t="n">
-        <v>0.0278</v>
+        <v>0.0323</v>
       </c>
       <c r="K96" s="40" t="n">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="L96" s="40" t="n">
         <v>0</v>
       </c>
       <c r="M96" s="40" t="n">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="N96" s="40" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="O96" s="41" t="n">
         <v>0</v>
@@ -17141,21 +17153,21 @@
       </c>
       <c r="F97" s="53" t="n"/>
       <c r="G97" s="55" t="n">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="H97" s="53" t="n"/>
       <c r="I97" s="53" t="n"/>
       <c r="J97" s="40" t="n">
-        <v>0.0556</v>
+        <v>0.0588</v>
       </c>
       <c r="K97" s="40" t="n">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="L97" s="40" t="n">
         <v>0</v>
       </c>
       <c r="M97" s="40" t="n">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="N97" s="40" t="n">
         <v>0.07000000000000001</v>
@@ -17278,28 +17290,26 @@
         <v>4000</v>
       </c>
       <c r="F100" s="53" t="n"/>
-      <c r="G100" s="55" t="n">
-        <v>2800</v>
-      </c>
+      <c r="G100" s="55" t="n"/>
       <c r="H100" s="53" t="n"/>
       <c r="I100" s="53" t="n"/>
       <c r="J100" s="40" t="n">
         <v>0.0345</v>
       </c>
       <c r="K100" s="40" t="n">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="L100" s="40" t="n">
         <v>0</v>
       </c>
       <c r="M100" s="40" t="n">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="N100" s="40" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="O100" s="41" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="101">
@@ -18153,24 +18163,24 @@
       </c>
       <c r="F119" s="53" t="n"/>
       <c r="G119" s="55" t="n">
-        <v>3500</v>
+        <v>3000</v>
       </c>
       <c r="H119" s="53" t="n"/>
       <c r="I119" s="53" t="n"/>
       <c r="J119" s="40" t="n">
-        <v>0.0278</v>
+        <v>0.0323</v>
       </c>
       <c r="K119" s="40" t="n">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="L119" s="40" t="n">
         <v>0</v>
       </c>
       <c r="M119" s="40" t="n">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="N119" s="40" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="O119" s="41" t="n">
         <v>0</v>
@@ -18294,7 +18304,7 @@
         <v>23.5</v>
       </c>
       <c r="G122" s="55" t="n">
-        <v>400</v>
+        <v>425</v>
       </c>
       <c r="H122" s="40" t="n">
         <v>1.5</v>
@@ -18303,22 +18313,22 @@
         <v>8.5</v>
       </c>
       <c r="J122" s="40" t="n">
-        <v>0.2</v>
+        <v>0.1905</v>
       </c>
       <c r="K122" s="40" t="n">
-        <v>5.15</v>
+        <v>5.09</v>
       </c>
       <c r="L122" s="40" t="n">
         <v>6</v>
       </c>
       <c r="M122" s="40" t="n">
-        <v>5.49</v>
+        <v>5.46</v>
       </c>
       <c r="N122" s="40" t="n">
         <v>1.19</v>
       </c>
       <c r="O122" s="41" t="n">
-        <v>0.0015</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="123">
@@ -18345,24 +18355,24 @@
       </c>
       <c r="F123" s="53" t="n"/>
       <c r="G123" s="55" t="n">
-        <v>2200</v>
+        <v>2400</v>
       </c>
       <c r="H123" s="53" t="n"/>
       <c r="I123" s="53" t="n"/>
       <c r="J123" s="40" t="n">
-        <v>0.0435</v>
+        <v>0.04</v>
       </c>
       <c r="K123" s="40" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="L123" s="40" t="n">
         <v>0</v>
       </c>
       <c r="M123" s="40" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="N123" s="40" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="O123" s="41" t="n">
         <v>0</v>
@@ -18437,28 +18447,26 @@
         <v>4200</v>
       </c>
       <c r="F125" s="53" t="n"/>
-      <c r="G125" s="55" t="n">
-        <v>2800</v>
-      </c>
+      <c r="G125" s="55" t="n"/>
       <c r="H125" s="53" t="n"/>
       <c r="I125" s="53" t="n"/>
       <c r="J125" s="40" t="n">
         <v>0.0345</v>
       </c>
       <c r="K125" s="40" t="n">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="L125" s="40" t="n">
         <v>0</v>
       </c>
       <c r="M125" s="40" t="n">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="N125" s="40" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="O125" s="41" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="126">
@@ -18807,24 +18815,24 @@
       </c>
       <c r="F133" s="53" t="n"/>
       <c r="G133" s="55" t="n">
-        <v>3300</v>
+        <v>6000</v>
       </c>
       <c r="H133" s="53" t="n"/>
       <c r="I133" s="53" t="n"/>
       <c r="J133" s="40" t="n">
-        <v>0.0294</v>
+        <v>0.0164</v>
       </c>
       <c r="K133" s="40" t="n">
-        <v>0.18</v>
+        <v>0.1</v>
       </c>
       <c r="L133" s="40" t="n">
         <v>0</v>
       </c>
       <c r="M133" s="40" t="n">
-        <v>0.18</v>
+        <v>0.1</v>
       </c>
       <c r="N133" s="40" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="O133" s="41" t="n">
         <v>0</v>
@@ -18899,27 +18907,28 @@
         <v>4000</v>
       </c>
       <c r="F135" s="53" t="n"/>
-      <c r="G135" s="53" t="n"/>
+      <c r="G135" s="55" t="n">
+        <v>1600</v>
+      </c>
       <c r="H135" s="53" t="n"/>
       <c r="I135" s="53" t="n"/>
-      <c r="J135" s="53">
-        <f>IF(OR(ISBLANK(G135), NOT(ISNUMBER(G135))), "", IF(G135 &lt; 0, -G135 / (-G135 + 100), 100 / (G135 + 100)))</f>
-        <v/>
+      <c r="J135" s="40" t="n">
+        <v>0.0588</v>
       </c>
       <c r="K135" s="40" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="L135" s="40" t="n">
         <v>0</v>
       </c>
       <c r="M135" s="40" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="N135" s="40" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="O135" s="41" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136">
@@ -19314,24 +19323,24 @@
       </c>
       <c r="F144" s="53" t="n"/>
       <c r="G144" s="55" t="n">
-        <v>2400</v>
+        <v>3000</v>
       </c>
       <c r="H144" s="53" t="n"/>
       <c r="I144" s="53" t="n"/>
       <c r="J144" s="40" t="n">
-        <v>0.04</v>
+        <v>0.0323</v>
       </c>
       <c r="K144" s="40" t="n">
-        <v>0.24</v>
+        <v>0.19</v>
       </c>
       <c r="L144" s="40" t="n">
         <v>0</v>
       </c>
       <c r="M144" s="40" t="n">
-        <v>0.24</v>
+        <v>0.19</v>
       </c>
       <c r="N144" s="40" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="O144" s="41" t="n">
         <v>0</v>
@@ -19683,7 +19692,7 @@
         <v>1.86</v>
       </c>
       <c r="N5" s="41" t="n">
-        <v>0.0873</v>
+        <v>0.0864</v>
       </c>
     </row>
     <row r="6">
@@ -19709,31 +19718,31 @@
         <v>9000</v>
       </c>
       <c r="F6" s="38" t="n">
-        <v>80</v>
+        <v>78.5</v>
       </c>
       <c r="G6" s="54" t="n">
-        <v>-120</v>
+        <v>-125</v>
       </c>
       <c r="H6" s="38" t="n">
         <v>7.5</v>
       </c>
       <c r="I6" s="39" t="n">
-        <v>0.5455</v>
+        <v>0.5556</v>
       </c>
       <c r="J6" s="39" t="n">
-        <v>15.02</v>
+        <v>14.93</v>
       </c>
       <c r="K6" s="39" t="n">
         <v>17.9</v>
       </c>
       <c r="L6" s="40" t="n">
-        <v>16.17</v>
+        <v>16.12</v>
       </c>
       <c r="M6" s="40" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="N6" s="41" t="n">
-        <v>0.1154</v>
+        <v>0.1131</v>
       </c>
     </row>
     <row r="7">
@@ -19760,26 +19769,26 @@
       </c>
       <c r="F7" s="38" t="n"/>
       <c r="G7" s="54" t="n">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="H7" s="38" t="n"/>
       <c r="I7" s="39" t="n">
-        <v>0.3774</v>
+        <v>0.3571</v>
       </c>
       <c r="J7" s="39" t="n">
-        <v>2.26</v>
+        <v>2.14</v>
       </c>
       <c r="K7" s="39" t="n">
-        <v>14.2</v>
+        <v>15.3</v>
       </c>
       <c r="L7" s="40" t="n">
-        <v>7.04</v>
+        <v>7.41</v>
       </c>
       <c r="M7" s="40" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="N7" s="41" t="n">
-        <v>0.0059</v>
+        <v>0.0074</v>
       </c>
     </row>
     <row r="8">
@@ -19806,26 +19815,26 @@
       </c>
       <c r="F8" s="38" t="n"/>
       <c r="G8" s="54" t="n">
-        <v>-110</v>
+        <v>105</v>
       </c>
       <c r="H8" s="38" t="n"/>
       <c r="I8" s="39" t="n">
-        <v>0.5238</v>
+        <v>0.4878</v>
       </c>
       <c r="J8" s="39" t="n">
-        <v>3.14</v>
+        <v>2.93</v>
       </c>
       <c r="K8" s="39" t="n">
-        <v>23.3</v>
+        <v>0</v>
       </c>
       <c r="L8" s="40" t="n">
-        <v>11.21</v>
+        <v>2.93</v>
       </c>
       <c r="M8" s="40" t="n">
-        <v>1.23</v>
+        <v>0.32</v>
       </c>
       <c r="N8" s="41" t="n">
-        <v>0.0322</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -19875,7 +19884,7 @@
         <v>1.86</v>
       </c>
       <c r="N9" s="41" t="n">
-        <v>0.0793</v>
+        <v>0.0785</v>
       </c>
     </row>
     <row r="10">
@@ -19904,28 +19913,28 @@
         <v>73.5</v>
       </c>
       <c r="G10" s="54" t="n">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="H10" s="38" t="n">
         <v>5.5</v>
       </c>
       <c r="I10" s="45" t="n">
-        <v>0.3846</v>
+        <v>0.3922</v>
       </c>
       <c r="J10" s="45" t="n">
-        <v>12.41</v>
+        <v>12.45</v>
       </c>
       <c r="K10" s="45" t="n">
         <v>16.2</v>
       </c>
       <c r="L10" s="40" t="n">
-        <v>13.92</v>
+        <v>13.95</v>
       </c>
       <c r="M10" s="40" t="n">
         <v>2.08</v>
       </c>
       <c r="N10" s="41" t="n">
-        <v>0.1026</v>
+        <v>0.1023</v>
       </c>
     </row>
     <row r="11">
@@ -19995,7 +20004,7 @@
         <v>7900</v>
       </c>
       <c r="F12" s="38" t="n">
-        <v>69</v>
+        <v>68.5</v>
       </c>
       <c r="G12" s="54" t="n">
         <v>250</v>
@@ -20007,19 +20016,19 @@
         <v>0.2857</v>
       </c>
       <c r="J12" s="45" t="n">
-        <v>11.36</v>
+        <v>11.31</v>
       </c>
       <c r="K12" s="45" t="n">
         <v>16.4</v>
       </c>
       <c r="L12" s="40" t="n">
-        <v>13.38</v>
+        <v>13.35</v>
       </c>
       <c r="M12" s="40" t="n">
         <v>1.69</v>
       </c>
       <c r="N12" s="41" t="n">
-        <v>0.0723</v>
+        <v>0.07099999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -20048,28 +20057,28 @@
         <v>66.5</v>
       </c>
       <c r="G13" s="54" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="H13" s="38" t="n">
         <v>5.5</v>
       </c>
       <c r="I13" s="39" t="n">
-        <v>0.3704</v>
+        <v>0.3636</v>
       </c>
       <c r="J13" s="39" t="n">
-        <v>11.62</v>
+        <v>11.58</v>
       </c>
       <c r="K13" s="39" t="n">
         <v>14.2</v>
       </c>
       <c r="L13" s="40" t="n">
-        <v>12.65</v>
+        <v>12.63</v>
       </c>
       <c r="M13" s="40" t="n">
         <v>2.04</v>
       </c>
       <c r="N13" s="41" t="n">
-        <v>0.08160000000000001</v>
+        <v>0.0803</v>
       </c>
     </row>
     <row r="14">
@@ -20098,28 +20107,28 @@
         <v>62.5</v>
       </c>
       <c r="G14" s="54" t="n">
-        <v>155</v>
+        <v>175</v>
       </c>
       <c r="H14" s="38" t="n">
         <v>5.5</v>
       </c>
       <c r="I14" s="45" t="n">
-        <v>0.3922</v>
+        <v>0.3636</v>
       </c>
       <c r="J14" s="45" t="n">
-        <v>11.35</v>
+        <v>11.18</v>
       </c>
       <c r="K14" s="45" t="n">
         <v>13.8</v>
       </c>
       <c r="L14" s="40" t="n">
-        <v>12.33</v>
+        <v>12.23</v>
       </c>
       <c r="M14" s="40" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="N14" s="41" t="n">
-        <v>0.0603</v>
+        <v>0.058</v>
       </c>
     </row>
     <row r="15">
@@ -20145,31 +20154,31 @@
         <v>8400</v>
       </c>
       <c r="F15" s="38" t="n">
-        <v>72</v>
+        <v>73.5</v>
       </c>
       <c r="G15" s="54" t="n">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="H15" s="38" t="n">
         <v>5.5</v>
       </c>
       <c r="I15" s="39" t="n">
-        <v>0.3704</v>
+        <v>0.3774</v>
       </c>
       <c r="J15" s="39" t="n">
-        <v>12.17</v>
+        <v>12.36</v>
       </c>
       <c r="K15" s="39" t="n">
         <v>17.3</v>
       </c>
       <c r="L15" s="40" t="n">
-        <v>14.22</v>
+        <v>14.34</v>
       </c>
       <c r="M15" s="40" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="N15" s="41" t="n">
-        <v>0.0822</v>
+        <v>0.0837</v>
       </c>
     </row>
     <row r="16">
@@ -20195,7 +20204,7 @@
         <v>8800</v>
       </c>
       <c r="F16" s="38" t="n">
-        <v>81.5</v>
+        <v>83.5</v>
       </c>
       <c r="G16" s="54" t="n">
         <v>120</v>
@@ -20207,19 +20216,19 @@
         <v>0.4545</v>
       </c>
       <c r="J16" s="45" t="n">
-        <v>14.63</v>
+        <v>14.83</v>
       </c>
       <c r="K16" s="45" t="n">
-        <v>20</v>
+        <v>20.3</v>
       </c>
       <c r="L16" s="40" t="n">
-        <v>16.78</v>
+        <v>17.02</v>
       </c>
       <c r="M16" s="40" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="N16" s="41" t="n">
-        <v>0.1342</v>
+        <v>0.1391</v>
       </c>
     </row>
     <row r="17">
@@ -20245,7 +20254,7 @@
         <v>7800</v>
       </c>
       <c r="F17" s="38" t="n">
-        <v>83</v>
+        <v>83.5</v>
       </c>
       <c r="G17" s="54" t="n">
         <v>135</v>
@@ -20257,19 +20266,19 @@
         <v>0.4255</v>
       </c>
       <c r="J17" s="39" t="n">
-        <v>13.6</v>
+        <v>13.65</v>
       </c>
       <c r="K17" s="39" t="n">
         <v>16.1</v>
       </c>
       <c r="L17" s="40" t="n">
-        <v>14.6</v>
+        <v>14.63</v>
       </c>
       <c r="M17" s="40" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="N17" s="41" t="n">
-        <v>0.0989</v>
+        <v>0.09859999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -20295,31 +20304,31 @@
         <v>7700</v>
       </c>
       <c r="F18" s="38" t="n">
-        <v>67.5</v>
+        <v>68.5</v>
       </c>
       <c r="G18" s="54" t="n">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="H18" s="38" t="n">
         <v>4.5</v>
       </c>
       <c r="I18" s="39" t="n">
-        <v>0.4202</v>
+        <v>0.4255</v>
       </c>
       <c r="J18" s="39" t="n">
-        <v>11.52</v>
+        <v>11.65</v>
       </c>
       <c r="K18" s="39" t="n">
         <v>15.8</v>
       </c>
       <c r="L18" s="40" t="n">
-        <v>13.23</v>
+        <v>13.31</v>
       </c>
       <c r="M18" s="40" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="N18" s="41" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.0727</v>
       </c>
     </row>
     <row r="19">
@@ -20345,27 +20354,25 @@
         <v>7500</v>
       </c>
       <c r="F19" s="38" t="n"/>
-      <c r="G19" s="54" t="n">
-        <v>148</v>
-      </c>
+      <c r="G19" s="54" t="n"/>
       <c r="H19" s="38" t="n"/>
       <c r="I19" s="45" t="n">
         <v>0.4032</v>
       </c>
       <c r="J19" s="45" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="K19" s="45" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="40" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M19" s="40" t="n">
-        <v>0.32</v>
+        <v>0</v>
       </c>
       <c r="N19" s="41" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="20">
@@ -20391,31 +20398,31 @@
         <v>7000</v>
       </c>
       <c r="F20" s="38" t="n">
-        <v>65</v>
+        <v>65.5</v>
       </c>
       <c r="G20" s="54" t="n">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="H20" s="38" t="n">
         <v>4.5</v>
       </c>
       <c r="I20" s="39" t="n">
-        <v>0.3922</v>
+        <v>0.4</v>
       </c>
       <c r="J20" s="39" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="K20" s="39" t="n">
-        <v>13.2</v>
+        <v>13.4</v>
       </c>
       <c r="L20" s="40" t="n">
-        <v>11.94</v>
+        <v>12.08</v>
       </c>
       <c r="M20" s="40" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="N20" s="41" t="n">
-        <v>0.0568</v>
+        <v>0.0586</v>
       </c>
     </row>
     <row r="21">
@@ -20440,28 +20447,32 @@
       <c r="E21" s="44" t="n">
         <v>5100</v>
       </c>
-      <c r="F21" s="46" t="n"/>
+      <c r="F21" s="38" t="n">
+        <v>31</v>
+      </c>
       <c r="G21" s="54" t="n">
-        <v>390</v>
-      </c>
-      <c r="H21" s="46" t="n"/>
+        <v>420</v>
+      </c>
+      <c r="H21" s="38" t="n">
+        <v>2.5</v>
+      </c>
       <c r="I21" s="45" t="n">
-        <v>0.2041</v>
+        <v>0.1923</v>
       </c>
       <c r="J21" s="45" t="n">
-        <v>1.22</v>
+        <v>5.5</v>
       </c>
       <c r="K21" s="45" t="n">
         <v>6.9</v>
       </c>
       <c r="L21" s="40" t="n">
-        <v>3.49</v>
+        <v>6.06</v>
       </c>
       <c r="M21" s="40" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.19</v>
       </c>
       <c r="N21" s="41" t="n">
-        <v>0</v>
+        <v>0.0046</v>
       </c>
     </row>
     <row r="22">
@@ -20490,28 +20501,28 @@
         <v>40.5</v>
       </c>
       <c r="G22" s="54" t="n">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="H22" s="38" t="n">
         <v>3.5</v>
       </c>
       <c r="I22" s="45" t="n">
-        <v>0.2326</v>
+        <v>0.2273</v>
       </c>
       <c r="J22" s="45" t="n">
-        <v>7.2</v>
+        <v>7.16</v>
       </c>
       <c r="K22" s="45" t="n">
         <v>9.9</v>
       </c>
       <c r="L22" s="40" t="n">
-        <v>8.279999999999999</v>
+        <v>8.26</v>
       </c>
       <c r="M22" s="40" t="n">
         <v>1.38</v>
       </c>
       <c r="N22" s="41" t="n">
-        <v>0.0171</v>
+        <v>0.0167</v>
       </c>
     </row>
     <row r="23">
@@ -20537,7 +20548,7 @@
         <v>5700</v>
       </c>
       <c r="F23" s="38" t="n">
-        <v>51</v>
+        <v>49.5</v>
       </c>
       <c r="G23" s="54" t="n">
         <v>220</v>
@@ -20549,19 +20560,19 @@
         <v>0.3125</v>
       </c>
       <c r="J23" s="39" t="n">
-        <v>8.73</v>
+        <v>8.57</v>
       </c>
       <c r="K23" s="39" t="n">
         <v>11.4</v>
       </c>
       <c r="L23" s="40" t="n">
-        <v>9.800000000000001</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="M23" s="40" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="N23" s="41" t="n">
-        <v>0.0359</v>
+        <v>0.0343</v>
       </c>
     </row>
     <row r="24">
@@ -20631,7 +20642,7 @@
         <v>6300</v>
       </c>
       <c r="F25" s="38" t="n">
-        <v>54.5</v>
+        <v>53.5</v>
       </c>
       <c r="G25" s="54" t="n">
         <v>210</v>
@@ -20643,19 +20654,19 @@
         <v>0.3226</v>
       </c>
       <c r="J25" s="39" t="n">
-        <v>9.140000000000001</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="K25" s="39" t="n">
         <v>10.1</v>
       </c>
       <c r="L25" s="40" t="n">
-        <v>9.52</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="M25" s="40" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="N25" s="41" t="n">
-        <v>0.0282</v>
+        <v>0.0272</v>
       </c>
     </row>
     <row r="26">
@@ -20681,7 +20692,7 @@
         <v>5500</v>
       </c>
       <c r="F26" s="38" t="n">
-        <v>27.5</v>
+        <v>26.5</v>
       </c>
       <c r="G26" s="54" t="n">
         <v>450</v>
@@ -20693,19 +20704,19 @@
         <v>0.1818</v>
       </c>
       <c r="J26" s="45" t="n">
-        <v>5.09</v>
+        <v>4.99</v>
       </c>
       <c r="K26" s="45" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="L26" s="40" t="n">
-        <v>6.33</v>
+        <v>6.27</v>
       </c>
       <c r="M26" s="40" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="N26" s="41" t="n">
-        <v>0.0054</v>
+        <v>0.0051</v>
       </c>
     </row>
     <row r="27">
@@ -20731,27 +20742,25 @@
         <v>6000</v>
       </c>
       <c r="F27" s="46" t="n"/>
-      <c r="G27" s="54" t="n">
-        <v>245</v>
-      </c>
+      <c r="G27" s="54" t="n"/>
       <c r="H27" s="46" t="n"/>
       <c r="I27" s="45" t="n">
         <v>0.2899</v>
       </c>
       <c r="J27" s="45" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="K27" s="45" t="n">
-        <v>12.9</v>
+        <v>0</v>
       </c>
       <c r="L27" s="40" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="M27" s="40" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="N27" s="41" t="n">
-        <v>0.0043</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="28">
@@ -20777,7 +20786,7 @@
         <v>5800</v>
       </c>
       <c r="F28" s="38" t="n">
-        <v>54</v>
+        <v>51.5</v>
       </c>
       <c r="G28" s="54" t="n">
         <v>330</v>
@@ -20789,19 +20798,19 @@
         <v>0.2326</v>
       </c>
       <c r="J28" s="45" t="n">
-        <v>9.050000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K28" s="45" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="L28" s="40" t="n">
-        <v>9.51</v>
+        <v>9.4</v>
       </c>
       <c r="M28" s="40" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="N28" s="41" t="n">
-        <v>0.0312</v>
+        <v>0.0295</v>
       </c>
     </row>
     <row r="29">
@@ -20830,28 +20839,28 @@
         <v>48.5</v>
       </c>
       <c r="G29" s="54" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="H29" s="38" t="n">
         <v>4.5</v>
       </c>
       <c r="I29" s="39" t="n">
-        <v>0.2857</v>
+        <v>0.2941</v>
       </c>
       <c r="J29" s="39" t="n">
-        <v>8.81</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="K29" s="39" t="n">
         <v>11.5</v>
       </c>
       <c r="L29" s="40" t="n">
-        <v>9.890000000000001</v>
+        <v>9.92</v>
       </c>
       <c r="M29" s="40" t="n">
         <v>1.55</v>
       </c>
       <c r="N29" s="41" t="n">
-        <v>0.0319</v>
+        <v>0.032</v>
       </c>
     </row>
     <row r="30">
@@ -20921,31 +20930,31 @@
         <v>5900</v>
       </c>
       <c r="F31" s="38" t="n">
-        <v>40.5</v>
+        <v>42.5</v>
       </c>
       <c r="G31" s="54" t="n">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="H31" s="38" t="n">
         <v>4.5</v>
       </c>
       <c r="I31" s="39" t="n">
-        <v>0.2222</v>
+        <v>0.2174</v>
       </c>
       <c r="J31" s="39" t="n">
-        <v>7.63</v>
+        <v>7.8</v>
       </c>
       <c r="K31" s="39" t="n">
         <v>7.7</v>
       </c>
       <c r="L31" s="40" t="n">
-        <v>7.66</v>
+        <v>7.76</v>
       </c>
       <c r="M31" s="40" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="N31" s="41" t="n">
-        <v>0.0125</v>
+        <v>0.0131</v>
       </c>
     </row>
     <row r="32">
@@ -20974,28 +20983,28 @@
         <v>52.5</v>
       </c>
       <c r="G32" s="54" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="H32" s="38" t="n">
         <v>4.5</v>
       </c>
       <c r="I32" s="45" t="n">
-        <v>0.3226</v>
+        <v>0.3333</v>
       </c>
       <c r="J32" s="45" t="n">
-        <v>9.44</v>
+        <v>9.5</v>
       </c>
       <c r="K32" s="45" t="n">
         <v>10.3</v>
       </c>
       <c r="L32" s="40" t="n">
-        <v>9.779999999999999</v>
+        <v>9.82</v>
       </c>
       <c r="M32" s="40" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="N32" s="41" t="n">
-        <v>0.03</v>
+        <v>0.0302</v>
       </c>
     </row>
     <row r="33">
@@ -21021,31 +21030,31 @@
         <v>5700</v>
       </c>
       <c r="F33" s="38" t="n">
-        <v>40</v>
+        <v>39.5</v>
       </c>
       <c r="G33" s="54" t="n">
-        <v>370</v>
+        <v>400</v>
       </c>
       <c r="H33" s="38" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="I33" s="39" t="n">
-        <v>0.2128</v>
+        <v>0.2</v>
       </c>
       <c r="J33" s="39" t="n">
-        <v>7.03</v>
+        <v>7.4</v>
       </c>
       <c r="K33" s="39" t="n">
         <v>9.6</v>
       </c>
       <c r="L33" s="40" t="n">
-        <v>8.06</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="M33" s="40" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="N33" s="41" t="n">
-        <v>0.0163</v>
+        <v>0.0181</v>
       </c>
     </row>
     <row r="34">
@@ -21118,28 +21127,28 @@
         <v>36.5</v>
       </c>
       <c r="G35" s="54" t="n">
-        <v>390</v>
+        <v>425</v>
       </c>
       <c r="H35" s="38" t="n">
         <v>4.5</v>
       </c>
       <c r="I35" s="39" t="n">
-        <v>0.2041</v>
+        <v>0.1905</v>
       </c>
       <c r="J35" s="39" t="n">
-        <v>7.12</v>
+        <v>7.04</v>
       </c>
       <c r="K35" s="39" t="n">
         <v>7.6</v>
       </c>
       <c r="L35" s="40" t="n">
-        <v>7.31</v>
+        <v>7.27</v>
       </c>
       <c r="M35" s="40" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="N35" s="41" t="n">
-        <v>0.0119</v>
+        <v>0.0115</v>
       </c>
     </row>
     <row r="36">
@@ -21165,31 +21174,31 @@
         <v>6100</v>
       </c>
       <c r="F36" s="38" t="n">
-        <v>42.5</v>
+        <v>49.5</v>
       </c>
       <c r="G36" s="54" t="n">
-        <v>360</v>
+        <v>380</v>
       </c>
       <c r="H36" s="38" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="I36" s="39" t="n">
-        <v>0.2174</v>
+        <v>0.2083</v>
       </c>
       <c r="J36" s="39" t="n">
-        <v>7.3</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="K36" s="39" t="n">
         <v>7.5</v>
       </c>
       <c r="L36" s="40" t="n">
-        <v>7.38</v>
+        <v>8.07</v>
       </c>
       <c r="M36" s="40" t="n">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="N36" s="41" t="n">
-        <v>0.0101</v>
+        <v>0.0148</v>
       </c>
     </row>
     <row r="37">
@@ -21215,31 +21224,31 @@
         <v>5900</v>
       </c>
       <c r="F37" s="38" t="n">
-        <v>43.5</v>
+        <v>38.5</v>
       </c>
       <c r="G37" s="54" t="n">
-        <v>270</v>
+        <v>300</v>
       </c>
       <c r="H37" s="38" t="n">
         <v>3.5</v>
       </c>
       <c r="I37" s="39" t="n">
-        <v>0.2703</v>
+        <v>0.25</v>
       </c>
       <c r="J37" s="39" t="n">
-        <v>7.72</v>
+        <v>7.1</v>
       </c>
       <c r="K37" s="39" t="n">
         <v>10.3</v>
       </c>
       <c r="L37" s="40" t="n">
-        <v>8.75</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="M37" s="40" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="N37" s="41" t="n">
-        <v>0.0219</v>
+        <v>0.0182</v>
       </c>
     </row>
     <row r="38">
@@ -21309,31 +21318,31 @@
         <v>5800</v>
       </c>
       <c r="F39" s="38" t="n">
-        <v>28.5</v>
+        <v>27.5</v>
       </c>
       <c r="G39" s="54" t="n">
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="H39" s="38" t="n">
         <v>2.5</v>
       </c>
       <c r="I39" s="45" t="n">
-        <v>0.2</v>
+        <v>0.1923</v>
       </c>
       <c r="J39" s="45" t="n">
-        <v>5.3</v>
+        <v>5.15</v>
       </c>
       <c r="K39" s="45" t="n">
         <v>7.3</v>
       </c>
       <c r="L39" s="40" t="n">
-        <v>6.1</v>
+        <v>6.01</v>
       </c>
       <c r="M39" s="40" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N39" s="41" t="n">
-        <v>0.0041</v>
+        <v>0.0037</v>
       </c>
     </row>
     <row r="40">
@@ -21359,31 +21368,31 @@
         <v>5600</v>
       </c>
       <c r="F40" s="38" t="n">
-        <v>35.5</v>
+        <v>34.5</v>
       </c>
       <c r="G40" s="54" t="n">
-        <v>390</v>
+        <v>425</v>
       </c>
       <c r="H40" s="38" t="n">
         <v>3.5</v>
       </c>
       <c r="I40" s="45" t="n">
-        <v>0.2041</v>
+        <v>0.1905</v>
       </c>
       <c r="J40" s="45" t="n">
-        <v>6.52</v>
+        <v>6.34</v>
       </c>
       <c r="K40" s="45" t="n">
         <v>6.8</v>
       </c>
       <c r="L40" s="40" t="n">
-        <v>6.63</v>
+        <v>6.53</v>
       </c>
       <c r="M40" s="40" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="N40" s="41" t="n">
-        <v>0.0067</v>
+        <v>0.0062</v>
       </c>
     </row>
     <row r="41">
@@ -21498,23 +21507,23 @@
       </c>
       <c r="F43" s="46" t="n"/>
       <c r="G43" s="54" t="n">
-        <v>400</v>
+        <v>475</v>
       </c>
       <c r="H43" s="46" t="n"/>
       <c r="I43" s="45" t="n">
-        <v>0.2</v>
+        <v>0.1739</v>
       </c>
       <c r="J43" s="45" t="n">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="K43" s="45" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="L43" s="40" t="n">
-        <v>2.92</v>
+        <v>3.27</v>
       </c>
       <c r="M43" s="40" t="n">
-        <v>0.51</v>
+        <v>0.57</v>
       </c>
       <c r="N43" s="41" t="n">
         <v>0</v>
@@ -21542,28 +21551,32 @@
       <c r="E44" s="44" t="n">
         <v>5300</v>
       </c>
-      <c r="F44" s="46" t="n"/>
+      <c r="F44" s="38" t="n">
+        <v>25.5</v>
+      </c>
       <c r="G44" s="54" t="n">
         <v>400</v>
       </c>
-      <c r="H44" s="46" t="n"/>
+      <c r="H44" s="38" t="n">
+        <v>2.5</v>
+      </c>
       <c r="I44" s="45" t="n">
         <v>0.2</v>
       </c>
       <c r="J44" s="45" t="n">
-        <v>1.2</v>
+        <v>5</v>
       </c>
       <c r="K44" s="45" t="n">
         <v>7.5</v>
       </c>
       <c r="L44" s="40" t="n">
-        <v>3.72</v>
+        <v>6</v>
       </c>
       <c r="M44" s="40" t="n">
-        <v>0.7</v>
+        <v>1.13</v>
       </c>
       <c r="N44" s="41" t="n">
-        <v>0</v>
+        <v>0.0042</v>
       </c>
     </row>
     <row r="45">
@@ -21589,31 +21602,31 @@
         <v>4000</v>
       </c>
       <c r="F45" s="38" t="n">
-        <v>22</v>
+        <v>21.5</v>
       </c>
       <c r="G45" s="54" t="n">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="H45" s="38" t="n">
         <v>2.5</v>
       </c>
       <c r="I45" s="45" t="n">
-        <v>0.1887</v>
+        <v>0.1905</v>
       </c>
       <c r="J45" s="45" t="n">
-        <v>4.58</v>
+        <v>4.54</v>
       </c>
       <c r="K45" s="45" t="n">
         <v>7.2</v>
       </c>
       <c r="L45" s="40" t="n">
-        <v>5.63</v>
+        <v>5.61</v>
       </c>
       <c r="M45" s="40" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="N45" s="41" t="n">
-        <v>0.0041</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="46">
@@ -21639,31 +21652,31 @@
         <v>5300</v>
       </c>
       <c r="F46" s="38" t="n">
-        <v>42.5</v>
+        <v>44.5</v>
       </c>
       <c r="G46" s="54" t="n">
-        <v>240</v>
+        <v>270</v>
       </c>
       <c r="H46" s="38" t="n">
         <v>4.5</v>
       </c>
       <c r="I46" s="45" t="n">
-        <v>0.2941</v>
+        <v>0.2703</v>
       </c>
       <c r="J46" s="45" t="n">
-        <v>8.26</v>
+        <v>8.32</v>
       </c>
       <c r="K46" s="45" t="n">
-        <v>7.7</v>
+        <v>9.9</v>
       </c>
       <c r="L46" s="40" t="n">
-        <v>8.039999999999999</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="M46" s="40" t="n">
-        <v>1.52</v>
+        <v>1.69</v>
       </c>
       <c r="N46" s="41" t="n">
-        <v>0.0177</v>
+        <v>0.0273</v>
       </c>
     </row>
     <row r="47">
@@ -21690,23 +21703,23 @@
       </c>
       <c r="F47" s="46" t="n"/>
       <c r="G47" s="54" t="n">
-        <v>1200</v>
+        <v>1050</v>
       </c>
       <c r="H47" s="46" t="n"/>
       <c r="I47" s="45" t="n">
-        <v>0.0769</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="J47" s="45" t="n">
-        <v>0.46</v>
+        <v>0.52</v>
       </c>
       <c r="K47" s="45" t="n">
         <v>3.4</v>
       </c>
       <c r="L47" s="40" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="M47" s="40" t="n">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="N47" s="41" t="n">
         <v>0</v>
@@ -21735,31 +21748,31 @@
         <v>4900</v>
       </c>
       <c r="F48" s="38" t="n">
-        <v>35.5</v>
+        <v>36.5</v>
       </c>
       <c r="G48" s="54" t="n">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="H48" s="38" t="n">
         <v>2.5</v>
       </c>
       <c r="I48" s="39" t="n">
-        <v>0.2381</v>
+        <v>0.2439</v>
       </c>
       <c r="J48" s="39" t="n">
-        <v>6.23</v>
+        <v>6.36</v>
       </c>
       <c r="K48" s="39" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L48" s="40" t="n">
-        <v>6.54</v>
+        <v>7.82</v>
       </c>
       <c r="M48" s="40" t="n">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="N48" s="41" t="n">
-        <v>0.0075</v>
+        <v>0.0172</v>
       </c>
     </row>
     <row r="49">
@@ -21784,28 +21797,32 @@
       <c r="E49" s="37" t="n">
         <v>5000</v>
       </c>
-      <c r="F49" s="46" t="n"/>
+      <c r="F49" s="38" t="n">
+        <v>26.5</v>
+      </c>
       <c r="G49" s="54" t="n">
-        <v>370</v>
-      </c>
-      <c r="H49" s="46" t="n"/>
+        <v>400</v>
+      </c>
+      <c r="H49" s="38" t="n">
+        <v>2.5</v>
+      </c>
       <c r="I49" s="39" t="n">
-        <v>0.2128</v>
+        <v>0.2</v>
       </c>
       <c r="J49" s="39" t="n">
-        <v>1.28</v>
+        <v>5.1</v>
       </c>
       <c r="K49" s="39" t="n">
         <v>7</v>
       </c>
       <c r="L49" s="40" t="n">
-        <v>3.57</v>
+        <v>5.86</v>
       </c>
       <c r="M49" s="40" t="n">
-        <v>0.71</v>
+        <v>1.17</v>
       </c>
       <c r="N49" s="41" t="n">
-        <v>0</v>
+        <v>0.0039</v>
       </c>
     </row>
     <row r="50">
@@ -21831,7 +21848,7 @@
         <v>5200</v>
       </c>
       <c r="F50" s="38" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="G50" s="54" t="n">
         <v>650</v>
@@ -21843,16 +21860,16 @@
         <v>0.1333</v>
       </c>
       <c r="J50" s="39" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="K50" s="39" t="n">
         <v>4</v>
       </c>
       <c r="L50" s="40" t="n">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="M50" s="40" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="N50" s="41" t="n">
         <v>0</v>
@@ -21881,7 +21898,7 @@
         <v>5200</v>
       </c>
       <c r="F51" s="38" t="n">
-        <v>35.5</v>
+        <v>33.5</v>
       </c>
       <c r="G51" s="54" t="n">
         <v>425</v>
@@ -21893,19 +21910,19 @@
         <v>0.1905</v>
       </c>
       <c r="J51" s="39" t="n">
-        <v>5.94</v>
+        <v>5.74</v>
       </c>
       <c r="K51" s="39" t="n">
         <v>6.4</v>
       </c>
       <c r="L51" s="40" t="n">
-        <v>6.13</v>
+        <v>6.01</v>
       </c>
       <c r="M51" s="40" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="N51" s="41" t="n">
-        <v>0.0049</v>
+        <v>0.0043</v>
       </c>
     </row>
     <row r="52">
@@ -21974,28 +21991,32 @@
       <c r="E53" s="37" t="n">
         <v>5400</v>
       </c>
-      <c r="F53" s="46" t="n"/>
+      <c r="F53" s="38" t="n">
+        <v>22</v>
+      </c>
       <c r="G53" s="54" t="n">
-        <v>650</v>
-      </c>
-      <c r="H53" s="46" t="n"/>
+        <v>550</v>
+      </c>
+      <c r="H53" s="38" t="n">
+        <v>1.5</v>
+      </c>
       <c r="I53" s="39" t="n">
-        <v>0.1333</v>
+        <v>0.1538</v>
       </c>
       <c r="J53" s="39" t="n">
-        <v>0.8</v>
+        <v>3.87</v>
       </c>
       <c r="K53" s="39" t="n">
         <v>6.9</v>
       </c>
       <c r="L53" s="40" t="n">
-        <v>3.24</v>
+        <v>5.08</v>
       </c>
       <c r="M53" s="40" t="n">
-        <v>0.6</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="N53" s="41" t="n">
-        <v>0</v>
+        <v>0.0013</v>
       </c>
     </row>
     <row r="54">
@@ -22066,23 +22087,23 @@
       </c>
       <c r="F55" s="46" t="n"/>
       <c r="G55" s="54" t="n">
-        <v>1300</v>
+        <v>1550</v>
       </c>
       <c r="H55" s="46" t="n"/>
       <c r="I55" s="39" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0606</v>
       </c>
       <c r="J55" s="39" t="n">
-        <v>0.43</v>
+        <v>0.36</v>
       </c>
       <c r="K55" s="39" t="n">
         <v>0</v>
       </c>
       <c r="L55" s="40" t="n">
-        <v>0.43</v>
+        <v>0.36</v>
       </c>
       <c r="M55" s="40" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N55" s="41" t="n">
         <v>0</v>
@@ -22114,28 +22135,28 @@
         <v>38.5</v>
       </c>
       <c r="G56" s="54" t="n">
-        <v>290</v>
+        <v>310</v>
       </c>
       <c r="H56" s="38" t="n">
         <v>4.5</v>
       </c>
       <c r="I56" s="45" t="n">
-        <v>0.2564</v>
+        <v>0.2439</v>
       </c>
       <c r="J56" s="45" t="n">
-        <v>7.64</v>
+        <v>7.56</v>
       </c>
       <c r="K56" s="45" t="n">
         <v>8</v>
       </c>
       <c r="L56" s="40" t="n">
-        <v>7.78</v>
+        <v>7.74</v>
       </c>
       <c r="M56" s="40" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="N56" s="41" t="n">
-        <v>0.0143</v>
+        <v>0.0138</v>
       </c>
     </row>
     <row r="57">
@@ -22161,31 +22182,31 @@
         <v>4900</v>
       </c>
       <c r="F57" s="38" t="n">
-        <v>20.5</v>
+        <v>19.5</v>
       </c>
       <c r="G57" s="54" t="n">
-        <v>800</v>
+        <v>750</v>
       </c>
       <c r="H57" s="38" t="n">
         <v>1.5</v>
       </c>
       <c r="I57" s="39" t="n">
-        <v>0.1111</v>
+        <v>0.1176</v>
       </c>
       <c r="J57" s="39" t="n">
-        <v>3.47</v>
+        <v>3.41</v>
       </c>
       <c r="K57" s="39" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="L57" s="40" t="n">
-        <v>4.88</v>
+        <v>5.04</v>
       </c>
       <c r="M57" s="40" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="N57" s="41" t="n">
-        <v>0.001</v>
+        <v>0.0014</v>
       </c>
     </row>
     <row r="58">
@@ -22235,7 +22256,7 @@
         <v>1.09</v>
       </c>
       <c r="N58" s="41" t="n">
-        <v>0.0022</v>
+        <v>0.0021</v>
       </c>
     </row>
     <row r="59">
@@ -22351,26 +22372,26 @@
       </c>
       <c r="F61" s="38" t="n"/>
       <c r="G61" s="54" t="n">
-        <v>350</v>
+        <v>280</v>
       </c>
       <c r="H61" s="38" t="n"/>
       <c r="I61" s="39" t="n">
-        <v>0.2222</v>
+        <v>0.2632</v>
       </c>
       <c r="J61" s="39" t="n">
-        <v>1.33</v>
+        <v>1.58</v>
       </c>
       <c r="K61" s="39" t="n">
-        <v>5.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L61" s="40" t="n">
-        <v>3.08</v>
+        <v>4.63</v>
       </c>
       <c r="M61" s="40" t="n">
-        <v>0.63</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="N61" s="41" t="n">
-        <v>0</v>
+        <v>0.0005999999999999999</v>
       </c>
     </row>
     <row r="62">
@@ -22443,28 +22464,28 @@
         <v>29.5</v>
       </c>
       <c r="G63" s="54" t="n">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="H63" s="38" t="n">
         <v>2.5</v>
       </c>
       <c r="I63" s="45" t="n">
-        <v>0.2632</v>
+        <v>0.2564</v>
       </c>
       <c r="J63" s="45" t="n">
-        <v>5.78</v>
+        <v>5.74</v>
       </c>
       <c r="K63" s="45" t="n">
         <v>7</v>
       </c>
       <c r="L63" s="40" t="n">
-        <v>6.27</v>
+        <v>6.24</v>
       </c>
       <c r="M63" s="40" t="n">
         <v>1.14</v>
       </c>
       <c r="N63" s="41" t="n">
-        <v>0.0051</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="64">
@@ -22490,7 +22511,7 @@
         <v>4500</v>
       </c>
       <c r="F64" s="38" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="G64" s="54" t="n">
         <v>1000</v>
@@ -22502,16 +22523,16 @@
         <v>0.09089999999999999</v>
       </c>
       <c r="J64" s="39" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="K64" s="39" t="n">
         <v>4.3</v>
       </c>
       <c r="L64" s="40" t="n">
-        <v>3.16</v>
+        <v>3.13</v>
       </c>
       <c r="M64" s="40" t="n">
-        <v>0.7</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="N64" s="41" t="n">
         <v>0</v>
@@ -22540,28 +22561,28 @@
         <v>4800</v>
       </c>
       <c r="F65" s="38" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="G65" s="54" t="n">
-        <v>450</v>
+        <v>475</v>
       </c>
       <c r="H65" s="38" t="n">
         <v>1.5</v>
       </c>
       <c r="I65" s="45" t="n">
-        <v>0.1818</v>
+        <v>0.1739</v>
       </c>
       <c r="J65" s="45" t="n">
-        <v>3.09</v>
+        <v>3.24</v>
       </c>
       <c r="K65" s="45" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L65" s="40" t="n">
-        <v>3.89</v>
+        <v>4.03</v>
       </c>
       <c r="M65" s="40" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.84</v>
       </c>
       <c r="N65" s="41" t="n">
         <v>0</v>
@@ -22590,7 +22611,7 @@
         <v>5800</v>
       </c>
       <c r="F66" s="38" t="n">
-        <v>34</v>
+        <v>33.5</v>
       </c>
       <c r="G66" s="54" t="n">
         <v>250</v>
@@ -22602,19 +22623,19 @@
         <v>0.2857</v>
       </c>
       <c r="J66" s="45" t="n">
-        <v>6.86</v>
+        <v>6.81</v>
       </c>
       <c r="K66" s="45" t="n">
         <v>8.4</v>
       </c>
       <c r="L66" s="40" t="n">
-        <v>7.48</v>
+        <v>7.45</v>
       </c>
       <c r="M66" s="40" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="N66" s="41" t="n">
-        <v>0.0115</v>
+        <v>0.0111</v>
       </c>
     </row>
     <row r="67">
@@ -22640,19 +22661,19 @@
         <v>5000</v>
       </c>
       <c r="F67" s="38" t="n">
-        <v>21.5</v>
+        <v>20.5</v>
       </c>
       <c r="G67" s="54" t="n">
-        <v>900</v>
+        <v>750</v>
       </c>
       <c r="H67" s="38" t="n">
         <v>1.5</v>
       </c>
       <c r="I67" s="39" t="n">
-        <v>0.1</v>
+        <v>0.1176</v>
       </c>
       <c r="J67" s="39" t="n">
-        <v>3.5</v>
+        <v>3.51</v>
       </c>
       <c r="K67" s="39" t="n">
         <v>5.3</v>
@@ -22741,23 +22762,23 @@
       </c>
       <c r="F69" s="46" t="n"/>
       <c r="G69" s="54" t="n">
-        <v>390</v>
+        <v>425</v>
       </c>
       <c r="H69" s="46" t="n"/>
       <c r="I69" s="45" t="n">
-        <v>0.2041</v>
+        <v>0.1905</v>
       </c>
       <c r="J69" s="45" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="K69" s="45" t="n">
-        <v>4.4</v>
+        <v>6.3</v>
       </c>
       <c r="L69" s="40" t="n">
-        <v>2.49</v>
+        <v>3.21</v>
       </c>
       <c r="M69" s="40" t="n">
-        <v>0.62</v>
+        <v>0.8</v>
       </c>
       <c r="N69" s="41" t="n">
         <v>0</v>
@@ -22786,7 +22807,7 @@
         <v>4600</v>
       </c>
       <c r="F70" s="38" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="G70" s="54" t="n">
         <v>750</v>
@@ -22798,16 +22819,16 @@
         <v>0.1176</v>
       </c>
       <c r="J70" s="39" t="n">
-        <v>2.71</v>
+        <v>3.06</v>
       </c>
       <c r="K70" s="39" t="n">
-        <v>3.6</v>
+        <v>5.4</v>
       </c>
       <c r="L70" s="40" t="n">
-        <v>3.06</v>
+        <v>3.99</v>
       </c>
       <c r="M70" s="40" t="n">
-        <v>0.67</v>
+        <v>0.87</v>
       </c>
       <c r="N70" s="41" t="n">
         <v>0</v>
@@ -22836,31 +22857,31 @@
         <v>5400</v>
       </c>
       <c r="F71" s="38" t="n">
-        <v>22.5</v>
+        <v>20.5</v>
       </c>
       <c r="G71" s="54" t="n">
-        <v>525</v>
+        <v>600</v>
       </c>
       <c r="H71" s="38" t="n">
         <v>1.5</v>
       </c>
       <c r="I71" s="45" t="n">
-        <v>0.16</v>
+        <v>0.1429</v>
       </c>
       <c r="J71" s="45" t="n">
-        <v>3.96</v>
+        <v>3.66</v>
       </c>
       <c r="K71" s="45" t="n">
         <v>5.2</v>
       </c>
       <c r="L71" s="40" t="n">
-        <v>4.46</v>
+        <v>4.27</v>
       </c>
       <c r="M71" s="40" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="N71" s="41" t="n">
-        <v>0.0003</v>
+        <v>0.0001</v>
       </c>
     </row>
     <row r="72">
@@ -22887,23 +22908,23 @@
       </c>
       <c r="F72" s="46" t="n"/>
       <c r="G72" s="54" t="n">
-        <v>1900</v>
+        <v>1500</v>
       </c>
       <c r="H72" s="46" t="n"/>
       <c r="I72" s="45" t="n">
-        <v>0.05</v>
+        <v>0.0625</v>
       </c>
       <c r="J72" s="45" t="n">
-        <v>0.3</v>
+        <v>0.38</v>
       </c>
       <c r="K72" s="45" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="L72" s="40" t="n">
-        <v>0.3</v>
+        <v>0.78</v>
       </c>
       <c r="M72" s="40" t="n">
-        <v>0.08</v>
+        <v>0.2</v>
       </c>
       <c r="N72" s="41" t="n">
         <v>0</v>
@@ -22932,31 +22953,31 @@
         <v>4700</v>
       </c>
       <c r="F73" s="38" t="n">
-        <v>26.5</v>
+        <v>28.5</v>
       </c>
       <c r="G73" s="54" t="n">
-        <v>460</v>
+        <v>500</v>
       </c>
       <c r="H73" s="38" t="n">
         <v>2.5</v>
       </c>
       <c r="I73" s="45" t="n">
-        <v>0.1786</v>
+        <v>0.1667</v>
       </c>
       <c r="J73" s="45" t="n">
-        <v>4.97</v>
+        <v>5.1</v>
       </c>
       <c r="K73" s="45" t="n">
-        <v>4.4</v>
+        <v>8.4</v>
       </c>
       <c r="L73" s="40" t="n">
-        <v>4.74</v>
+        <v>6.42</v>
       </c>
       <c r="M73" s="40" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="N73" s="41" t="n">
-        <v>0.0008</v>
+        <v>0.0071</v>
       </c>
     </row>
     <row r="74">
@@ -22983,23 +23004,23 @@
       </c>
       <c r="F74" s="38" t="n"/>
       <c r="G74" s="54" t="n">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="H74" s="38" t="n"/>
       <c r="I74" s="39" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0667</v>
       </c>
       <c r="J74" s="39" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="K74" s="39" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="L74" s="40" t="n">
-        <v>0.78</v>
+        <v>1.08</v>
       </c>
       <c r="M74" s="40" t="n">
-        <v>0.17</v>
+        <v>0.24</v>
       </c>
       <c r="N74" s="41" t="n">
         <v>0</v>
@@ -23029,20 +23050,20 @@
       </c>
       <c r="F75" s="38" t="n"/>
       <c r="G75" s="54" t="n">
-        <v>1100</v>
+        <v>1150</v>
       </c>
       <c r="H75" s="38" t="n"/>
       <c r="I75" s="45" t="n">
-        <v>0.0833</v>
+        <v>0.08</v>
       </c>
       <c r="J75" s="45" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="K75" s="45" t="n">
         <v>5.4</v>
       </c>
       <c r="L75" s="40" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="M75" s="40" t="n">
         <v>0.52</v>
@@ -23074,31 +23095,31 @@
         <v>5400</v>
       </c>
       <c r="F76" s="38" t="n">
-        <v>24.5</v>
+        <v>23.5</v>
       </c>
       <c r="G76" s="54" t="n">
-        <v>460</v>
+        <v>475</v>
       </c>
       <c r="H76" s="38" t="n">
         <v>2.5</v>
       </c>
       <c r="I76" s="39" t="n">
-        <v>0.1786</v>
+        <v>0.1739</v>
       </c>
       <c r="J76" s="39" t="n">
-        <v>4.77</v>
+        <v>4.64</v>
       </c>
       <c r="K76" s="39" t="n">
         <v>6</v>
       </c>
       <c r="L76" s="40" t="n">
-        <v>5.26</v>
+        <v>5.19</v>
       </c>
       <c r="M76" s="40" t="n">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="N76" s="41" t="n">
-        <v>0.0017</v>
+        <v>0.0015</v>
       </c>
     </row>
     <row r="77">
@@ -23124,28 +23145,28 @@
         <v>4900</v>
       </c>
       <c r="F77" s="38" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="G77" s="54" t="n">
-        <v>1000</v>
+        <v>850</v>
       </c>
       <c r="H77" s="38" t="n">
         <v>1.5</v>
       </c>
       <c r="I77" s="45" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.1053</v>
       </c>
       <c r="J77" s="45" t="n">
-        <v>3.25</v>
+        <v>3.13</v>
       </c>
       <c r="K77" s="45" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="L77" s="40" t="n">
-        <v>3.71</v>
+        <v>3.88</v>
       </c>
       <c r="M77" s="40" t="n">
-        <v>0.76</v>
+        <v>0.79</v>
       </c>
       <c r="N77" s="41" t="n">
         <v>0</v>
@@ -23175,23 +23196,23 @@
       </c>
       <c r="F78" s="38" t="n"/>
       <c r="G78" s="54" t="n">
-        <v>1400</v>
+        <v>1200</v>
       </c>
       <c r="H78" s="38" t="n"/>
       <c r="I78" s="45" t="n">
-        <v>0.0667</v>
+        <v>0.0769</v>
       </c>
       <c r="J78" s="45" t="n">
-        <v>0.4</v>
+        <v>0.46</v>
       </c>
       <c r="K78" s="45" t="n">
         <v>4.1</v>
       </c>
       <c r="L78" s="40" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="M78" s="40" t="n">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="N78" s="41" t="n">
         <v>0</v>
@@ -23220,31 +23241,31 @@
         <v>4900</v>
       </c>
       <c r="F79" s="38" t="n">
-        <v>20.5</v>
+        <v>19.5</v>
       </c>
       <c r="G79" s="54" t="n">
-        <v>600</v>
+        <v>650</v>
       </c>
       <c r="H79" s="38" t="n">
         <v>1.5</v>
       </c>
       <c r="I79" s="45" t="n">
-        <v>0.1429</v>
+        <v>0.1333</v>
       </c>
       <c r="J79" s="45" t="n">
-        <v>3.66</v>
+        <v>3.5</v>
       </c>
       <c r="K79" s="45" t="n">
         <v>5</v>
       </c>
       <c r="L79" s="40" t="n">
-        <v>4.19</v>
+        <v>4.1</v>
       </c>
       <c r="M79" s="40" t="n">
-        <v>0.86</v>
+        <v>0.84</v>
       </c>
       <c r="N79" s="41" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -23361,23 +23382,23 @@
       </c>
       <c r="F82" s="46" t="n"/>
       <c r="G82" s="54" t="n">
-        <v>700</v>
+        <v>1300</v>
       </c>
       <c r="H82" s="46" t="n"/>
       <c r="I82" s="39" t="n">
-        <v>0.125</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="J82" s="39" t="n">
-        <v>0.75</v>
+        <v>0.43</v>
       </c>
       <c r="K82" s="39" t="n">
         <v>1.4</v>
       </c>
       <c r="L82" s="40" t="n">
-        <v>1.01</v>
+        <v>0.82</v>
       </c>
       <c r="M82" s="40" t="n">
-        <v>0.22</v>
+        <v>0.18</v>
       </c>
       <c r="N82" s="41" t="n">
         <v>0</v>
@@ -23407,23 +23428,23 @@
       </c>
       <c r="F83" s="46" t="n"/>
       <c r="G83" s="54" t="n">
-        <v>1200</v>
+        <v>1350</v>
       </c>
       <c r="H83" s="46" t="n"/>
       <c r="I83" s="39" t="n">
-        <v>0.0769</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="J83" s="39" t="n">
-        <v>0.46</v>
+        <v>0.41</v>
       </c>
       <c r="K83" s="39" t="n">
         <v>0</v>
       </c>
       <c r="L83" s="40" t="n">
-        <v>0.46</v>
+        <v>0.41</v>
       </c>
       <c r="M83" s="40" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="N83" s="41" t="n">
         <v>0</v>
@@ -23586,23 +23607,23 @@
       </c>
       <c r="F87" s="46" t="n"/>
       <c r="G87" s="54" t="n">
-        <v>600</v>
+        <v>550</v>
       </c>
       <c r="H87" s="46" t="n"/>
       <c r="I87" s="45" t="n">
-        <v>0.1429</v>
+        <v>0.1538</v>
       </c>
       <c r="J87" s="45" t="n">
-        <v>0.86</v>
+        <v>0.92</v>
       </c>
       <c r="K87" s="45" t="n">
         <v>5.4</v>
       </c>
       <c r="L87" s="40" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="M87" s="40" t="n">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="N87" s="41" t="n">
         <v>0</v>
@@ -23630,22 +23651,26 @@
       <c r="E88" s="44" t="n">
         <v>4800</v>
       </c>
-      <c r="F88" s="46" t="n"/>
+      <c r="F88" s="38" t="n">
+        <v>8.5</v>
+      </c>
       <c r="G88" s="54" t="n">
-        <v>850</v>
-      </c>
-      <c r="H88" s="46" t="n"/>
+        <v>950</v>
+      </c>
+      <c r="H88" s="38" t="n">
+        <v>0.5</v>
+      </c>
       <c r="I88" s="45" t="n">
-        <v>0.1053</v>
+        <v>0.09520000000000001</v>
       </c>
       <c r="J88" s="45" t="n">
-        <v>0.63</v>
+        <v>1.67</v>
       </c>
       <c r="K88" s="45" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="L88" s="40" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="M88" s="40" t="n">
         <v>0.35</v>
@@ -23812,7 +23837,7 @@
         <v>4800</v>
       </c>
       <c r="F92" s="38" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="G92" s="54" t="n">
         <v>600</v>
@@ -23824,16 +23849,16 @@
         <v>0.1429</v>
       </c>
       <c r="J92" s="39" t="n">
-        <v>3.16</v>
+        <v>3.06</v>
       </c>
       <c r="K92" s="39" t="n">
         <v>3.9</v>
       </c>
       <c r="L92" s="40" t="n">
-        <v>3.45</v>
+        <v>3.39</v>
       </c>
       <c r="M92" s="40" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="N92" s="41" t="n">
         <v>0</v>
@@ -23863,23 +23888,23 @@
       </c>
       <c r="F93" s="38" t="n"/>
       <c r="G93" s="54" t="n">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="H93" s="38" t="n"/>
       <c r="I93" s="39" t="n">
-        <v>0.0385</v>
+        <v>0.0476</v>
       </c>
       <c r="J93" s="39" t="n">
-        <v>0.23</v>
+        <v>0.29</v>
       </c>
       <c r="K93" s="39" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="L93" s="40" t="n">
-        <v>0.74</v>
+        <v>0.97</v>
       </c>
       <c r="M93" s="40" t="n">
-        <v>0.18</v>
+        <v>0.24</v>
       </c>
       <c r="N93" s="41" t="n">
         <v>0</v>
@@ -23909,23 +23934,23 @@
       </c>
       <c r="F94" s="38" t="n"/>
       <c r="G94" s="54" t="n">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="H94" s="38" t="n"/>
       <c r="I94" s="45" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0769</v>
       </c>
       <c r="J94" s="45" t="n">
-        <v>0.43</v>
+        <v>0.46</v>
       </c>
       <c r="K94" s="45" t="n">
         <v>0</v>
       </c>
       <c r="L94" s="40" t="n">
-        <v>0.43</v>
+        <v>0.46</v>
       </c>
       <c r="M94" s="40" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="N94" s="41" t="n">
         <v>0</v>
@@ -23955,23 +23980,23 @@
       </c>
       <c r="F95" s="46" t="n"/>
       <c r="G95" s="54" t="n">
-        <v>1400</v>
+        <v>1200</v>
       </c>
       <c r="H95" s="46" t="n"/>
       <c r="I95" s="39" t="n">
-        <v>0.0667</v>
+        <v>0.0769</v>
       </c>
       <c r="J95" s="39" t="n">
-        <v>0.4</v>
+        <v>0.46</v>
       </c>
       <c r="K95" s="39" t="n">
         <v>0</v>
       </c>
       <c r="L95" s="40" t="n">
-        <v>0.4</v>
+        <v>0.46</v>
       </c>
       <c r="M95" s="40" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="N95" s="41" t="n">
         <v>0</v>
@@ -24091,23 +24116,23 @@
       </c>
       <c r="F98" s="46" t="n"/>
       <c r="G98" s="54" t="n">
-        <v>600</v>
+        <v>575</v>
       </c>
       <c r="H98" s="46" t="n"/>
       <c r="I98" s="39" t="n">
-        <v>0.1429</v>
+        <v>0.1481</v>
       </c>
       <c r="J98" s="39" t="n">
-        <v>0.86</v>
+        <v>0.89</v>
       </c>
       <c r="K98" s="39" t="n">
         <v>0</v>
       </c>
       <c r="L98" s="40" t="n">
-        <v>0.86</v>
+        <v>0.89</v>
       </c>
       <c r="M98" s="40" t="n">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="N98" s="41" t="n">
         <v>0</v>
@@ -24137,20 +24162,20 @@
       </c>
       <c r="F99" s="46" t="n"/>
       <c r="G99" s="54" t="n">
-        <v>1600</v>
+        <v>1550</v>
       </c>
       <c r="H99" s="46" t="n"/>
       <c r="I99" s="39" t="n">
-        <v>0.0588</v>
+        <v>0.0606</v>
       </c>
       <c r="J99" s="39" t="n">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="K99" s="39" t="n">
         <v>0</v>
       </c>
       <c r="L99" s="40" t="n">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="M99" s="40" t="n">
         <v>0.08</v>
@@ -24228,20 +24253,20 @@
       </c>
       <c r="F101" s="46" t="n"/>
       <c r="G101" s="54" t="n">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="H101" s="46" t="n"/>
       <c r="I101" s="45" t="n">
-        <v>0.0625</v>
+        <v>0.0588</v>
       </c>
       <c r="J101" s="45" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="K101" s="45" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="L101" s="40" t="n">
-        <v>0.98</v>
+        <v>1.01</v>
       </c>
       <c r="M101" s="40" t="n">
         <v>0.22</v>
@@ -24409,22 +24434,22 @@
         <v>5.5</v>
       </c>
       <c r="G105" s="54" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="H105" s="38" t="n">
         <v>1.5</v>
       </c>
       <c r="I105" s="45" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.09520000000000001</v>
       </c>
       <c r="J105" s="45" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="K105" s="45" t="n">
         <v>3.1</v>
       </c>
       <c r="L105" s="40" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="M105" s="40" t="n">
         <v>0.48</v>
@@ -24459,25 +24484,25 @@
         <v>16.5</v>
       </c>
       <c r="G106" s="54" t="n">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="H106" s="38" t="n">
         <v>1.5</v>
       </c>
       <c r="I106" s="45" t="n">
-        <v>0.125</v>
+        <v>0.1111</v>
       </c>
       <c r="J106" s="45" t="n">
-        <v>3.15</v>
+        <v>3.07</v>
       </c>
       <c r="K106" s="45" t="n">
         <v>4.3</v>
       </c>
       <c r="L106" s="40" t="n">
-        <v>3.61</v>
+        <v>3.56</v>
       </c>
       <c r="M106" s="40" t="n">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="N106" s="41" t="n">
         <v>0</v>
@@ -24686,23 +24711,23 @@
       </c>
       <c r="F111" s="46" t="n"/>
       <c r="G111" s="54" t="n">
-        <v>700</v>
+        <v>650</v>
       </c>
       <c r="H111" s="46" t="n"/>
       <c r="I111" s="45" t="n">
-        <v>0.125</v>
+        <v>0.1333</v>
       </c>
       <c r="J111" s="45" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="K111" s="45" t="n">
-        <v>3.4</v>
+        <v>7.9</v>
       </c>
       <c r="L111" s="40" t="n">
-        <v>1.81</v>
+        <v>3.64</v>
       </c>
       <c r="M111" s="40" t="n">
-        <v>0.42</v>
+        <v>0.85</v>
       </c>
       <c r="N111" s="41" t="n">
         <v>0</v>
@@ -24778,23 +24803,23 @@
       </c>
       <c r="F113" s="46" t="n"/>
       <c r="G113" s="54" t="n">
-        <v>1200</v>
+        <v>1400</v>
       </c>
       <c r="H113" s="46" t="n"/>
       <c r="I113" s="39" t="n">
-        <v>0.0769</v>
+        <v>0.0667</v>
       </c>
       <c r="J113" s="39" t="n">
-        <v>0.46</v>
+        <v>0.4</v>
       </c>
       <c r="K113" s="39" t="n">
         <v>0</v>
       </c>
       <c r="L113" s="40" t="n">
-        <v>0.46</v>
+        <v>0.4</v>
       </c>
       <c r="M113" s="40" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="N113" s="41" t="n">
         <v>0</v>
@@ -24824,23 +24849,23 @@
       </c>
       <c r="F114" s="46" t="n"/>
       <c r="G114" s="54" t="n">
-        <v>2200</v>
+        <v>2500</v>
       </c>
       <c r="H114" s="46" t="n"/>
       <c r="I114" s="39" t="n">
-        <v>0.0435</v>
+        <v>0.0385</v>
       </c>
       <c r="J114" s="39" t="n">
-        <v>0.26</v>
+        <v>0.23</v>
       </c>
       <c r="K114" s="39" t="n">
         <v>0</v>
       </c>
       <c r="L114" s="40" t="n">
-        <v>0.26</v>
+        <v>0.23</v>
       </c>
       <c r="M114" s="40" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="N114" s="41" t="n">
         <v>0</v>
@@ -24870,23 +24895,23 @@
       </c>
       <c r="F115" s="38" t="n"/>
       <c r="G115" s="54" t="n">
-        <v>1500</v>
+        <v>1800</v>
       </c>
       <c r="H115" s="38" t="n"/>
       <c r="I115" s="39" t="n">
-        <v>0.0625</v>
+        <v>0.0526</v>
       </c>
       <c r="J115" s="39" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
       <c r="K115" s="39" t="n">
         <v>0</v>
       </c>
       <c r="L115" s="40" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
       <c r="M115" s="40" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N115" s="41" t="n">
         <v>0</v>
@@ -25006,20 +25031,20 @@
       </c>
       <c r="F118" s="46" t="n"/>
       <c r="G118" s="54" t="n">
-        <v>1500</v>
+        <v>1700</v>
       </c>
       <c r="H118" s="46" t="n"/>
       <c r="I118" s="45" t="n">
-        <v>0.0625</v>
+        <v>0.0556</v>
       </c>
       <c r="J118" s="45" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="K118" s="45" t="n">
         <v>2.1</v>
       </c>
       <c r="L118" s="40" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="M118" s="40" t="n">
         <v>0.22</v>
@@ -25192,23 +25217,23 @@
       </c>
       <c r="F122" s="38" t="n"/>
       <c r="G122" s="54" t="n">
-        <v>1600</v>
+        <v>1800</v>
       </c>
       <c r="H122" s="38" t="n"/>
       <c r="I122" s="39" t="n">
-        <v>0.0588</v>
+        <v>0.0526</v>
       </c>
       <c r="J122" s="39" t="n">
-        <v>0.35</v>
+        <v>0.32</v>
       </c>
       <c r="K122" s="39" t="n">
         <v>0</v>
       </c>
       <c r="L122" s="40" t="n">
-        <v>0.35</v>
+        <v>0.32</v>
       </c>
       <c r="M122" s="40" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N122" s="41" t="n">
         <v>0</v>
@@ -25238,23 +25263,23 @@
       </c>
       <c r="F123" s="46" t="n"/>
       <c r="G123" s="54" t="n">
-        <v>1500</v>
+        <v>1300</v>
       </c>
       <c r="H123" s="46" t="n"/>
       <c r="I123" s="45" t="n">
-        <v>0.0625</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="J123" s="45" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="K123" s="45" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="L123" s="40" t="n">
-        <v>1.1</v>
+        <v>1.42</v>
       </c>
       <c r="M123" s="40" t="n">
-        <v>0.26</v>
+        <v>0.34</v>
       </c>
       <c r="N123" s="41" t="n">
         <v>0</v>
@@ -25330,23 +25355,23 @@
       </c>
       <c r="F125" s="46" t="n"/>
       <c r="G125" s="54" t="n">
-        <v>3500</v>
+        <v>2800</v>
       </c>
       <c r="H125" s="46" t="n"/>
       <c r="I125" s="39" t="n">
-        <v>0.0278</v>
+        <v>0.0345</v>
       </c>
       <c r="J125" s="39" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="K125" s="39" t="n">
         <v>0</v>
       </c>
       <c r="L125" s="40" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="M125" s="40" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="N125" s="41" t="n">
         <v>0</v>
@@ -25426,23 +25451,23 @@
       </c>
       <c r="F127" s="38" t="n"/>
       <c r="G127" s="54" t="n">
-        <v>440</v>
+        <v>550</v>
       </c>
       <c r="H127" s="38" t="n"/>
       <c r="I127" s="39" t="n">
-        <v>0.1852</v>
+        <v>0.1538</v>
       </c>
       <c r="J127" s="39" t="n">
-        <v>1.11</v>
+        <v>0.92</v>
       </c>
       <c r="K127" s="39" t="n">
-        <v>2.9</v>
+        <v>7.5</v>
       </c>
       <c r="L127" s="40" t="n">
-        <v>1.83</v>
+        <v>3.55</v>
       </c>
       <c r="M127" s="40" t="n">
-        <v>0.41</v>
+        <v>0.79</v>
       </c>
       <c r="N127" s="41" t="n">
         <v>0</v>
@@ -25568,20 +25593,20 @@
       </c>
       <c r="F130" s="46" t="n"/>
       <c r="G130" s="54" t="n">
-        <v>1900</v>
+        <v>1700</v>
       </c>
       <c r="H130" s="46" t="n"/>
       <c r="I130" s="39" t="n">
-        <v>0.05</v>
+        <v>0.0556</v>
       </c>
       <c r="J130" s="39" t="n">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="K130" s="39" t="n">
         <v>1.1</v>
       </c>
       <c r="L130" s="40" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="M130" s="40" t="n">
         <v>0.15</v>
@@ -25614,23 +25639,23 @@
       </c>
       <c r="F131" s="46" t="n"/>
       <c r="G131" s="54" t="n">
-        <v>1500</v>
+        <v>1900</v>
       </c>
       <c r="H131" s="46" t="n"/>
       <c r="I131" s="45" t="n">
-        <v>0.0625</v>
+        <v>0.05</v>
       </c>
       <c r="J131" s="45" t="n">
-        <v>0.38</v>
+        <v>0.3</v>
       </c>
       <c r="K131" s="45" t="n">
         <v>0</v>
       </c>
       <c r="L131" s="40" t="n">
-        <v>0.38</v>
+        <v>0.3</v>
       </c>
       <c r="M131" s="40" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N131" s="41" t="n">
         <v>0</v>
@@ -25894,13 +25919,13 @@
         <v>0.33</v>
       </c>
       <c r="K137" s="39" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="L137" s="40" t="n">
-        <v>0.33</v>
+        <v>1.28</v>
       </c>
       <c r="M137" s="40" t="n">
-        <v>0.08</v>
+        <v>0.31</v>
       </c>
       <c r="N137" s="41" t="n">
         <v>0</v>
@@ -25930,23 +25955,23 @@
       </c>
       <c r="F138" s="53" t="n"/>
       <c r="G138" s="55" t="n">
-        <v>3500</v>
+        <v>3000</v>
       </c>
       <c r="H138" s="53" t="n"/>
       <c r="I138" s="40" t="n">
-        <v>0.0278</v>
+        <v>0.0323</v>
       </c>
       <c r="J138" s="40" t="n">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="K138" s="40" t="n">
         <v>0</v>
       </c>
       <c r="L138" s="40" t="n">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="M138" s="40" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="N138" s="41" t="n">
         <v>0</v>
@@ -26109,23 +26134,23 @@
       </c>
       <c r="F142" s="53" t="n"/>
       <c r="G142" s="55" t="n">
-        <v>1800</v>
+        <v>2000</v>
       </c>
       <c r="H142" s="53" t="n"/>
       <c r="I142" s="40" t="n">
-        <v>0.0526</v>
+        <v>0.0476</v>
       </c>
       <c r="J142" s="40" t="n">
-        <v>0.32</v>
+        <v>0.29</v>
       </c>
       <c r="K142" s="40" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="L142" s="40" t="n">
-        <v>0.32</v>
+        <v>1.65</v>
       </c>
       <c r="M142" s="40" t="n">
-        <v>0.08</v>
+        <v>0.4</v>
       </c>
       <c r="N142" s="41" t="n">
         <v>0</v>
@@ -26289,20 +26314,20 @@
       </c>
       <c r="F146" s="53" t="n"/>
       <c r="G146" s="55" t="n">
-        <v>4000</v>
+        <v>3500</v>
       </c>
       <c r="H146" s="53" t="n"/>
       <c r="I146" s="40" t="n">
-        <v>0.0244</v>
+        <v>0.0278</v>
       </c>
       <c r="J146" s="40" t="n">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="K146" s="40" t="n">
         <v>0</v>
       </c>
       <c r="L146" s="40" t="n">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="M146" s="40" t="n">
         <v>0.04</v>
@@ -26647,23 +26672,23 @@
       </c>
       <c r="F154" s="53" t="n"/>
       <c r="G154" s="55" t="n">
-        <v>2800</v>
+        <v>2400</v>
       </c>
       <c r="H154" s="53" t="n"/>
       <c r="I154" s="40" t="n">
-        <v>0.0345</v>
+        <v>0.04</v>
       </c>
       <c r="J154" s="40" t="n">
-        <v>0.21</v>
+        <v>0.24</v>
       </c>
       <c r="K154" s="40" t="n">
         <v>0</v>
       </c>
       <c r="L154" s="40" t="n">
-        <v>0.21</v>
+        <v>0.24</v>
       </c>
       <c r="M154" s="40" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="N154" s="41" t="n">
         <v>0</v>
@@ -26693,23 +26718,23 @@
       </c>
       <c r="F155" s="53" t="n"/>
       <c r="G155" s="55" t="n">
-        <v>850</v>
+        <v>900</v>
       </c>
       <c r="H155" s="53" t="n"/>
       <c r="I155" s="40" t="n">
-        <v>0.1053</v>
+        <v>0.1</v>
       </c>
       <c r="J155" s="40" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="K155" s="40" t="n">
         <v>4.5</v>
       </c>
       <c r="L155" s="40" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="M155" s="40" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="N155" s="41" t="n">
         <v>0</v>
@@ -26739,23 +26764,23 @@
       </c>
       <c r="F156" s="53" t="n"/>
       <c r="G156" s="55" t="n">
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="H156" s="53" t="n"/>
       <c r="I156" s="40" t="n">
-        <v>0.0769</v>
+        <v>0.0625</v>
       </c>
       <c r="J156" s="40" t="n">
-        <v>0.46</v>
+        <v>0.38</v>
       </c>
       <c r="K156" s="40" t="n">
         <v>0</v>
       </c>
       <c r="L156" s="40" t="n">
-        <v>0.46</v>
+        <v>0.38</v>
       </c>
       <c r="M156" s="40" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="N156" s="41" t="n">
         <v>0</v>
@@ -26874,28 +26899,28 @@
         <v>5100</v>
       </c>
       <c r="F159" s="40" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="G159" s="55" t="n">
-        <v>775</v>
+        <v>900</v>
       </c>
       <c r="H159" s="40" t="n">
         <v>1.5</v>
       </c>
       <c r="I159" s="40" t="n">
-        <v>0.1143</v>
+        <v>0.1</v>
       </c>
       <c r="J159" s="40" t="n">
-        <v>2.29</v>
+        <v>2.15</v>
       </c>
       <c r="K159" s="40" t="n">
         <v>1.6</v>
       </c>
       <c r="L159" s="40" t="n">
-        <v>2.01</v>
+        <v>1.93</v>
       </c>
       <c r="M159" s="40" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="N159" s="41" t="n">
         <v>0</v>
@@ -28598,13 +28623,13 @@
         <v>0</v>
       </c>
       <c r="K197" s="40" t="n">
-        <v>1.7</v>
+        <v>3.4</v>
       </c>
       <c r="L197" s="40" t="n">
-        <v>1.7</v>
+        <v>3.4</v>
       </c>
       <c r="M197" s="40" t="n">
-        <v>0.42</v>
+        <v>0.85</v>
       </c>
       <c r="N197" s="41" t="n">
         <v>0</v>
@@ -29084,28 +29109,28 @@
         <v>4000</v>
       </c>
       <c r="F208" s="40" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="G208" s="55" t="n">
-        <v>775</v>
+        <v>900</v>
       </c>
       <c r="H208" s="40" t="n">
         <v>1.5</v>
       </c>
       <c r="I208" s="40" t="n">
-        <v>0.1143</v>
+        <v>0.1</v>
       </c>
       <c r="J208" s="40" t="n">
-        <v>2.29</v>
+        <v>2.15</v>
       </c>
       <c r="K208" s="40" t="n">
         <v>1.6</v>
       </c>
       <c r="L208" s="40" t="n">
-        <v>2.01</v>
+        <v>1.93</v>
       </c>
       <c r="M208" s="40" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="N208" s="41" t="n">
         <v>0</v>
@@ -30396,23 +30421,23 @@
       </c>
       <c r="F237" s="53" t="n"/>
       <c r="G237" s="55" t="n">
-        <v>2800</v>
+        <v>2400</v>
       </c>
       <c r="H237" s="53" t="n"/>
       <c r="I237" s="40" t="n">
-        <v>0.0345</v>
+        <v>0.04</v>
       </c>
       <c r="J237" s="40" t="n">
-        <v>0.21</v>
+        <v>0.24</v>
       </c>
       <c r="K237" s="40" t="n">
         <v>0</v>
       </c>
       <c r="L237" s="40" t="n">
-        <v>0.21</v>
+        <v>0.24</v>
       </c>
       <c r="M237" s="40" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="N237" s="41" t="n">
         <v>0</v>
@@ -31052,23 +31077,23 @@
       </c>
       <c r="F252" s="53" t="n"/>
       <c r="G252" s="55" t="n">
-        <v>825</v>
+        <v>900</v>
       </c>
       <c r="H252" s="53" t="n"/>
       <c r="I252" s="40" t="n">
-        <v>0.1081</v>
+        <v>0.1</v>
       </c>
       <c r="J252" s="40" t="n">
-        <v>0.65</v>
+        <v>0.6</v>
       </c>
       <c r="K252" s="40" t="n">
         <v>5.2</v>
       </c>
       <c r="L252" s="40" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="M252" s="40" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="N252" s="41" t="n">
         <v>0</v>
@@ -31213,31 +31238,31 @@
         <v>8000</v>
       </c>
       <c r="F5" s="38" t="n">
-        <v>71.5</v>
+        <v>70.5</v>
       </c>
       <c r="G5" s="54" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="H5" s="38" t="n">
         <v>6.5</v>
       </c>
       <c r="I5" s="39" t="n">
-        <v>0.4167</v>
+        <v>0.4762</v>
       </c>
       <c r="J5" s="39" t="n">
-        <v>12.9</v>
+        <v>13.16</v>
       </c>
       <c r="K5" s="39" t="n">
         <v>17.1</v>
       </c>
       <c r="L5" s="40" t="n">
-        <v>14.58</v>
+        <v>14.73</v>
       </c>
       <c r="M5" s="40" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="N5" s="41" t="n">
-        <v>0.0785</v>
+        <v>0.07920000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -31263,31 +31288,31 @@
         <v>5500</v>
       </c>
       <c r="F6" s="38" t="n">
-        <v>50.5</v>
+        <v>52.5</v>
       </c>
       <c r="G6" s="54" t="n">
-        <v>270</v>
+        <v>245</v>
       </c>
       <c r="H6" s="38" t="n">
         <v>5.5</v>
       </c>
       <c r="I6" s="39" t="n">
-        <v>0.2703</v>
+        <v>0.2899</v>
       </c>
       <c r="J6" s="39" t="n">
-        <v>9.42</v>
+        <v>9.74</v>
       </c>
       <c r="K6" s="39" t="n">
         <v>13</v>
       </c>
       <c r="L6" s="40" t="n">
-        <v>10.85</v>
+        <v>11.04</v>
       </c>
       <c r="M6" s="40" t="n">
-        <v>1.97</v>
+        <v>2.01</v>
       </c>
       <c r="N6" s="41" t="n">
-        <v>0.0485</v>
+        <v>0.0503</v>
       </c>
     </row>
     <row r="7">
@@ -31359,7 +31384,7 @@
         <v>7200</v>
       </c>
       <c r="F8" s="38" t="n">
-        <v>64.5</v>
+        <v>62.5</v>
       </c>
       <c r="G8" s="54" t="n">
         <v>155</v>
@@ -31371,19 +31396,19 @@
         <v>0.3922</v>
       </c>
       <c r="J8" s="39" t="n">
-        <v>12.55</v>
+        <v>12.35</v>
       </c>
       <c r="K8" s="39" t="n">
         <v>14</v>
       </c>
       <c r="L8" s="40" t="n">
-        <v>13.13</v>
+        <v>13.01</v>
       </c>
       <c r="M8" s="40" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="N8" s="41" t="n">
-        <v>0.0643</v>
+        <v>0.0609</v>
       </c>
     </row>
     <row r="9">
@@ -31409,31 +31434,31 @@
         <v>6500</v>
       </c>
       <c r="F9" s="38" t="n">
-        <v>70</v>
+        <v>70.5</v>
       </c>
       <c r="G9" s="54" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="H9" s="38" t="n">
         <v>5.5</v>
       </c>
       <c r="I9" s="45" t="n">
-        <v>0.4167</v>
+        <v>0.4545</v>
       </c>
       <c r="J9" s="45" t="n">
-        <v>12.25</v>
+        <v>12.53</v>
       </c>
       <c r="K9" s="45" t="n">
         <v>15.6</v>
       </c>
       <c r="L9" s="40" t="n">
-        <v>13.59</v>
+        <v>13.76</v>
       </c>
       <c r="M9" s="40" t="n">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="N9" s="41" t="n">
-        <v>0.082</v>
+        <v>0.0834</v>
       </c>
     </row>
     <row r="10">
@@ -31483,7 +31508,7 @@
         <v>1.79</v>
       </c>
       <c r="N10" s="41" t="n">
-        <v>0.0377</v>
+        <v>0.0368</v>
       </c>
     </row>
     <row r="11">
@@ -31512,28 +31537,28 @@
         <v>22.5</v>
       </c>
       <c r="G11" s="54" t="n">
-        <v>390</v>
+        <v>360</v>
       </c>
       <c r="H11" s="38" t="n">
         <v>2.5</v>
       </c>
       <c r="I11" s="45" t="n">
-        <v>0.2041</v>
+        <v>0.2174</v>
       </c>
       <c r="J11" s="45" t="n">
-        <v>4.72</v>
+        <v>4.8</v>
       </c>
       <c r="K11" s="45" t="n">
         <v>6.4</v>
       </c>
       <c r="L11" s="40" t="n">
-        <v>5.39</v>
+        <v>5.44</v>
       </c>
       <c r="M11" s="40" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N11" s="41" t="n">
-        <v>0.0035</v>
+        <v>0.0036</v>
       </c>
     </row>
     <row r="12">
@@ -31559,27 +31584,25 @@
         <v>5400</v>
       </c>
       <c r="F12" s="38" t="n"/>
-      <c r="G12" s="54" t="n">
-        <v>295</v>
-      </c>
+      <c r="G12" s="54" t="n"/>
       <c r="H12" s="38" t="n"/>
       <c r="I12" s="45" t="n">
         <v>0.2532</v>
       </c>
       <c r="J12" s="45" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="K12" s="45" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="40" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="M12" s="40" t="n">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="N12" s="41" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="13">
@@ -31629,7 +31652,7 @@
         <v>1.62</v>
       </c>
       <c r="N13" s="41" t="n">
-        <v>0.0205</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="14">
@@ -31658,28 +31681,28 @@
         <v>30.5</v>
       </c>
       <c r="G14" s="54" t="n">
-        <v>370</v>
+        <v>330</v>
       </c>
       <c r="H14" s="38" t="n">
         <v>3.5</v>
       </c>
       <c r="I14" s="45" t="n">
-        <v>0.2128</v>
+        <v>0.2326</v>
       </c>
       <c r="J14" s="45" t="n">
-        <v>6.08</v>
+        <v>6.2</v>
       </c>
       <c r="K14" s="45" t="n">
         <v>7.4</v>
       </c>
       <c r="L14" s="40" t="n">
-        <v>6.61</v>
+        <v>6.68</v>
       </c>
       <c r="M14" s="40" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="N14" s="41" t="n">
-        <v>0.0092</v>
+        <v>0.0094</v>
       </c>
     </row>
     <row r="15">
@@ -31706,26 +31729,26 @@
       </c>
       <c r="F15" s="38" t="n"/>
       <c r="G15" s="54" t="n">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="H15" s="38" t="n"/>
       <c r="I15" s="39" t="n">
-        <v>0.3077</v>
+        <v>0.2985</v>
       </c>
       <c r="J15" s="39" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="K15" s="39" t="n">
-        <v>6.5</v>
+        <v>7.4</v>
       </c>
       <c r="L15" s="40" t="n">
-        <v>3.71</v>
+        <v>4.03</v>
       </c>
       <c r="M15" s="40" t="n">
-        <v>0.76</v>
+        <v>0.82</v>
       </c>
       <c r="N15" s="41" t="n">
-        <v>0.0004</v>
+        <v>0.0007</v>
       </c>
     </row>
     <row r="16">
@@ -31751,31 +31774,31 @@
         <v>5300</v>
       </c>
       <c r="F16" s="38" t="n">
-        <v>31.5</v>
+        <v>26.5</v>
       </c>
       <c r="G16" s="54" t="n">
-        <v>240</v>
+        <v>270</v>
       </c>
       <c r="H16" s="38" t="n">
         <v>3.5</v>
       </c>
       <c r="I16" s="39" t="n">
-        <v>0.2941</v>
+        <v>0.2703</v>
       </c>
       <c r="J16" s="39" t="n">
-        <v>6.66</v>
+        <v>6.02</v>
       </c>
       <c r="K16" s="39" t="n">
         <v>7.6</v>
       </c>
       <c r="L16" s="40" t="n">
-        <v>7.04</v>
+        <v>6.65</v>
       </c>
       <c r="M16" s="40" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="N16" s="41" t="n">
-        <v>0.0107</v>
+        <v>0.0083</v>
       </c>
     </row>
     <row r="17">
@@ -31801,31 +31824,31 @@
         <v>5400</v>
       </c>
       <c r="F17" s="38" t="n">
-        <v>30.5</v>
+        <v>28.5</v>
       </c>
       <c r="G17" s="54" t="n">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="H17" s="38" t="n">
         <v>3.5</v>
       </c>
       <c r="I17" s="45" t="n">
-        <v>0.2899</v>
+        <v>0.2941</v>
       </c>
       <c r="J17" s="45" t="n">
-        <v>6.54</v>
+        <v>6.36</v>
       </c>
       <c r="K17" s="45" t="n">
         <v>7.4</v>
       </c>
       <c r="L17" s="40" t="n">
-        <v>6.88</v>
+        <v>6.78</v>
       </c>
       <c r="M17" s="40" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="N17" s="41" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.008800000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -31854,28 +31877,28 @@
         <v>49.5</v>
       </c>
       <c r="G18" s="54" t="n">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="H18" s="38" t="n">
         <v>4.5</v>
       </c>
       <c r="I18" s="39" t="n">
-        <v>0.3636</v>
+        <v>0.3571</v>
       </c>
       <c r="J18" s="39" t="n">
-        <v>9.380000000000001</v>
+        <v>9.34</v>
       </c>
       <c r="K18" s="39" t="n">
         <v>11</v>
       </c>
       <c r="L18" s="40" t="n">
-        <v>10.03</v>
+        <v>10.01</v>
       </c>
       <c r="M18" s="40" t="n">
         <v>1.82</v>
       </c>
       <c r="N18" s="41" t="n">
-        <v>0.0371</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="19">
@@ -31904,28 +31927,28 @@
         <v>34.5</v>
       </c>
       <c r="G19" s="54" t="n">
-        <v>290</v>
+        <v>310</v>
       </c>
       <c r="H19" s="38" t="n">
         <v>3.5</v>
       </c>
       <c r="I19" s="45" t="n">
-        <v>0.2564</v>
+        <v>0.2439</v>
       </c>
       <c r="J19" s="45" t="n">
-        <v>6.74</v>
+        <v>6.66</v>
       </c>
       <c r="K19" s="45" t="n">
         <v>8.9</v>
       </c>
       <c r="L19" s="40" t="n">
-        <v>7.6</v>
+        <v>7.56</v>
       </c>
       <c r="M19" s="40" t="n">
         <v>1.43</v>
       </c>
       <c r="N19" s="41" t="n">
-        <v>0.0144</v>
+        <v>0.0138</v>
       </c>
     </row>
     <row r="20">
@@ -31995,31 +32018,31 @@
         <v>5300</v>
       </c>
       <c r="F21" s="38" t="n">
-        <v>20.5</v>
+        <v>22.5</v>
       </c>
       <c r="G21" s="54" t="n">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="H21" s="38" t="n">
         <v>2.5</v>
       </c>
       <c r="I21" s="45" t="n">
-        <v>0.2326</v>
+        <v>0.2381</v>
       </c>
       <c r="J21" s="45" t="n">
-        <v>4.7</v>
+        <v>4.93</v>
       </c>
       <c r="K21" s="45" t="n">
         <v>5.3</v>
       </c>
       <c r="L21" s="40" t="n">
-        <v>4.94</v>
+        <v>5.08</v>
       </c>
       <c r="M21" s="40" t="n">
-        <v>0.93</v>
+        <v>0.96</v>
       </c>
       <c r="N21" s="41" t="n">
-        <v>0.0023</v>
+        <v>0.0025</v>
       </c>
     </row>
     <row r="22">
@@ -32048,28 +32071,28 @@
         <v>16.5</v>
       </c>
       <c r="G22" s="54" t="n">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="H22" s="38" t="n">
         <v>1.5</v>
       </c>
       <c r="I22" s="39" t="n">
-        <v>0.2273</v>
+        <v>0.2381</v>
       </c>
       <c r="J22" s="39" t="n">
-        <v>3.76</v>
+        <v>3.83</v>
       </c>
       <c r="K22" s="39" t="n">
         <v>4.4</v>
       </c>
       <c r="L22" s="40" t="n">
-        <v>4.02</v>
+        <v>4.06</v>
       </c>
       <c r="M22" s="40" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="N22" s="41" t="n">
-        <v>0.0008</v>
+        <v>0.0009</v>
       </c>
     </row>
     <row r="23">
@@ -32095,31 +32118,31 @@
         <v>5000</v>
       </c>
       <c r="F23" s="38" t="n">
-        <v>21.5</v>
+        <v>18.5</v>
       </c>
       <c r="G23" s="54" t="n">
-        <v>425</v>
+        <v>410</v>
       </c>
       <c r="H23" s="38" t="n">
         <v>2.5</v>
       </c>
       <c r="I23" s="45" t="n">
-        <v>0.1905</v>
+        <v>0.1961</v>
       </c>
       <c r="J23" s="45" t="n">
-        <v>4.54</v>
+        <v>4.28</v>
       </c>
       <c r="K23" s="45" t="n">
         <v>4.7</v>
       </c>
       <c r="L23" s="40" t="n">
-        <v>4.61</v>
+        <v>4.45</v>
       </c>
       <c r="M23" s="40" t="n">
-        <v>0.92</v>
+        <v>0.89</v>
       </c>
       <c r="N23" s="41" t="n">
-        <v>0.0017</v>
+        <v>0.0013</v>
       </c>
     </row>
     <row r="24">
@@ -32146,26 +32169,26 @@
       </c>
       <c r="F24" s="46" t="n"/>
       <c r="G24" s="54" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="H24" s="46" t="n"/>
       <c r="I24" s="39" t="n">
-        <v>0.2941</v>
+        <v>0.2899</v>
       </c>
       <c r="J24" s="39" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="K24" s="39" t="n">
-        <v>7.1</v>
+        <v>7.9</v>
       </c>
       <c r="L24" s="40" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="M24" s="40" t="n">
-        <v>0.75</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="N24" s="41" t="n">
-        <v>0.0005</v>
+        <v>0.0009</v>
       </c>
     </row>
     <row r="25">
@@ -32191,31 +32214,31 @@
         <v>4900</v>
       </c>
       <c r="F25" s="38" t="n">
-        <v>21</v>
+        <v>21.5</v>
       </c>
       <c r="G25" s="54" t="n">
-        <v>500</v>
+        <v>475</v>
       </c>
       <c r="H25" s="38" t="n">
         <v>2.5</v>
       </c>
       <c r="I25" s="45" t="n">
-        <v>0.1667</v>
+        <v>0.1739</v>
       </c>
       <c r="J25" s="45" t="n">
-        <v>4.35</v>
+        <v>4.44</v>
       </c>
       <c r="K25" s="45" t="n">
         <v>5.1</v>
       </c>
       <c r="L25" s="40" t="n">
-        <v>4.65</v>
+        <v>4.71</v>
       </c>
       <c r="M25" s="40" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="N25" s="41" t="n">
-        <v>0.0018</v>
+        <v>0.0019</v>
       </c>
     </row>
     <row r="26">
@@ -32294,13 +32317,13 @@
         <v>0</v>
       </c>
       <c r="K27" s="45" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="L27" s="40" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="M27" s="40" t="n">
-        <v>0.68</v>
+        <v>0.75</v>
       </c>
       <c r="N27" s="41" t="n">
         <v>0</v>
@@ -32332,25 +32355,25 @@
         <v>8.5</v>
       </c>
       <c r="G28" s="54" t="n">
-        <v>575</v>
+        <v>650</v>
       </c>
       <c r="H28" s="38" t="n">
         <v>1.5</v>
       </c>
       <c r="I28" s="45" t="n">
-        <v>0.1481</v>
+        <v>0.1333</v>
       </c>
       <c r="J28" s="45" t="n">
-        <v>2.49</v>
+        <v>2.4</v>
       </c>
       <c r="K28" s="45" t="n">
         <v>3.5</v>
       </c>
       <c r="L28" s="40" t="n">
-        <v>2.89</v>
+        <v>2.84</v>
       </c>
       <c r="M28" s="40" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="N28" s="41" t="n">
         <v>0</v>
@@ -32475,31 +32498,31 @@
         <v>4900</v>
       </c>
       <c r="F31" s="38" t="n">
-        <v>39.5</v>
+        <v>40.5</v>
       </c>
       <c r="G31" s="54" t="n">
-        <v>290</v>
+        <v>260</v>
       </c>
       <c r="H31" s="38" t="n">
         <v>3.5</v>
       </c>
       <c r="I31" s="39" t="n">
-        <v>0.2564</v>
+        <v>0.2778</v>
       </c>
       <c r="J31" s="39" t="n">
-        <v>7.24</v>
+        <v>7.47</v>
       </c>
       <c r="K31" s="39" t="n">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="L31" s="40" t="n">
-        <v>7.02</v>
+        <v>7.28</v>
       </c>
       <c r="M31" s="40" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="N31" s="41" t="n">
-        <v>0.0117</v>
+        <v>0.0132</v>
       </c>
     </row>
     <row r="32">
@@ -32526,23 +32549,23 @@
       </c>
       <c r="F32" s="46" t="n"/>
       <c r="G32" s="54" t="n">
-        <v>1200</v>
+        <v>1150</v>
       </c>
       <c r="H32" s="46" t="n"/>
       <c r="I32" s="45" t="n">
-        <v>0.0769</v>
+        <v>0.08</v>
       </c>
       <c r="J32" s="45" t="n">
-        <v>0.46</v>
+        <v>0.48</v>
       </c>
       <c r="K32" s="45" t="n">
         <v>1.5</v>
       </c>
       <c r="L32" s="40" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="M32" s="40" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="N32" s="41" t="n">
         <v>0</v>
@@ -32572,23 +32595,23 @@
       </c>
       <c r="F33" s="38" t="n"/>
       <c r="G33" s="54" t="n">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="H33" s="38" t="n"/>
       <c r="I33" s="39" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.0769</v>
       </c>
       <c r="J33" s="39" t="n">
-        <v>0.55</v>
+        <v>0.46</v>
       </c>
       <c r="K33" s="39" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="L33" s="40" t="n">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
       <c r="M33" s="40" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="N33" s="41" t="n">
         <v>0</v>
@@ -32641,7 +32664,7 @@
         <v>0.97</v>
       </c>
       <c r="N34" s="41" t="n">
-        <v>0.0022</v>
+        <v>0.0021</v>
       </c>
     </row>
     <row r="35">
@@ -32668,23 +32691,23 @@
       </c>
       <c r="F35" s="38" t="n"/>
       <c r="G35" s="54" t="n">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="H35" s="38" t="n"/>
       <c r="I35" s="45" t="n">
-        <v>0.125</v>
+        <v>0.1</v>
       </c>
       <c r="J35" s="45" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="K35" s="45" t="n">
         <v>2.5</v>
       </c>
       <c r="L35" s="40" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="M35" s="40" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="N35" s="41" t="n">
         <v>0</v>
@@ -32803,7 +32826,7 @@
         <v>4600</v>
       </c>
       <c r="F38" s="38" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="G38" s="54" t="n">
         <v>1200</v>
@@ -32815,16 +32838,16 @@
         <v>0.0769</v>
       </c>
       <c r="J38" s="39" t="n">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="K38" s="39" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="L38" s="40" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="M38" s="40" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="N38" s="41" t="n">
         <v>0</v>
@@ -32944,26 +32967,26 @@
       </c>
       <c r="F41" s="38" t="n"/>
       <c r="G41" s="54" t="n">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="H41" s="38" t="n"/>
       <c r="I41" s="45" t="n">
-        <v>0.2899</v>
+        <v>0.2817</v>
       </c>
       <c r="J41" s="45" t="n">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="K41" s="45" t="n">
-        <v>7.4</v>
+        <v>8.5</v>
       </c>
       <c r="L41" s="40" t="n">
-        <v>4</v>
+        <v>4.41</v>
       </c>
       <c r="M41" s="40" t="n">
-        <v>0.78</v>
+        <v>0.87</v>
       </c>
       <c r="N41" s="41" t="n">
-        <v>0.0007</v>
+        <v>0.0012</v>
       </c>
     </row>
     <row r="42">
@@ -32988,28 +33011,32 @@
       <c r="E42" s="37" t="n">
         <v>4000</v>
       </c>
-      <c r="F42" s="38" t="n"/>
+      <c r="F42" s="38" t="n">
+        <v>18.5</v>
+      </c>
       <c r="G42" s="54" t="n">
-        <v>1100</v>
-      </c>
-      <c r="H42" s="38" t="n"/>
+        <v>700</v>
+      </c>
+      <c r="H42" s="38" t="n">
+        <v>1.5</v>
+      </c>
       <c r="I42" s="39" t="n">
-        <v>0.0833</v>
+        <v>0.125</v>
       </c>
       <c r="J42" s="39" t="n">
-        <v>0.5</v>
+        <v>3.35</v>
       </c>
       <c r="K42" s="39" t="n">
         <v>6.8</v>
       </c>
       <c r="L42" s="40" t="n">
-        <v>3.02</v>
+        <v>4.73</v>
       </c>
       <c r="M42" s="40" t="n">
-        <v>0.76</v>
+        <v>1.18</v>
       </c>
       <c r="N42" s="41" t="n">
-        <v>0</v>
+        <v>0.0025</v>
       </c>
     </row>
     <row r="43">
@@ -33036,23 +33063,23 @@
       </c>
       <c r="F43" s="46" t="n"/>
       <c r="G43" s="54" t="n">
-        <v>1000</v>
+        <v>850</v>
       </c>
       <c r="H43" s="46" t="n"/>
       <c r="I43" s="45" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.1053</v>
       </c>
       <c r="J43" s="45" t="n">
-        <v>0.55</v>
+        <v>0.63</v>
       </c>
       <c r="K43" s="45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L43" s="40" t="n">
-        <v>1.53</v>
+        <v>0.63</v>
       </c>
       <c r="M43" s="40" t="n">
-        <v>0.34</v>
+        <v>0.14</v>
       </c>
       <c r="N43" s="41" t="n">
         <v>0</v>
@@ -33081,7 +33108,7 @@
         <v>4700</v>
       </c>
       <c r="F44" s="38" t="n">
-        <v>20.5</v>
+        <v>21.5</v>
       </c>
       <c r="G44" s="54" t="n">
         <v>450</v>
@@ -33093,19 +33120,19 @@
         <v>0.1818</v>
       </c>
       <c r="J44" s="45" t="n">
-        <v>4.39</v>
+        <v>4.49</v>
       </c>
       <c r="K44" s="45" t="n">
         <v>5</v>
       </c>
       <c r="L44" s="40" t="n">
-        <v>4.63</v>
+        <v>4.69</v>
       </c>
       <c r="M44" s="40" t="n">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="N44" s="41" t="n">
-        <v>0.0019</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="45">
@@ -33131,31 +33158,31 @@
         <v>4500</v>
       </c>
       <c r="F45" s="38" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="G45" s="54" t="n">
         <v>575</v>
       </c>
       <c r="H45" s="38" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="I45" s="39" t="n">
         <v>0.1481</v>
       </c>
       <c r="J45" s="39" t="n">
-        <v>3.04</v>
+        <v>3.24</v>
       </c>
       <c r="K45" s="39" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="L45" s="40" t="n">
-        <v>3.14</v>
+        <v>3.42</v>
       </c>
       <c r="M45" s="40" t="n">
-        <v>0.7</v>
+        <v>0.76</v>
       </c>
       <c r="N45" s="41" t="n">
-        <v>0</v>
+        <v>0.0002</v>
       </c>
     </row>
     <row r="46">
@@ -33182,23 +33209,23 @@
       </c>
       <c r="F46" s="46" t="n"/>
       <c r="G46" s="54" t="n">
-        <v>1800</v>
+        <v>1300</v>
       </c>
       <c r="H46" s="46" t="n"/>
       <c r="I46" s="39" t="n">
-        <v>0.0526</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="J46" s="39" t="n">
-        <v>0.32</v>
+        <v>0.43</v>
       </c>
       <c r="K46" s="39" t="n">
         <v>1.1</v>
       </c>
       <c r="L46" s="40" t="n">
-        <v>0.63</v>
+        <v>0.7</v>
       </c>
       <c r="M46" s="40" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="N46" s="41" t="n">
         <v>0</v>
@@ -33228,23 +33255,23 @@
       </c>
       <c r="F47" s="46" t="n"/>
       <c r="G47" s="54" t="n">
-        <v>1600</v>
+        <v>1200</v>
       </c>
       <c r="H47" s="46" t="n"/>
       <c r="I47" s="45" t="n">
-        <v>0.0588</v>
+        <v>0.0769</v>
       </c>
       <c r="J47" s="45" t="n">
-        <v>0.35</v>
+        <v>0.46</v>
       </c>
       <c r="K47" s="45" t="n">
         <v>1.3</v>
       </c>
       <c r="L47" s="40" t="n">
-        <v>0.73</v>
+        <v>0.8</v>
       </c>
       <c r="M47" s="40" t="n">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="N47" s="41" t="n">
         <v>0</v>
@@ -33318,23 +33345,23 @@
       </c>
       <c r="F49" s="46" t="n"/>
       <c r="G49" s="54" t="n">
-        <v>1300</v>
+        <v>1050</v>
       </c>
       <c r="H49" s="46" t="n"/>
       <c r="I49" s="45" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="J49" s="45" t="n">
-        <v>0.43</v>
+        <v>0.52</v>
       </c>
       <c r="K49" s="45" t="n">
         <v>0</v>
       </c>
       <c r="L49" s="40" t="n">
-        <v>0.43</v>
+        <v>0.52</v>
       </c>
       <c r="M49" s="40" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="N49" s="41" t="n">
         <v>0</v>
@@ -33364,23 +33391,23 @@
       </c>
       <c r="F50" s="46" t="n"/>
       <c r="G50" s="54" t="n">
-        <v>800</v>
+        <v>850</v>
       </c>
       <c r="H50" s="46" t="n"/>
       <c r="I50" s="39" t="n">
-        <v>0.1111</v>
+        <v>0.1053</v>
       </c>
       <c r="J50" s="39" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="K50" s="39" t="n">
         <v>1.5</v>
       </c>
       <c r="L50" s="40" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="M50" s="40" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="N50" s="41" t="n">
         <v>0</v>
@@ -33465,13 +33492,13 @@
         <v>0.55</v>
       </c>
       <c r="K52" s="40" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="L52" s="40" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="M52" s="40" t="n">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="N52" s="41" t="n">
         <v>0</v>
@@ -33592,23 +33619,23 @@
       </c>
       <c r="F55" s="40" t="n"/>
       <c r="G55" s="55" t="n">
-        <v>525</v>
+        <v>700</v>
       </c>
       <c r="H55" s="40" t="n"/>
       <c r="I55" s="40" t="n">
-        <v>0.16</v>
+        <v>0.125</v>
       </c>
       <c r="J55" s="40" t="n">
-        <v>0.96</v>
+        <v>0.75</v>
       </c>
       <c r="K55" s="40" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="L55" s="40" t="n">
-        <v>1.26</v>
+        <v>1.41</v>
       </c>
       <c r="M55" s="40" t="n">
-        <v>0.3</v>
+        <v>0.34</v>
       </c>
       <c r="N55" s="41" t="n">
         <v>0</v>
@@ -33684,23 +33711,23 @@
       </c>
       <c r="F57" s="53" t="n"/>
       <c r="G57" s="55" t="n">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="H57" s="53" t="n"/>
       <c r="I57" s="40" t="n">
-        <v>0.0323</v>
+        <v>0.0385</v>
       </c>
       <c r="J57" s="40" t="n">
-        <v>0.19</v>
+        <v>0.23</v>
       </c>
       <c r="K57" s="40" t="n">
         <v>1.4</v>
       </c>
       <c r="L57" s="40" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="M57" s="40" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="N57" s="41" t="n">
         <v>0</v>
@@ -33774,23 +33801,23 @@
       </c>
       <c r="F59" s="53" t="n"/>
       <c r="G59" s="55" t="n">
-        <v>2200</v>
+        <v>3300</v>
       </c>
       <c r="H59" s="53" t="n"/>
       <c r="I59" s="40" t="n">
-        <v>0.0435</v>
+        <v>0.0294</v>
       </c>
       <c r="J59" s="40" t="n">
-        <v>0.26</v>
+        <v>0.18</v>
       </c>
       <c r="K59" s="40" t="n">
         <v>1.1</v>
       </c>
       <c r="L59" s="40" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="M59" s="40" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="N59" s="41" t="n">
         <v>0</v>
@@ -33922,13 +33949,13 @@
         <v>0.46</v>
       </c>
       <c r="K62" s="40" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="L62" s="40" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="M62" s="40" t="n">
-        <v>0.26</v>
+        <v>0.29</v>
       </c>
       <c r="N62" s="41" t="n">
         <v>0</v>
@@ -34135,20 +34162,20 @@
       </c>
       <c r="F67" s="53" t="n"/>
       <c r="G67" s="55" t="n">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="H67" s="53" t="n"/>
       <c r="I67" s="40" t="n">
-        <v>0.0833</v>
+        <v>0.0769</v>
       </c>
       <c r="J67" s="40" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="K67" s="40" t="n">
         <v>1.7</v>
       </c>
       <c r="L67" s="40" t="n">
-        <v>0.98</v>
+        <v>0.96</v>
       </c>
       <c r="M67" s="40" t="n">
         <v>0.22</v>
@@ -34179,25 +34206,29 @@
       <c r="E68" s="52" t="n">
         <v>4300</v>
       </c>
-      <c r="F68" s="53" t="n"/>
+      <c r="F68" s="40" t="n">
+        <v>1.5</v>
+      </c>
       <c r="G68" s="55" t="n">
         <v>1150</v>
       </c>
-      <c r="H68" s="53" t="n"/>
+      <c r="H68" s="40" t="n">
+        <v>0.5</v>
+      </c>
       <c r="I68" s="40" t="n">
         <v>0.08</v>
       </c>
       <c r="J68" s="40" t="n">
-        <v>0.48</v>
+        <v>0.88</v>
       </c>
       <c r="K68" s="40" t="n">
         <v>0</v>
       </c>
       <c r="L68" s="40" t="n">
-        <v>0.48</v>
+        <v>0.88</v>
       </c>
       <c r="M68" s="40" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="N68" s="41" t="n">
         <v>0</v>
@@ -34227,23 +34258,23 @@
       </c>
       <c r="F69" s="53" t="n"/>
       <c r="G69" s="55" t="n">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="H69" s="53" t="n"/>
       <c r="I69" s="40" t="n">
-        <v>0.0833</v>
+        <v>0.0769</v>
       </c>
       <c r="J69" s="40" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="K69" s="40" t="n">
         <v>0</v>
       </c>
       <c r="L69" s="40" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="M69" s="40" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="N69" s="41" t="n">
         <v>0</v>
@@ -34273,23 +34304,23 @@
       </c>
       <c r="F70" s="53" t="n"/>
       <c r="G70" s="55" t="n">
-        <v>1300</v>
+        <v>1000</v>
       </c>
       <c r="H70" s="53" t="n"/>
       <c r="I70" s="40" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="J70" s="40" t="n">
-        <v>0.43</v>
+        <v>0.55</v>
       </c>
       <c r="K70" s="40" t="n">
         <v>1.5</v>
       </c>
       <c r="L70" s="40" t="n">
-        <v>0.86</v>
+        <v>0.93</v>
       </c>
       <c r="M70" s="40" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="N70" s="41" t="n">
         <v>0</v>
@@ -34365,23 +34396,23 @@
       </c>
       <c r="F72" s="53" t="n"/>
       <c r="G72" s="55" t="n">
-        <v>2500</v>
+        <v>2200</v>
       </c>
       <c r="H72" s="53" t="n"/>
       <c r="I72" s="40" t="n">
-        <v>0.0385</v>
+        <v>0.0435</v>
       </c>
       <c r="J72" s="40" t="n">
-        <v>0.23</v>
+        <v>0.26</v>
       </c>
       <c r="K72" s="40" t="n">
         <v>0</v>
       </c>
       <c r="L72" s="40" t="n">
-        <v>0.23</v>
+        <v>0.26</v>
       </c>
       <c r="M72" s="40" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N72" s="41" t="n">
         <v>0</v>
@@ -34411,23 +34442,23 @@
       </c>
       <c r="F73" s="53" t="n"/>
       <c r="G73" s="55" t="n">
-        <v>2200</v>
+        <v>2000</v>
       </c>
       <c r="H73" s="53" t="n"/>
       <c r="I73" s="40" t="n">
-        <v>0.0435</v>
+        <v>0.0476</v>
       </c>
       <c r="J73" s="40" t="n">
-        <v>0.26</v>
+        <v>0.29</v>
       </c>
       <c r="K73" s="40" t="n">
         <v>0</v>
       </c>
       <c r="L73" s="40" t="n">
-        <v>0.26</v>
+        <v>0.29</v>
       </c>
       <c r="M73" s="40" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N73" s="41" t="n">
         <v>0</v>
@@ -34457,23 +34488,23 @@
       </c>
       <c r="F74" s="53" t="n"/>
       <c r="G74" s="55" t="n">
-        <v>1500</v>
+        <v>1700</v>
       </c>
       <c r="H74" s="53" t="n"/>
       <c r="I74" s="40" t="n">
-        <v>0.0625</v>
+        <v>0.0556</v>
       </c>
       <c r="J74" s="40" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="K74" s="40" t="n">
         <v>0</v>
       </c>
       <c r="L74" s="40" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="M74" s="40" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="N74" s="41" t="n">
         <v>0</v>
@@ -34547,23 +34578,23 @@
       </c>
       <c r="F76" s="53" t="n"/>
       <c r="G76" s="55" t="n">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="H76" s="53" t="n"/>
       <c r="I76" s="40" t="n">
-        <v>0.0625</v>
+        <v>0.0667</v>
       </c>
       <c r="J76" s="40" t="n">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="K76" s="40" t="n">
         <v>0</v>
       </c>
       <c r="L76" s="40" t="n">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="M76" s="40" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="N76" s="41" t="n">
         <v>0</v>
@@ -34637,23 +34668,23 @@
       </c>
       <c r="F78" s="53" t="n"/>
       <c r="G78" s="55" t="n">
-        <v>1150</v>
+        <v>1400</v>
       </c>
       <c r="H78" s="53" t="n"/>
       <c r="I78" s="40" t="n">
-        <v>0.08</v>
+        <v>0.0667</v>
       </c>
       <c r="J78" s="40" t="n">
-        <v>0.48</v>
+        <v>0.4</v>
       </c>
       <c r="K78" s="40" t="n">
         <v>0</v>
       </c>
       <c r="L78" s="40" t="n">
-        <v>0.48</v>
+        <v>0.4</v>
       </c>
       <c r="M78" s="40" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="N78" s="41" t="n">
         <v>0</v>
@@ -34729,20 +34760,20 @@
       </c>
       <c r="F80" s="53" t="n"/>
       <c r="G80" s="55" t="n">
-        <v>5500</v>
+        <v>4500</v>
       </c>
       <c r="H80" s="53" t="n"/>
       <c r="I80" s="40" t="n">
-        <v>0.0179</v>
+        <v>0.0217</v>
       </c>
       <c r="J80" s="40" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="K80" s="40" t="n">
         <v>0</v>
       </c>
       <c r="L80" s="40" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="M80" s="40" t="n">
         <v>0.03</v>
@@ -34775,23 +34806,23 @@
       </c>
       <c r="F81" s="53" t="n"/>
       <c r="G81" s="55" t="n">
-        <v>1600</v>
+        <v>2000</v>
       </c>
       <c r="H81" s="53" t="n"/>
       <c r="I81" s="40" t="n">
-        <v>0.0588</v>
+        <v>0.0476</v>
       </c>
       <c r="J81" s="40" t="n">
-        <v>0.35</v>
+        <v>0.29</v>
       </c>
       <c r="K81" s="40" t="n">
         <v>0</v>
       </c>
       <c r="L81" s="40" t="n">
-        <v>0.35</v>
+        <v>0.29</v>
       </c>
       <c r="M81" s="40" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N81" s="41" t="n">
         <v>0</v>
@@ -34867,23 +34898,23 @@
       </c>
       <c r="F83" s="53" t="n"/>
       <c r="G83" s="55" t="n">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="H83" s="53" t="n"/>
       <c r="I83" s="40" t="n">
-        <v>0.0323</v>
+        <v>0.0244</v>
       </c>
       <c r="J83" s="40" t="n">
-        <v>0.19</v>
+        <v>0.15</v>
       </c>
       <c r="K83" s="40" t="n">
         <v>0</v>
       </c>
       <c r="L83" s="40" t="n">
-        <v>0.19</v>
+        <v>0.15</v>
       </c>
       <c r="M83" s="40" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="N83" s="41" t="n">
         <v>0</v>
@@ -34959,23 +34990,23 @@
       </c>
       <c r="F85" s="53" t="n"/>
       <c r="G85" s="55" t="n">
-        <v>1000</v>
+        <v>1700</v>
       </c>
       <c r="H85" s="53" t="n"/>
       <c r="I85" s="40" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.0556</v>
       </c>
       <c r="J85" s="40" t="n">
-        <v>0.55</v>
+        <v>0.33</v>
       </c>
       <c r="K85" s="40" t="n">
         <v>0</v>
       </c>
       <c r="L85" s="40" t="n">
-        <v>0.55</v>
+        <v>0.33</v>
       </c>
       <c r="M85" s="40" t="n">
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
       <c r="N85" s="41" t="n">
         <v>0</v>
@@ -35005,23 +35036,23 @@
       </c>
       <c r="F86" s="53" t="n"/>
       <c r="G86" s="55" t="n">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="H86" s="53" t="n"/>
       <c r="I86" s="40" t="n">
-        <v>0.0385</v>
+        <v>0.0476</v>
       </c>
       <c r="J86" s="40" t="n">
-        <v>0.23</v>
+        <v>0.29</v>
       </c>
       <c r="K86" s="40" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L86" s="40" t="n">
-        <v>0.23</v>
+        <v>0.77</v>
       </c>
       <c r="M86" s="40" t="n">
-        <v>0.06</v>
+        <v>0.19</v>
       </c>
       <c r="N86" s="41" t="n">
         <v>0</v>
@@ -35095,23 +35126,23 @@
       </c>
       <c r="F88" s="53" t="n"/>
       <c r="G88" s="55" t="n">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="H88" s="53" t="n"/>
       <c r="I88" s="40" t="n">
-        <v>0.0244</v>
+        <v>0.0323</v>
       </c>
       <c r="J88" s="40" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="K88" s="40" t="n">
         <v>0</v>
       </c>
       <c r="L88" s="40" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="M88" s="40" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="N88" s="41" t="n">
         <v>0</v>
@@ -35185,23 +35216,23 @@
       </c>
       <c r="F90" s="53" t="n"/>
       <c r="G90" s="55" t="n">
-        <v>3000</v>
+        <v>3300</v>
       </c>
       <c r="H90" s="53" t="n"/>
       <c r="I90" s="40" t="n">
-        <v>0.0323</v>
+        <v>0.0294</v>
       </c>
       <c r="J90" s="40" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="K90" s="40" t="n">
         <v>0</v>
       </c>
       <c r="L90" s="40" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="M90" s="40" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="N90" s="41" t="n">
         <v>0</v>
@@ -35321,23 +35352,23 @@
       </c>
       <c r="F93" s="53" t="n"/>
       <c r="G93" s="55" t="n">
-        <v>2200</v>
+        <v>2400</v>
       </c>
       <c r="H93" s="53" t="n"/>
       <c r="I93" s="40" t="n">
-        <v>0.0435</v>
+        <v>0.04</v>
       </c>
       <c r="J93" s="40" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="K93" s="40" t="n">
         <v>0</v>
       </c>
       <c r="L93" s="40" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="M93" s="40" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="N93" s="41" t="n">
         <v>0</v>
@@ -35367,23 +35398,23 @@
       </c>
       <c r="F94" s="53" t="n"/>
       <c r="G94" s="55" t="n">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="H94" s="53" t="n"/>
       <c r="I94" s="40" t="n">
-        <v>0.0278</v>
+        <v>0.0385</v>
       </c>
       <c r="J94" s="40" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="K94" s="40" t="n">
         <v>0</v>
       </c>
       <c r="L94" s="40" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="M94" s="40" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="N94" s="41" t="n">
         <v>0</v>
@@ -35502,20 +35533,20 @@
       </c>
       <c r="F97" s="53" t="n"/>
       <c r="G97" s="55" t="n">
-        <v>4000</v>
+        <v>3500</v>
       </c>
       <c r="H97" s="53" t="n"/>
       <c r="I97" s="40" t="n">
-        <v>0.0244</v>
+        <v>0.0278</v>
       </c>
       <c r="J97" s="40" t="n">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="K97" s="40" t="n">
         <v>0</v>
       </c>
       <c r="L97" s="40" t="n">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="M97" s="40" t="n">
         <v>0.04</v>
@@ -35548,23 +35579,23 @@
       </c>
       <c r="F98" s="53" t="n"/>
       <c r="G98" s="55" t="n">
-        <v>3500</v>
+        <v>2800</v>
       </c>
       <c r="H98" s="53" t="n"/>
       <c r="I98" s="40" t="n">
-        <v>0.0278</v>
+        <v>0.0345</v>
       </c>
       <c r="J98" s="40" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="K98" s="40" t="n">
         <v>0</v>
       </c>
       <c r="L98" s="40" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="M98" s="40" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="N98" s="41" t="n">
         <v>0</v>
@@ -35594,23 +35625,23 @@
       </c>
       <c r="F99" s="53" t="n"/>
       <c r="G99" s="55" t="n">
-        <v>4000</v>
+        <v>4500</v>
       </c>
       <c r="H99" s="53" t="n"/>
       <c r="I99" s="40" t="n">
-        <v>0.0244</v>
+        <v>0.0217</v>
       </c>
       <c r="J99" s="40" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="K99" s="40" t="n">
         <v>0</v>
       </c>
       <c r="L99" s="40" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="M99" s="40" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="N99" s="41" t="n">
         <v>0</v>
@@ -35775,23 +35806,23 @@
       </c>
       <c r="F103" s="53" t="n"/>
       <c r="G103" s="55" t="n">
-        <v>5000</v>
+        <v>3500</v>
       </c>
       <c r="H103" s="53" t="n"/>
       <c r="I103" s="40" t="n">
-        <v>0.0196</v>
+        <v>0.0278</v>
       </c>
       <c r="J103" s="40" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="K103" s="40" t="n">
         <v>0</v>
       </c>
       <c r="L103" s="40" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="M103" s="40" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="N103" s="41" t="n">
         <v>0</v>
@@ -35821,23 +35852,23 @@
       </c>
       <c r="F104" s="53" t="n"/>
       <c r="G104" s="55" t="n">
-        <v>1200</v>
+        <v>2500</v>
       </c>
       <c r="H104" s="53" t="n"/>
       <c r="I104" s="40" t="n">
-        <v>0.0769</v>
+        <v>0.0385</v>
       </c>
       <c r="J104" s="40" t="n">
-        <v>0.46</v>
+        <v>0.23</v>
       </c>
       <c r="K104" s="40" t="n">
         <v>0</v>
       </c>
       <c r="L104" s="40" t="n">
-        <v>0.46</v>
+        <v>0.23</v>
       </c>
       <c r="M104" s="40" t="n">
-        <v>0.11</v>
+        <v>0.05</v>
       </c>
       <c r="N104" s="41" t="n">
         <v>0</v>
@@ -36496,27 +36527,25 @@
         <v>4000</v>
       </c>
       <c r="F119" s="53" t="n"/>
-      <c r="G119" s="55" t="n">
-        <v>1800</v>
-      </c>
+      <c r="G119" s="55" t="n"/>
       <c r="H119" s="53" t="n"/>
       <c r="I119" s="40" t="n">
         <v>0.0526</v>
       </c>
       <c r="J119" s="40" t="n">
-        <v>0.32</v>
+        <v>0</v>
       </c>
       <c r="K119" s="40" t="n">
         <v>0</v>
       </c>
       <c r="L119" s="40" t="n">
-        <v>0.32</v>
+        <v>0</v>
       </c>
       <c r="M119" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N119" s="41" t="n">
         <v>0.08</v>
-      </c>
-      <c r="N119" s="41" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -37756,23 +37785,23 @@
       </c>
       <c r="F147" s="53" t="n"/>
       <c r="G147" s="55" t="n">
-        <v>1600</v>
+        <v>1200</v>
       </c>
       <c r="H147" s="53" t="n"/>
       <c r="I147" s="40" t="n">
-        <v>0.0588</v>
+        <v>0.0769</v>
       </c>
       <c r="J147" s="40" t="n">
-        <v>0.35</v>
+        <v>0.46</v>
       </c>
       <c r="K147" s="40" t="n">
         <v>1.3</v>
       </c>
       <c r="L147" s="40" t="n">
-        <v>0.73</v>
+        <v>0.8</v>
       </c>
       <c r="M147" s="40" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="N147" s="41" t="n">
         <v>0</v>
@@ -37846,27 +37875,25 @@
         <v>4000</v>
       </c>
       <c r="F149" s="53" t="n"/>
-      <c r="G149" s="55" t="n">
-        <v>1800</v>
-      </c>
+      <c r="G149" s="55" t="n"/>
       <c r="H149" s="53" t="n"/>
       <c r="I149" s="40" t="n">
         <v>0.0526</v>
       </c>
       <c r="J149" s="40" t="n">
-        <v>0.32</v>
+        <v>0</v>
       </c>
       <c r="K149" s="40" t="n">
         <v>0</v>
       </c>
       <c r="L149" s="40" t="n">
-        <v>0.32</v>
+        <v>0</v>
       </c>
       <c r="M149" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N149" s="41" t="n">
         <v>0.08</v>
-      </c>
-      <c r="N149" s="41" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="150">
@@ -37939,23 +37966,23 @@
       </c>
       <c r="F151" s="53" t="n"/>
       <c r="G151" s="55" t="n">
-        <v>1200</v>
+        <v>2500</v>
       </c>
       <c r="H151" s="53" t="n"/>
       <c r="I151" s="40" t="n">
-        <v>0.0769</v>
+        <v>0.0385</v>
       </c>
       <c r="J151" s="40" t="n">
-        <v>0.46</v>
+        <v>0.23</v>
       </c>
       <c r="K151" s="40" t="n">
         <v>0</v>
       </c>
       <c r="L151" s="40" t="n">
-        <v>0.46</v>
+        <v>0.23</v>
       </c>
       <c r="M151" s="40" t="n">
-        <v>0.11</v>
+        <v>0.05</v>
       </c>
       <c r="N151" s="41" t="n">
         <v>0</v>
@@ -38255,23 +38282,23 @@
       </c>
       <c r="F158" s="53" t="n"/>
       <c r="G158" s="55" t="n">
-        <v>5000</v>
+        <v>3500</v>
       </c>
       <c r="H158" s="53" t="n"/>
       <c r="I158" s="40" t="n">
-        <v>0.0196</v>
+        <v>0.0278</v>
       </c>
       <c r="J158" s="40" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="K158" s="40" t="n">
         <v>0</v>
       </c>
       <c r="L158" s="40" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="M158" s="40" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="N158" s="41" t="n">
         <v>0</v>
@@ -38409,7 +38436,7 @@
         <v>1.66</v>
       </c>
       <c r="I5" s="41" t="n">
-        <v>0.013</v>
+        <v>0.0128</v>
       </c>
       <c r="J5" s="40" t="n">
         <v>1.86</v>
@@ -38441,16 +38468,16 @@
         <v>4000</v>
       </c>
       <c r="F6" s="38" t="n">
-        <v>24.5</v>
+        <v>24</v>
       </c>
       <c r="G6" s="45" t="n">
-        <v>6.6</v>
+        <v>6.85</v>
       </c>
       <c r="H6" s="45" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="I6" s="41" t="n">
-        <v>0.0086</v>
+        <v>0.0097</v>
       </c>
       <c r="J6" s="40" t="n">
         <v>1.47</v>
@@ -38491,7 +38518,7 @@
         <v>1.7</v>
       </c>
       <c r="I7" s="41" t="n">
-        <v>0.0122</v>
+        <v>0.012</v>
       </c>
       <c r="J7" s="40" t="n">
         <v>1.39</v>
@@ -38523,16 +38550,16 @@
         <v>4700</v>
       </c>
       <c r="F8" s="38" t="n">
-        <v>25</v>
+        <v>24.75</v>
       </c>
       <c r="G8" s="45" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="H8" s="45" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="I8" s="41" t="n">
-        <v>0.0063</v>
+        <v>0.0065</v>
       </c>
       <c r="J8" s="40" t="n">
         <v>1.57</v>
@@ -38573,7 +38600,7 @@
         <v>1.82</v>
       </c>
       <c r="I9" s="41" t="n">
-        <v>0.0127</v>
+        <v>0.0125</v>
       </c>
       <c r="J9" s="40" t="n">
         <v>2.07</v>
@@ -38614,7 +38641,7 @@
         <v>1.72</v>
       </c>
       <c r="I10" s="41" t="n">
-        <v>0.0151</v>
+        <v>0.0148</v>
       </c>
       <c r="J10" s="40" t="n">
         <v>1.64</v>
@@ -38646,16 +38673,16 @@
         <v>3200</v>
       </c>
       <c r="F11" s="38" t="n">
-        <v>18.75</v>
+        <v>18.5</v>
       </c>
       <c r="G11" s="39" t="n">
-        <v>8.69</v>
+        <v>8.77</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="I11" s="41" t="n">
-        <v>0.0289</v>
+        <v>0.0294</v>
       </c>
       <c r="J11" s="40" t="n">
         <v>1.63</v>
@@ -38687,16 +38714,16 @@
         <v>4600</v>
       </c>
       <c r="F12" s="38" t="n">
-        <v>18.75</v>
+        <v>18.5</v>
       </c>
       <c r="G12" s="39" t="n">
-        <v>8.69</v>
+        <v>8.77</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="I12" s="41" t="n">
-        <v>0.018</v>
+        <v>0.0183</v>
       </c>
       <c r="J12" s="40" t="n">
         <v>1.35</v>
@@ -38737,7 +38764,7 @@
         <v>1.63</v>
       </c>
       <c r="I13" s="41" t="n">
-        <v>0.0061</v>
+        <v>0.006</v>
       </c>
       <c r="J13" s="40" t="n">
         <v>1.78</v>
@@ -38778,7 +38805,7 @@
         <v>1.97</v>
       </c>
       <c r="I14" s="41" t="n">
-        <v>0.0112</v>
+        <v>0.0111</v>
       </c>
       <c r="J14" s="40" t="n">
         <v>2.2</v>
@@ -38819,7 +38846,7 @@
         <v>2.26</v>
       </c>
       <c r="I15" s="41" t="n">
-        <v>0.0168</v>
+        <v>0.0166</v>
       </c>
       <c r="J15" s="40" t="n">
         <v>1.86</v>
@@ -38860,7 +38887,7 @@
         <v>1.56</v>
       </c>
       <c r="I16" s="41" t="n">
-        <v>0.0131</v>
+        <v>0.0129</v>
       </c>
       <c r="J16" s="40" t="n">
         <v>1.83</v>
@@ -38901,7 +38928,7 @@
         <v>2.06</v>
       </c>
       <c r="I17" s="41" t="n">
-        <v>0.0163</v>
+        <v>0.0161</v>
       </c>
       <c r="J17" s="40" t="n">
         <v>1.27</v>
@@ -38933,16 +38960,16 @@
         <v>4200</v>
       </c>
       <c r="F18" s="38" t="n">
-        <v>24.5</v>
+        <v>24</v>
       </c>
       <c r="G18" s="45" t="n">
-        <v>6.6</v>
+        <v>6.85</v>
       </c>
       <c r="H18" s="45" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="I18" s="41" t="n">
-        <v>0.0081</v>
+        <v>0.0091</v>
       </c>
       <c r="J18" s="40" t="n">
         <v>1.57</v>
@@ -38974,16 +39001,16 @@
         <v>3400</v>
       </c>
       <c r="F19" s="38" t="n">
-        <v>25</v>
+        <v>24.75</v>
       </c>
       <c r="G19" s="39" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="I19" s="41" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.01</v>
       </c>
       <c r="J19" s="40" t="n">
         <v>1.73</v>
@@ -39024,7 +39051,7 @@
         <v>1.54</v>
       </c>
       <c r="I20" s="41" t="n">
-        <v>0.0057</v>
+        <v>0.0056</v>
       </c>
       <c r="J20" s="40" t="n">
         <v>1.55</v>
@@ -39065,7 +39092,7 @@
         <v>1.52</v>
       </c>
       <c r="I21" s="41" t="n">
-        <v>0.008</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="J21" s="40" t="n">
         <v>2.25</v>
@@ -39106,7 +39133,7 @@
         <v>2.25</v>
       </c>
       <c r="I22" s="41" t="n">
-        <v>0.0175</v>
+        <v>0.0173</v>
       </c>
       <c r="J22" s="40" t="n">
         <v>2.04</v>
@@ -39147,7 +39174,7 @@
         <v>2.05</v>
       </c>
       <c r="I23" s="41" t="n">
-        <v>0.0203</v>
+        <v>0.02</v>
       </c>
       <c r="J23" s="40" t="n">
         <v>1.68</v>
@@ -39188,7 +39215,7 @@
         <v>2.81</v>
       </c>
       <c r="I24" s="41" t="n">
-        <v>0.0285</v>
+        <v>0.0281</v>
       </c>
       <c r="J24" s="40" t="n">
         <v>1.35</v>
@@ -39229,7 +39256,7 @@
         <v>1.79</v>
       </c>
       <c r="I25" s="41" t="n">
-        <v>0.0075</v>
+        <v>0.0074</v>
       </c>
       <c r="J25" s="40" t="n">
         <v>2.07</v>
@@ -39261,16 +39288,16 @@
         <v>3300</v>
       </c>
       <c r="F26" s="38" t="n">
-        <v>23</v>
+        <v>22.5</v>
       </c>
       <c r="G26" s="45" t="n">
-        <v>7.2</v>
+        <v>7.38</v>
       </c>
       <c r="H26" s="45" t="n">
-        <v>2.18</v>
+        <v>2.23</v>
       </c>
       <c r="I26" s="41" t="n">
-        <v>0.0149</v>
+        <v>0.016</v>
       </c>
       <c r="J26" s="40" t="n">
         <v>1.88</v>
@@ -39311,7 +39338,7 @@
         <v>1.74</v>
       </c>
       <c r="I27" s="41" t="n">
-        <v>0.0131</v>
+        <v>0.0129</v>
       </c>
       <c r="J27" s="40" t="n">
         <v>1.37</v>
@@ -39352,7 +39379,7 @@
         <v>2.35</v>
       </c>
       <c r="I28" s="41" t="n">
-        <v>0.0203</v>
+        <v>0.02</v>
       </c>
       <c r="J28" s="40" t="n">
         <v>1.86</v>
@@ -39393,7 +39420,7 @@
         <v>3.11</v>
       </c>
       <c r="I29" s="41" t="n">
-        <v>0.0447</v>
+        <v>0.044</v>
       </c>
       <c r="J29" s="40" t="n">
         <v>1.97</v>
@@ -39434,7 +39461,7 @@
         <v>2.81</v>
       </c>
       <c r="I30" s="41" t="n">
-        <v>0.0285</v>
+        <v>0.0281</v>
       </c>
       <c r="J30" s="40" t="n">
         <v>2.33</v>

--- a/NFL Current Week Projections.xlsx
+++ b/NFL Current Week Projections.xlsx
@@ -7906,7 +7906,7 @@
         <v>2.34</v>
       </c>
       <c r="Q5" s="41" t="n">
-        <v>0.0283</v>
+        <v>0.0286</v>
       </c>
     </row>
     <row r="6">
@@ -7965,7 +7965,7 @@
         <v>2.29</v>
       </c>
       <c r="Q6" s="41" t="n">
-        <v>0.0242</v>
+        <v>0.0245</v>
       </c>
     </row>
     <row r="7">
@@ -8024,7 +8024,7 @@
         <v>2.35</v>
       </c>
       <c r="Q7" s="41" t="n">
-        <v>0.0333</v>
+        <v>0.0337</v>
       </c>
     </row>
     <row r="8">
@@ -8074,16 +8074,16 @@
         <v>13.24</v>
       </c>
       <c r="N8" s="40" t="n">
-        <v>27.9</v>
+        <v>27.7</v>
       </c>
       <c r="O8" s="40" t="n">
-        <v>19.1</v>
+        <v>19.02</v>
       </c>
       <c r="P8" s="40" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="Q8" s="41" t="n">
-        <v>0.0291</v>
+        <v>0.029</v>
       </c>
     </row>
     <row r="9">
@@ -8127,16 +8127,16 @@
         <v>4.6</v>
       </c>
       <c r="N9" s="40" t="n">
-        <v>26.9</v>
+        <v>0</v>
       </c>
       <c r="O9" s="40" t="n">
-        <v>13.52</v>
+        <v>4.6</v>
       </c>
       <c r="P9" s="40" t="n">
-        <v>1.57</v>
+        <v>0.53</v>
       </c>
       <c r="Q9" s="41" t="n">
-        <v>0.0062</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -8195,7 +8195,7 @@
         <v>2.32</v>
       </c>
       <c r="Q10" s="41" t="n">
-        <v>0.0248</v>
+        <v>0.0251</v>
       </c>
     </row>
     <row r="11">
@@ -8254,7 +8254,7 @@
         <v>2.6</v>
       </c>
       <c r="Q11" s="41" t="n">
-        <v>0.0371</v>
+        <v>0.0376</v>
       </c>
     </row>
     <row r="12">
@@ -8313,7 +8313,7 @@
         <v>2.55</v>
       </c>
       <c r="Q12" s="41" t="n">
-        <v>0.0335</v>
+        <v>0.0339</v>
       </c>
     </row>
     <row r="13">
@@ -8372,7 +8372,7 @@
         <v>2.37</v>
       </c>
       <c r="Q13" s="41" t="n">
-        <v>0.019</v>
+        <v>0.0192</v>
       </c>
     </row>
     <row r="14">
@@ -8431,7 +8431,7 @@
         <v>2.11</v>
       </c>
       <c r="Q14" s="41" t="n">
-        <v>0.0119</v>
+        <v>0.0121</v>
       </c>
     </row>
     <row r="15">
@@ -8490,7 +8490,7 @@
         <v>2.12</v>
       </c>
       <c r="Q15" s="41" t="n">
-        <v>0.0126</v>
+        <v>0.0127</v>
       </c>
     </row>
     <row r="16">
@@ -8549,7 +8549,7 @@
         <v>2.11</v>
       </c>
       <c r="Q16" s="41" t="n">
-        <v>0.0147</v>
+        <v>0.0148</v>
       </c>
     </row>
     <row r="17">
@@ -8599,16 +8599,16 @@
         <v>11</v>
       </c>
       <c r="N17" s="40" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="O17" s="40" t="n">
-        <v>15.68</v>
+        <v>15.72</v>
       </c>
       <c r="P17" s="40" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="Q17" s="41" t="n">
-        <v>0.0165</v>
+        <v>0.0169</v>
       </c>
     </row>
     <row r="18">
@@ -8769,7 +8769,7 @@
         <v>2.27</v>
       </c>
       <c r="Q20" s="41" t="n">
-        <v>0.0141</v>
+        <v>0.0143</v>
       </c>
     </row>
     <row r="21">
@@ -8828,7 +8828,7 @@
         <v>2.2</v>
       </c>
       <c r="Q21" s="41" t="n">
-        <v>0.0156</v>
+        <v>0.0158</v>
       </c>
     </row>
     <row r="22">
@@ -8887,7 +8887,7 @@
         <v>2.22</v>
       </c>
       <c r="Q22" s="41" t="n">
-        <v>0.0168</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="23">
@@ -9064,7 +9064,7 @@
         <v>2.43</v>
       </c>
       <c r="Q25" s="41" t="n">
-        <v>0.0256</v>
+        <v>0.026</v>
       </c>
     </row>
     <row r="26">
@@ -9106,16 +9106,16 @@
         <v>2.75</v>
       </c>
       <c r="N26" s="40" t="n">
-        <v>0</v>
+        <v>21.6</v>
       </c>
       <c r="O26" s="40" t="n">
-        <v>2.75</v>
+        <v>10.29</v>
       </c>
       <c r="P26" s="40" t="n">
-        <v>0.39</v>
+        <v>1.47</v>
       </c>
       <c r="Q26" s="41" t="n">
-        <v>0</v>
+        <v>0.0015</v>
       </c>
     </row>
     <row r="27">
@@ -9380,7 +9380,7 @@
         <v>2.58</v>
       </c>
       <c r="Q31" s="41" t="n">
-        <v>0.0256</v>
+        <v>0.026</v>
       </c>
     </row>
     <row r="32">
@@ -12718,7 +12718,7 @@
         <v>2.34</v>
       </c>
       <c r="O5" s="41" t="n">
-        <v>0.112</v>
+        <v>0.1132</v>
       </c>
     </row>
     <row r="6">
@@ -12771,7 +12771,7 @@
         <v>2.1</v>
       </c>
       <c r="O6" s="41" t="n">
-        <v>0.0737</v>
+        <v>0.0745</v>
       </c>
     </row>
     <row r="7">
@@ -12824,7 +12824,7 @@
         <v>1.96</v>
       </c>
       <c r="O7" s="41" t="n">
-        <v>0.0336</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="8">
@@ -12868,16 +12868,16 @@
         <v>13.95</v>
       </c>
       <c r="L8" s="45" t="n">
-        <v>22.5</v>
+        <v>20.2</v>
       </c>
       <c r="M8" s="40" t="n">
-        <v>17.37</v>
+        <v>16.45</v>
       </c>
       <c r="N8" s="40" t="n">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="O8" s="41" t="n">
-        <v>0.0518</v>
+        <v>0.0438</v>
       </c>
     </row>
     <row r="9">
@@ -12930,7 +12930,7 @@
         <v>1.71</v>
       </c>
       <c r="O9" s="41" t="n">
-        <v>0.0309</v>
+        <v>0.0312</v>
       </c>
     </row>
     <row r="10">
@@ -12983,7 +12983,7 @@
         <v>2.23</v>
       </c>
       <c r="O10" s="41" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.0786</v>
       </c>
     </row>
     <row r="11">
@@ -13027,16 +13027,16 @@
         <v>14.82</v>
       </c>
       <c r="L11" s="39" t="n">
-        <v>21</v>
+        <v>20.3</v>
       </c>
       <c r="M11" s="40" t="n">
-        <v>17.29</v>
+        <v>17.01</v>
       </c>
       <c r="N11" s="40" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="O11" s="41" t="n">
-        <v>0.0605</v>
+        <v>0.058</v>
       </c>
     </row>
     <row r="12">
@@ -13089,7 +13089,7 @@
         <v>2.01</v>
       </c>
       <c r="O12" s="41" t="n">
-        <v>0.0398</v>
+        <v>0.0402</v>
       </c>
     </row>
     <row r="13">
@@ -13142,7 +13142,7 @@
         <v>1.78</v>
       </c>
       <c r="O13" s="41" t="n">
-        <v>0.0157</v>
+        <v>0.0159</v>
       </c>
     </row>
     <row r="14">
@@ -13180,16 +13180,16 @@
         <v>2.93</v>
       </c>
       <c r="L14" s="39" t="n">
-        <v>15.4</v>
+        <v>0</v>
       </c>
       <c r="M14" s="40" t="n">
-        <v>7.92</v>
+        <v>2.93</v>
       </c>
       <c r="N14" s="40" t="n">
-        <v>1.15</v>
+        <v>0.42</v>
       </c>
       <c r="O14" s="41" t="n">
-        <v>0.0042</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -13233,16 +13233,16 @@
         <v>12.24</v>
       </c>
       <c r="L15" s="39" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="M15" s="40" t="n">
-        <v>13.34</v>
+        <v>13.38</v>
       </c>
       <c r="N15" s="40" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="O15" s="41" t="n">
-        <v>0.0287</v>
+        <v>0.0293</v>
       </c>
     </row>
     <row r="16">
@@ -13295,7 +13295,7 @@
         <v>1.78</v>
       </c>
       <c r="O16" s="41" t="n">
-        <v>0.0164</v>
+        <v>0.0166</v>
       </c>
     </row>
     <row r="17">
@@ -13344,7 +13344,7 @@
         <v>1.54</v>
       </c>
       <c r="O17" s="41" t="n">
-        <v>0.0086</v>
+        <v>0.008699999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -13433,16 +13433,16 @@
         <v>10.88</v>
       </c>
       <c r="L19" s="39" t="n">
-        <v>14.6</v>
+        <v>14.9</v>
       </c>
       <c r="M19" s="40" t="n">
-        <v>12.37</v>
+        <v>12.49</v>
       </c>
       <c r="N19" s="40" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="O19" s="41" t="n">
-        <v>0.0199</v>
+        <v>0.0208</v>
       </c>
     </row>
     <row r="20">
@@ -13586,7 +13586,7 @@
         <v>1.72</v>
       </c>
       <c r="O22" s="41" t="n">
-        <v>0.0175</v>
+        <v>0.0177</v>
       </c>
     </row>
     <row r="23">
@@ -13626,16 +13626,16 @@
         <v>4.13</v>
       </c>
       <c r="L23" s="45" t="n">
-        <v>7.3</v>
+        <v>8.6</v>
       </c>
       <c r="M23" s="40" t="n">
-        <v>5.4</v>
+        <v>5.92</v>
       </c>
       <c r="N23" s="40" t="n">
-        <v>0.82</v>
+        <v>0.9</v>
       </c>
       <c r="O23" s="41" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0011</v>
       </c>
     </row>
     <row r="24">
@@ -13673,16 +13673,16 @@
         <v>3.14</v>
       </c>
       <c r="L24" s="39" t="n">
-        <v>9.800000000000001</v>
+        <v>16</v>
       </c>
       <c r="M24" s="40" t="n">
-        <v>5.81</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="N24" s="40" t="n">
-        <v>0.92</v>
+        <v>1.32</v>
       </c>
       <c r="O24" s="41" t="n">
-        <v>0.001</v>
+        <v>0.0058</v>
       </c>
     </row>
     <row r="25">
@@ -13774,7 +13774,7 @@
         <v>4.15</v>
       </c>
       <c r="O26" s="41" t="n">
-        <v>0.2262</v>
+        <v>0.2286</v>
       </c>
     </row>
     <row r="27">
@@ -13872,7 +13872,7 @@
         <v>1.5</v>
       </c>
       <c r="O28" s="41" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="29">
@@ -13916,16 +13916,16 @@
         <v>7.54</v>
       </c>
       <c r="L29" s="39" t="n">
-        <v>11.4</v>
+        <v>10.7</v>
       </c>
       <c r="M29" s="40" t="n">
-        <v>9.09</v>
+        <v>8.81</v>
       </c>
       <c r="N29" s="40" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="O29" s="41" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.0089</v>
       </c>
     </row>
     <row r="30">
@@ -14025,7 +14025,7 @@
         <v>2.23</v>
       </c>
       <c r="O31" s="41" t="n">
-        <v>0.0315</v>
+        <v>0.0318</v>
       </c>
     </row>
     <row r="32">
@@ -14069,16 +14069,16 @@
         <v>12.32</v>
       </c>
       <c r="L32" s="45" t="n">
-        <v>14.9</v>
+        <v>15.3</v>
       </c>
       <c r="M32" s="40" t="n">
-        <v>13.35</v>
+        <v>13.51</v>
       </c>
       <c r="N32" s="40" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="O32" s="41" t="n">
-        <v>0.0349</v>
+        <v>0.0368</v>
       </c>
     </row>
     <row r="33">
@@ -14131,7 +14131,7 @@
         <v>1.8</v>
       </c>
       <c r="O33" s="41" t="n">
-        <v>0.018</v>
+        <v>0.0182</v>
       </c>
     </row>
     <row r="34">
@@ -14471,7 +14471,7 @@
         <v>1.59</v>
       </c>
       <c r="O40" s="41" t="n">
-        <v>0.0094</v>
+        <v>0.0095</v>
       </c>
     </row>
     <row r="41">
@@ -14515,16 +14515,16 @@
         <v>5.91</v>
       </c>
       <c r="L41" s="39" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="M41" s="40" t="n">
-        <v>6.07</v>
+        <v>6.11</v>
       </c>
       <c r="N41" s="40" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="O41" s="41" t="n">
-        <v>0.0017</v>
+        <v>0.0018</v>
       </c>
     </row>
     <row r="42">
@@ -14661,13 +14661,13 @@
         <v>2.11</v>
       </c>
       <c r="L44" s="45" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="M44" s="40" t="n">
-        <v>3.22</v>
+        <v>2.98</v>
       </c>
       <c r="N44" s="40" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="O44" s="41" t="n">
         <v>0</v>
@@ -14761,13 +14761,13 @@
         <v>0.75</v>
       </c>
       <c r="L46" s="45" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="M46" s="40" t="n">
-        <v>2.85</v>
+        <v>2.73</v>
       </c>
       <c r="N46" s="40" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="O46" s="41" t="n">
         <v>0</v>
@@ -14865,16 +14865,16 @@
         <v>5.09</v>
       </c>
       <c r="L48" s="39" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="M48" s="40" t="n">
-        <v>5.46</v>
+        <v>5.1</v>
       </c>
       <c r="N48" s="40" t="n">
-        <v>1.03</v>
+        <v>0.96</v>
       </c>
       <c r="O48" s="41" t="n">
-        <v>0.001</v>
+        <v>0.0005999999999999999</v>
       </c>
     </row>
     <row r="49">
@@ -15765,13 +15765,13 @@
         <v>0.86</v>
       </c>
       <c r="L67" s="40" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M67" s="40" t="n">
-        <v>0.86</v>
+        <v>2.35</v>
       </c>
       <c r="N67" s="40" t="n">
-        <v>0.19</v>
+        <v>0.54</v>
       </c>
       <c r="O67" s="41" t="n">
         <v>0</v>
@@ -15859,13 +15859,13 @@
         <v>0.8</v>
       </c>
       <c r="L69" s="40" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M69" s="40" t="n">
-        <v>0.8</v>
+        <v>3.76</v>
       </c>
       <c r="N69" s="40" t="n">
-        <v>0.16</v>
+        <v>0.74</v>
       </c>
       <c r="O69" s="41" t="n">
         <v>0</v>
@@ -16698,13 +16698,13 @@
         <v>1</v>
       </c>
       <c r="L87" s="40" t="n">
-        <v>5.7</v>
+        <v>6.7</v>
       </c>
       <c r="M87" s="40" t="n">
-        <v>2.88</v>
+        <v>3.28</v>
       </c>
       <c r="N87" s="40" t="n">
-        <v>0.72</v>
+        <v>0.82</v>
       </c>
       <c r="O87" s="41" t="n">
         <v>0</v>
@@ -18319,16 +18319,16 @@
         <v>5.09</v>
       </c>
       <c r="L122" s="40" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="M122" s="40" t="n">
-        <v>5.46</v>
+        <v>5.1</v>
       </c>
       <c r="N122" s="40" t="n">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="O122" s="41" t="n">
-        <v>0.001</v>
+        <v>0.0005999999999999999</v>
       </c>
     </row>
     <row r="123">
@@ -19692,7 +19692,7 @@
         <v>1.86</v>
       </c>
       <c r="N5" s="41" t="n">
-        <v>0.0864</v>
+        <v>0.08550000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -19742,7 +19742,7 @@
         <v>1.79</v>
       </c>
       <c r="N6" s="41" t="n">
-        <v>0.1131</v>
+        <v>0.1118</v>
       </c>
     </row>
     <row r="7">
@@ -19779,16 +19779,16 @@
         <v>2.14</v>
       </c>
       <c r="K7" s="39" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="L7" s="40" t="n">
-        <v>7.41</v>
+        <v>6.85</v>
       </c>
       <c r="M7" s="40" t="n">
-        <v>0.95</v>
+        <v>0.88</v>
       </c>
       <c r="N7" s="41" t="n">
-        <v>0.0074</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="8">
@@ -19825,16 +19825,16 @@
         <v>2.93</v>
       </c>
       <c r="K8" s="39" t="n">
-        <v>0</v>
+        <v>21.2</v>
       </c>
       <c r="L8" s="40" t="n">
-        <v>2.93</v>
+        <v>10.24</v>
       </c>
       <c r="M8" s="40" t="n">
-        <v>0.32</v>
+        <v>1.12</v>
       </c>
       <c r="N8" s="41" t="n">
-        <v>0</v>
+        <v>0.0226</v>
       </c>
     </row>
     <row r="9">
@@ -19884,7 +19884,7 @@
         <v>1.86</v>
       </c>
       <c r="N9" s="41" t="n">
-        <v>0.0785</v>
+        <v>0.0776</v>
       </c>
     </row>
     <row r="10">
@@ -19934,7 +19934,7 @@
         <v>2.08</v>
       </c>
       <c r="N10" s="41" t="n">
-        <v>0.1023</v>
+        <v>0.1012</v>
       </c>
     </row>
     <row r="11">
@@ -20028,7 +20028,7 @@
         <v>1.69</v>
       </c>
       <c r="N12" s="41" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.0703</v>
       </c>
     </row>
     <row r="13">
@@ -20078,7 +20078,7 @@
         <v>2.04</v>
       </c>
       <c r="N13" s="41" t="n">
-        <v>0.0803</v>
+        <v>0.0794</v>
       </c>
     </row>
     <row r="14">
@@ -20128,7 +20128,7 @@
         <v>1.68</v>
       </c>
       <c r="N14" s="41" t="n">
-        <v>0.058</v>
+        <v>0.0574</v>
       </c>
     </row>
     <row r="15">
@@ -20178,7 +20178,7 @@
         <v>1.71</v>
       </c>
       <c r="N15" s="41" t="n">
-        <v>0.0837</v>
+        <v>0.0828</v>
       </c>
     </row>
     <row r="16">
@@ -20219,16 +20219,16 @@
         <v>14.83</v>
       </c>
       <c r="K16" s="45" t="n">
-        <v>20.3</v>
+        <v>20.1</v>
       </c>
       <c r="L16" s="40" t="n">
-        <v>17.02</v>
+        <v>16.94</v>
       </c>
       <c r="M16" s="40" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="N16" s="41" t="n">
-        <v>0.1391</v>
+        <v>0.1355</v>
       </c>
     </row>
     <row r="17">
@@ -20269,16 +20269,16 @@
         <v>13.65</v>
       </c>
       <c r="K17" s="39" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="L17" s="40" t="n">
-        <v>14.63</v>
+        <v>14.59</v>
       </c>
       <c r="M17" s="40" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="N17" s="41" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.09660000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -20328,7 +20328,7 @@
         <v>1.73</v>
       </c>
       <c r="N18" s="41" t="n">
-        <v>0.0727</v>
+        <v>0.07190000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -20413,16 +20413,16 @@
         <v>11.2</v>
       </c>
       <c r="K20" s="39" t="n">
-        <v>13.4</v>
+        <v>13.2</v>
       </c>
       <c r="L20" s="40" t="n">
-        <v>12.08</v>
+        <v>12</v>
       </c>
       <c r="M20" s="40" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="N20" s="41" t="n">
-        <v>0.0586</v>
+        <v>0.0566</v>
       </c>
     </row>
     <row r="21">
@@ -20463,16 +20463,16 @@
         <v>5.5</v>
       </c>
       <c r="K21" s="45" t="n">
-        <v>6.9</v>
+        <v>7.4</v>
       </c>
       <c r="L21" s="40" t="n">
-        <v>6.06</v>
+        <v>6.26</v>
       </c>
       <c r="M21" s="40" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="N21" s="41" t="n">
-        <v>0.0046</v>
+        <v>0.0055</v>
       </c>
     </row>
     <row r="22">
@@ -20522,7 +20522,7 @@
         <v>1.38</v>
       </c>
       <c r="N22" s="41" t="n">
-        <v>0.0167</v>
+        <v>0.0166</v>
       </c>
     </row>
     <row r="23">
@@ -20572,7 +20572,7 @@
         <v>1.7</v>
       </c>
       <c r="N23" s="41" t="n">
-        <v>0.0343</v>
+        <v>0.0339</v>
       </c>
     </row>
     <row r="24">
@@ -20666,7 +20666,7 @@
         <v>1.5</v>
       </c>
       <c r="N25" s="41" t="n">
-        <v>0.0272</v>
+        <v>0.0269</v>
       </c>
     </row>
     <row r="26">
@@ -20716,7 +20716,7 @@
         <v>1.14</v>
       </c>
       <c r="N26" s="41" t="n">
-        <v>0.0051</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="27">
@@ -20810,7 +20810,7 @@
         <v>1.62</v>
       </c>
       <c r="N28" s="41" t="n">
-        <v>0.0295</v>
+        <v>0.0292</v>
       </c>
     </row>
     <row r="29">
@@ -20860,7 +20860,7 @@
         <v>1.55</v>
       </c>
       <c r="N29" s="41" t="n">
-        <v>0.032</v>
+        <v>0.0316</v>
       </c>
     </row>
     <row r="30">
@@ -20954,7 +20954,7 @@
         <v>1.32</v>
       </c>
       <c r="N31" s="41" t="n">
-        <v>0.0131</v>
+        <v>0.0129</v>
       </c>
     </row>
     <row r="32">
@@ -21004,7 +21004,7 @@
         <v>1.51</v>
       </c>
       <c r="N32" s="41" t="n">
-        <v>0.0302</v>
+        <v>0.0298</v>
       </c>
     </row>
     <row r="33">
@@ -21054,7 +21054,7 @@
         <v>1.45</v>
       </c>
       <c r="N33" s="41" t="n">
-        <v>0.0181</v>
+        <v>0.0179</v>
       </c>
     </row>
     <row r="34">
@@ -21148,7 +21148,7 @@
         <v>1.4</v>
       </c>
       <c r="N35" s="41" t="n">
-        <v>0.0115</v>
+        <v>0.0114</v>
       </c>
     </row>
     <row r="36">
@@ -21198,7 +21198,7 @@
         <v>1.32</v>
       </c>
       <c r="N36" s="41" t="n">
-        <v>0.0148</v>
+        <v>0.0147</v>
       </c>
     </row>
     <row r="37">
@@ -21248,7 +21248,7 @@
         <v>1.42</v>
       </c>
       <c r="N37" s="41" t="n">
-        <v>0.0182</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="38">
@@ -21392,7 +21392,7 @@
         <v>1.17</v>
       </c>
       <c r="N40" s="41" t="n">
-        <v>0.0062</v>
+        <v>0.0061</v>
       </c>
     </row>
     <row r="41">
@@ -21517,13 +21517,13 @@
         <v>1.04</v>
       </c>
       <c r="K43" s="45" t="n">
-        <v>6.6</v>
+        <v>5.5</v>
       </c>
       <c r="L43" s="40" t="n">
-        <v>3.27</v>
+        <v>2.83</v>
       </c>
       <c r="M43" s="40" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="N43" s="41" t="n">
         <v>0</v>
@@ -21576,7 +21576,7 @@
         <v>1.13</v>
       </c>
       <c r="N44" s="41" t="n">
-        <v>0.0042</v>
+        <v>0.0041</v>
       </c>
     </row>
     <row r="45">
@@ -21626,7 +21626,7 @@
         <v>1.4</v>
       </c>
       <c r="N45" s="41" t="n">
-        <v>0.004</v>
+        <v>0.0039</v>
       </c>
     </row>
     <row r="46">
@@ -21667,16 +21667,16 @@
         <v>8.32</v>
       </c>
       <c r="K46" s="45" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="L46" s="40" t="n">
-        <v>8.949999999999999</v>
+        <v>8.99</v>
       </c>
       <c r="M46" s="40" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="N46" s="41" t="n">
-        <v>0.0273</v>
+        <v>0.0275</v>
       </c>
     </row>
     <row r="47">
@@ -21763,16 +21763,16 @@
         <v>6.36</v>
       </c>
       <c r="K48" s="39" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="L48" s="40" t="n">
-        <v>7.82</v>
+        <v>7.58</v>
       </c>
       <c r="M48" s="40" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="N48" s="41" t="n">
-        <v>0.0172</v>
+        <v>0.0148</v>
       </c>
     </row>
     <row r="49">
@@ -21813,16 +21813,16 @@
         <v>5.1</v>
       </c>
       <c r="K49" s="39" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="L49" s="40" t="n">
-        <v>5.86</v>
+        <v>6.06</v>
       </c>
       <c r="M49" s="40" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="N49" s="41" t="n">
-        <v>0.0039</v>
+        <v>0.0047</v>
       </c>
     </row>
     <row r="50">
@@ -22156,7 +22156,7 @@
         <v>1.38</v>
       </c>
       <c r="N56" s="41" t="n">
-        <v>0.0138</v>
+        <v>0.0137</v>
       </c>
     </row>
     <row r="57">
@@ -22382,16 +22382,16 @@
         <v>1.58</v>
       </c>
       <c r="K61" s="39" t="n">
-        <v>9.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="L61" s="40" t="n">
-        <v>4.63</v>
+        <v>3.75</v>
       </c>
       <c r="M61" s="40" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.76</v>
       </c>
       <c r="N61" s="41" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -22485,7 +22485,7 @@
         <v>1.14</v>
       </c>
       <c r="N63" s="41" t="n">
-        <v>0.005</v>
+        <v>0.0049</v>
       </c>
     </row>
     <row r="64">
@@ -22576,13 +22576,13 @@
         <v>3.24</v>
       </c>
       <c r="K65" s="45" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L65" s="40" t="n">
-        <v>4.03</v>
+        <v>3.99</v>
       </c>
       <c r="M65" s="40" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="N65" s="41" t="n">
         <v>0</v>
@@ -22635,7 +22635,7 @@
         <v>1.28</v>
       </c>
       <c r="N66" s="41" t="n">
-        <v>0.0111</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="67">
@@ -22772,13 +22772,13 @@
         <v>1.14</v>
       </c>
       <c r="K69" s="45" t="n">
-        <v>6.3</v>
+        <v>4.4</v>
       </c>
       <c r="L69" s="40" t="n">
-        <v>3.21</v>
+        <v>2.45</v>
       </c>
       <c r="M69" s="40" t="n">
-        <v>0.8</v>
+        <v>0.61</v>
       </c>
       <c r="N69" s="41" t="n">
         <v>0</v>
@@ -22918,13 +22918,13 @@
         <v>0.38</v>
       </c>
       <c r="K72" s="45" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="L72" s="40" t="n">
-        <v>0.78</v>
+        <v>0.95</v>
       </c>
       <c r="M72" s="40" t="n">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="N72" s="41" t="n">
         <v>0</v>
@@ -22977,7 +22977,7 @@
         <v>1.37</v>
       </c>
       <c r="N73" s="41" t="n">
-        <v>0.0071</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="74">
@@ -23014,13 +23014,13 @@
         <v>0.4</v>
       </c>
       <c r="K74" s="39" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="L74" s="40" t="n">
-        <v>1.08</v>
+        <v>0.96</v>
       </c>
       <c r="M74" s="40" t="n">
-        <v>0.24</v>
+        <v>0.21</v>
       </c>
       <c r="N74" s="41" t="n">
         <v>0</v>
@@ -24446,13 +24446,13 @@
         <v>1.87</v>
       </c>
       <c r="K105" s="45" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="L105" s="40" t="n">
-        <v>2.36</v>
+        <v>2.72</v>
       </c>
       <c r="M105" s="40" t="n">
-        <v>0.48</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="N105" s="41" t="n">
         <v>0</v>
@@ -24721,13 +24721,13 @@
         <v>0.8</v>
       </c>
       <c r="K111" s="45" t="n">
-        <v>7.9</v>
+        <v>4</v>
       </c>
       <c r="L111" s="40" t="n">
-        <v>3.64</v>
+        <v>2.08</v>
       </c>
       <c r="M111" s="40" t="n">
-        <v>0.85</v>
+        <v>0.48</v>
       </c>
       <c r="N111" s="41" t="n">
         <v>0</v>
@@ -25365,13 +25365,13 @@
         <v>0.21</v>
       </c>
       <c r="K125" s="39" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="L125" s="40" t="n">
-        <v>0.21</v>
+        <v>0.96</v>
       </c>
       <c r="M125" s="40" t="n">
-        <v>0.05</v>
+        <v>0.22</v>
       </c>
       <c r="N125" s="41" t="n">
         <v>0</v>
@@ -25415,13 +25415,13 @@
         <v>1.96</v>
       </c>
       <c r="K126" s="39" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="L126" s="40" t="n">
-        <v>2.3</v>
+        <v>1.96</v>
       </c>
       <c r="M126" s="40" t="n">
-        <v>0.46</v>
+        <v>0.39</v>
       </c>
       <c r="N126" s="41" t="n">
         <v>0</v>
@@ -25461,13 +25461,13 @@
         <v>0.92</v>
       </c>
       <c r="K127" s="39" t="n">
-        <v>7.5</v>
+        <v>2.9</v>
       </c>
       <c r="L127" s="40" t="n">
-        <v>3.55</v>
+        <v>1.71</v>
       </c>
       <c r="M127" s="40" t="n">
-        <v>0.79</v>
+        <v>0.38</v>
       </c>
       <c r="N127" s="41" t="n">
         <v>0</v>
@@ -25919,13 +25919,13 @@
         <v>0.33</v>
       </c>
       <c r="K137" s="39" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="L137" s="40" t="n">
-        <v>1.28</v>
+        <v>0.33</v>
       </c>
       <c r="M137" s="40" t="n">
-        <v>0.31</v>
+        <v>0.08</v>
       </c>
       <c r="N137" s="41" t="n">
         <v>0</v>
@@ -26144,13 +26144,13 @@
         <v>0.29</v>
       </c>
       <c r="K142" s="40" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="L142" s="40" t="n">
-        <v>1.65</v>
+        <v>0.29</v>
       </c>
       <c r="M142" s="40" t="n">
-        <v>0.4</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N142" s="41" t="n">
         <v>0</v>
@@ -26914,13 +26914,13 @@
         <v>2.15</v>
       </c>
       <c r="K159" s="40" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="L159" s="40" t="n">
-        <v>1.93</v>
+        <v>2.13</v>
       </c>
       <c r="M159" s="40" t="n">
-        <v>0.38</v>
+        <v>0.42</v>
       </c>
       <c r="N159" s="41" t="n">
         <v>0</v>
@@ -29124,13 +29124,13 @@
         <v>2.15</v>
       </c>
       <c r="K208" s="40" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="L208" s="40" t="n">
-        <v>1.93</v>
+        <v>2.13</v>
       </c>
       <c r="M208" s="40" t="n">
-        <v>0.48</v>
+        <v>0.53</v>
       </c>
       <c r="N208" s="41" t="n">
         <v>0</v>
@@ -31262,7 +31262,7 @@
         <v>1.84</v>
       </c>
       <c r="N5" s="41" t="n">
-        <v>0.07920000000000001</v>
+        <v>0.0794</v>
       </c>
     </row>
     <row r="6">
@@ -31312,7 +31312,7 @@
         <v>2.01</v>
       </c>
       <c r="N6" s="41" t="n">
-        <v>0.0503</v>
+        <v>0.0504</v>
       </c>
     </row>
     <row r="7">
@@ -31408,7 +31408,7 @@
         <v>1.81</v>
       </c>
       <c r="N8" s="41" t="n">
-        <v>0.0609</v>
+        <v>0.0611</v>
       </c>
     </row>
     <row r="9">
@@ -31458,7 +31458,7 @@
         <v>2.12</v>
       </c>
       <c r="N9" s="41" t="n">
-        <v>0.0834</v>
+        <v>0.08359999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -31508,7 +31508,7 @@
         <v>1.79</v>
       </c>
       <c r="N10" s="41" t="n">
-        <v>0.0368</v>
+        <v>0.0369</v>
       </c>
     </row>
     <row r="11">
@@ -31652,7 +31652,7 @@
         <v>1.62</v>
       </c>
       <c r="N13" s="41" t="n">
-        <v>0.02</v>
+        <v>0.0201</v>
       </c>
     </row>
     <row r="14">
@@ -31739,16 +31739,16 @@
         <v>1.79</v>
       </c>
       <c r="K15" s="39" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="L15" s="40" t="n">
-        <v>4.03</v>
+        <v>3.71</v>
       </c>
       <c r="M15" s="40" t="n">
-        <v>0.82</v>
+        <v>0.76</v>
       </c>
       <c r="N15" s="41" t="n">
-        <v>0.0007</v>
+        <v>0.0004</v>
       </c>
     </row>
     <row r="16">
@@ -31798,7 +31798,7 @@
         <v>1.26</v>
       </c>
       <c r="N16" s="41" t="n">
-        <v>0.0083</v>
+        <v>0.008399999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -31898,7 +31898,7 @@
         <v>1.82</v>
       </c>
       <c r="N18" s="41" t="n">
-        <v>0.036</v>
+        <v>0.0361</v>
       </c>
     </row>
     <row r="19">
@@ -32179,16 +32179,16 @@
         <v>1.74</v>
       </c>
       <c r="K24" s="39" t="n">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
       <c r="L24" s="40" t="n">
-        <v>4.2</v>
+        <v>3.88</v>
       </c>
       <c r="M24" s="40" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.75</v>
       </c>
       <c r="N24" s="41" t="n">
-        <v>0.0009</v>
+        <v>0.0005</v>
       </c>
     </row>
     <row r="25">
@@ -32317,13 +32317,13 @@
         <v>0</v>
       </c>
       <c r="K27" s="45" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="L27" s="40" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="M27" s="40" t="n">
-        <v>0.75</v>
+        <v>0.68</v>
       </c>
       <c r="N27" s="41" t="n">
         <v>0</v>
@@ -32605,10 +32605,10 @@
         <v>0.46</v>
       </c>
       <c r="K33" s="39" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="L33" s="40" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="M33" s="40" t="n">
         <v>0.19</v>
@@ -32841,10 +32841,10 @@
         <v>1.06</v>
       </c>
       <c r="K38" s="39" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="L38" s="40" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="M38" s="40" t="n">
         <v>0.29</v>
@@ -32977,16 +32977,16 @@
         <v>1.69</v>
       </c>
       <c r="K41" s="45" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="L41" s="40" t="n">
-        <v>4.41</v>
+        <v>4.01</v>
       </c>
       <c r="M41" s="40" t="n">
-        <v>0.87</v>
+        <v>0.79</v>
       </c>
       <c r="N41" s="41" t="n">
-        <v>0.0012</v>
+        <v>0.0007</v>
       </c>
     </row>
     <row r="42">
@@ -33492,13 +33492,13 @@
         <v>0.55</v>
       </c>
       <c r="K52" s="40" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L52" s="40" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="M52" s="40" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="N52" s="41" t="n">
         <v>0</v>
@@ -33629,13 +33629,13 @@
         <v>0.75</v>
       </c>
       <c r="K55" s="40" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="L55" s="40" t="n">
-        <v>1.41</v>
+        <v>1.13</v>
       </c>
       <c r="M55" s="40" t="n">
-        <v>0.34</v>
+        <v>0.27</v>
       </c>
       <c r="N55" s="41" t="n">
         <v>0</v>
